--- a/database.xlsx
+++ b/database.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khant Swe\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khant Swe\OneDrive\桌面\全球腐蚀调研\Europe\Russia\russia-corrosion-map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7741BEFF-DCC1-4CED-AD03-E876DC73B622}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3361C74C-2420-4339-8066-AB7DBF634DB4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25135" windowHeight="10093" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="247">
   <si>
     <t>site_id</t>
   </si>
@@ -448,9 +448,6 @@
     <t>New Zealand</t>
   </si>
   <si>
-    <t>Sub-Antarctic Island</t>
-  </si>
-  <si>
     <t>Australia</t>
   </si>
   <si>
@@ -484,9 +481,6 @@
     <t>site_type</t>
   </si>
   <si>
-    <t>research station</t>
-  </si>
-  <si>
     <t>Research station</t>
   </si>
   <si>
@@ -508,12 +502,6 @@
     <t>Locality</t>
   </si>
   <si>
-    <t>Village/locality</t>
-  </si>
-  <si>
-    <t>Town/locality</t>
-  </si>
-  <si>
     <t xml:space="preserve">Village </t>
   </si>
   <si>
@@ -583,9 +571,6 @@
     <t>Sub-arctic test site</t>
   </si>
   <si>
-    <t>Sub-arctic/city</t>
-  </si>
-  <si>
     <t>AQ-AU-002</t>
   </si>
   <si>
@@ -706,9 +691,6 @@
     <t>Oslo</t>
   </si>
   <si>
-    <t>Coastal, Urban</t>
-  </si>
-  <si>
     <t>1980-2026</t>
   </si>
   <si>
@@ -773,6 +755,12 @@
   </si>
   <si>
     <t>source_3</t>
+  </si>
+  <si>
+    <t>Sub-Antarctic Islands</t>
+  </si>
+  <si>
+    <t>Town</t>
   </si>
 </sst>
 </file>
@@ -1227,7 +1215,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -1236,7 +1224,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -1254,13 +1242,13 @@
         <v>8</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="O1" s="3" t="s">
         <v>9</v>
@@ -1268,13 +1256,13 @@
     </row>
     <row r="2" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D2">
         <v>-77.52</v>
@@ -1289,13 +1277,13 @@
         <v>141</v>
       </c>
       <c r="I2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J2" t="s">
         <v>65</v>
       </c>
       <c r="K2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>140</v>
@@ -1308,13 +1296,13 @@
     </row>
     <row r="3" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D3">
         <v>-77.63</v>
@@ -1329,13 +1317,13 @@
         <v>141</v>
       </c>
       <c r="I3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J3" t="s">
         <v>66</v>
       </c>
       <c r="K3" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L3" s="4" t="s">
         <v>140</v>
@@ -1348,13 +1336,13 @@
     </row>
     <row r="4" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D4">
         <v>-66.55</v>
@@ -1372,7 +1360,7 @@
         <v>62</v>
       </c>
       <c r="I4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J4" t="s">
         <v>67</v>
@@ -1391,13 +1379,13 @@
     </row>
     <row r="5" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>142</v>
+        <v>245</v>
       </c>
       <c r="D5">
         <v>-52.81</v>
@@ -1406,13 +1394,13 @@
         <v>158.44</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>245</v>
       </c>
       <c r="G5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J5" t="s">
         <v>68</v>
@@ -1431,13 +1419,13 @@
     </row>
     <row r="6" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>142</v>
+        <v>245</v>
       </c>
       <c r="D6">
         <v>-51.55</v>
@@ -1446,13 +1434,13 @@
         <v>80.3</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>245</v>
       </c>
       <c r="G6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J6" t="s">
         <v>69</v>
@@ -1471,13 +1459,13 @@
     </row>
     <row r="7" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>142</v>
+        <v>245</v>
       </c>
       <c r="D7">
         <v>-46.88</v>
@@ -1486,13 +1474,13 @@
         <v>37.86</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>245</v>
       </c>
       <c r="G7" t="s">
         <v>139</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J7" t="s">
         <v>70</v>
@@ -1511,13 +1499,13 @@
     </row>
     <row r="8" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>142</v>
+        <v>245</v>
       </c>
       <c r="D8">
         <v>-60.716999999999999</v>
@@ -1526,13 +1514,13 @@
         <v>-45.6</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>245</v>
       </c>
       <c r="G8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J8" t="s">
         <v>71</v>
@@ -1551,13 +1539,13 @@
     </row>
     <row r="9" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D9">
         <v>-67.566999999999993</v>
@@ -1569,10 +1557,10 @@
         <v>59</v>
       </c>
       <c r="G9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J9" t="s">
         <v>71</v>
@@ -1591,13 +1579,13 @@
     </row>
     <row r="10" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B10" t="s">
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D10">
         <v>-67.599999999999994</v>
@@ -1609,10 +1597,10 @@
         <v>59</v>
       </c>
       <c r="G10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J10" t="s">
         <v>72</v>
@@ -1631,13 +1619,13 @@
     </row>
     <row r="11" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D11">
         <v>-68.483000000000004</v>
@@ -1652,7 +1640,7 @@
         <v>139</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J11" t="s">
         <v>73</v>
@@ -1671,13 +1659,13 @@
     </row>
     <row r="12" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B12" t="s">
         <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D12">
         <v>-68.650000000000006</v>
@@ -1689,10 +1677,10 @@
         <v>59</v>
       </c>
       <c r="G12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J12" t="s">
         <v>74</v>
@@ -1711,13 +1699,13 @@
     </row>
     <row r="13" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B13" t="s">
         <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D13">
         <v>-71.283000000000001</v>
@@ -1729,10 +1717,10 @@
         <v>59</v>
       </c>
       <c r="G13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J13" t="s">
         <v>75</v>
@@ -1751,13 +1739,13 @@
     </row>
     <row r="14" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B14" t="s">
         <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D14">
         <v>-76.05</v>
@@ -1769,10 +1757,10 @@
         <v>59</v>
       </c>
       <c r="G14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J14" t="s">
         <v>76</v>
@@ -1791,13 +1779,13 @@
     </row>
     <row r="15" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s">
         <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D15">
         <v>-78.45</v>
@@ -1815,7 +1803,7 @@
         <v>62</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J15" t="s">
         <v>77</v>
@@ -1834,13 +1822,13 @@
     </row>
     <row r="16" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B16" t="s">
         <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D16">
         <v>-90</v>
@@ -1852,10 +1840,10 @@
         <v>59</v>
       </c>
       <c r="G16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J16" t="s">
         <v>78</v>
@@ -1874,13 +1862,13 @@
     </row>
     <row r="17" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B17" t="s">
         <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D17">
         <v>67.13</v>
@@ -1895,16 +1883,16 @@
         <v>60</v>
       </c>
       <c r="I17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J17" t="s">
         <v>79</v>
       </c>
       <c r="K17" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
@@ -1914,13 +1902,13 @@
     </row>
     <row r="18" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D18">
         <v>68.760000000000005</v>
@@ -1935,16 +1923,16 @@
         <v>60</v>
       </c>
       <c r="I18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J18" t="s">
         <v>79</v>
       </c>
       <c r="K18" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
@@ -1954,13 +1942,13 @@
     </row>
     <row r="19" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B19" t="s">
         <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D19">
         <v>67.13</v>
@@ -1975,16 +1963,16 @@
         <v>60</v>
       </c>
       <c r="I19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J19" t="s">
         <v>80</v>
       </c>
       <c r="K19" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M19" s="4"/>
       <c r="N19" s="4"/>
@@ -1994,13 +1982,13 @@
     </row>
     <row r="20" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B20" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C20" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D20">
         <v>69.650000000000006</v>
@@ -2015,22 +2003,22 @@
         <v>60</v>
       </c>
       <c r="I20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J20" t="s">
         <v>81</v>
       </c>
       <c r="K20" t="s">
+        <v>229</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="N20" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="N20" s="4" t="s">
-        <v>241</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>104</v>
@@ -2038,13 +2026,13 @@
     </row>
     <row r="21" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B21" t="s">
         <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D21">
         <v>69.650000000000006</v>
@@ -2059,22 +2047,22 @@
         <v>60</v>
       </c>
       <c r="I21" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J21" t="s">
         <v>82</v>
       </c>
       <c r="K21" t="s">
+        <v>229</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="N21" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="N21" s="4" t="s">
-        <v>241</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>105</v>
@@ -2082,7 +2070,7 @@
     </row>
     <row r="22" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B22" t="s">
         <v>29</v>
@@ -2103,22 +2091,22 @@
         <v>60</v>
       </c>
       <c r="I22" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J22" t="s">
         <v>81</v>
       </c>
       <c r="K22" t="s">
+        <v>229</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="N22" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="M22" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="N22" s="4" t="s">
-        <v>241</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>106</v>
@@ -2126,13 +2114,13 @@
     </row>
     <row r="23" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B23" t="s">
         <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D23">
         <v>69.19</v>
@@ -2147,22 +2135,22 @@
         <v>60</v>
       </c>
       <c r="I23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J23" t="s">
         <v>82</v>
       </c>
       <c r="K23" t="s">
+        <v>229</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="N23" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="N23" s="4" t="s">
-        <v>241</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>107</v>
@@ -2170,13 +2158,13 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B24" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C24" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D24">
         <v>69.38</v>
@@ -2191,29 +2179,29 @@
         <v>60</v>
       </c>
       <c r="I24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J24" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="K24" t="s">
+        <v>229</v>
+      </c>
+      <c r="L24" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="L24" s="4" t="s">
-        <v>241</v>
       </c>
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
     </row>
     <row r="25" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
       </c>
       <c r="C25" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D25">
         <v>69.3</v>
@@ -2231,22 +2219,22 @@
         <v>62</v>
       </c>
       <c r="I25" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J25" t="s">
         <v>81</v>
       </c>
       <c r="K25" t="s">
+        <v>229</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="N25" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="M25" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="N25" s="4" t="s">
-        <v>241</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>108</v>
@@ -2254,13 +2242,13 @@
     </row>
     <row r="26" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B26" t="s">
         <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D26">
         <v>69.510000000000005</v>
@@ -2278,22 +2266,22 @@
         <v>62</v>
       </c>
       <c r="I26" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J26" t="s">
         <v>81</v>
       </c>
       <c r="K26" t="s">
+        <v>229</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="N26" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="L26" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="M26" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="N26" s="4" t="s">
-        <v>241</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>109</v>
@@ -2301,13 +2289,13 @@
     </row>
     <row r="27" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B27" t="s">
         <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>163</v>
+        <v>246</v>
       </c>
       <c r="D27">
         <v>69.56</v>
@@ -2325,22 +2313,22 @@
         <v>62</v>
       </c>
       <c r="I27" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J27" t="s">
         <v>81</v>
       </c>
       <c r="K27" t="s">
+        <v>229</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="N27" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="L27" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="M27" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="N27" s="4" t="s">
-        <v>241</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>110</v>
@@ -2348,13 +2336,13 @@
     </row>
     <row r="28" spans="1:15" ht="66.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B28" t="s">
         <v>34</v>
       </c>
       <c r="C28" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D28">
         <v>63.47</v>
@@ -2372,13 +2360,13 @@
         <v>62</v>
       </c>
       <c r="I28" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J28" t="s">
         <v>83</v>
       </c>
       <c r="K28" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L28" s="4" t="s">
         <v>140</v>
@@ -2391,13 +2379,13 @@
     </row>
     <row r="29" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B29" t="s">
         <v>35</v>
       </c>
       <c r="C29" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D29">
         <v>62.77</v>
@@ -2415,13 +2403,13 @@
         <v>62</v>
       </c>
       <c r="I29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J29" t="s">
         <v>83</v>
       </c>
       <c r="K29" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L29" s="4" t="s">
         <v>140</v>
@@ -2434,13 +2422,13 @@
     </row>
     <row r="30" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B30" t="s">
         <v>36</v>
       </c>
       <c r="C30" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D30">
         <v>60.83</v>
@@ -2458,13 +2446,13 @@
         <v>62</v>
       </c>
       <c r="I30" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J30" t="s">
         <v>83</v>
       </c>
       <c r="K30" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L30" s="4" t="s">
         <v>140</v>
@@ -2477,13 +2465,13 @@
     </row>
     <row r="31" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
       </c>
       <c r="C31" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D31">
         <v>68.03</v>
@@ -2501,13 +2489,13 @@
         <v>62</v>
       </c>
       <c r="I31" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J31" t="s">
         <v>83</v>
       </c>
       <c r="K31" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L31" s="4" t="s">
         <v>140</v>
@@ -2520,13 +2508,13 @@
     </row>
     <row r="32" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B32" t="s">
         <v>38</v>
       </c>
       <c r="C32" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D32">
         <v>61.15</v>
@@ -2544,13 +2532,13 @@
         <v>62</v>
       </c>
       <c r="I32" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J32" t="s">
         <v>83</v>
       </c>
       <c r="K32" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L32" s="4" t="s">
         <v>140</v>
@@ -2563,13 +2551,13 @@
     </row>
     <row r="33" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B33" t="s">
         <v>39</v>
       </c>
       <c r="C33" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D33">
         <v>58.6</v>
@@ -2587,13 +2575,13 @@
         <v>62</v>
       </c>
       <c r="I33" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J33" t="s">
         <v>83</v>
       </c>
       <c r="K33" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L33" s="4" t="s">
         <v>140</v>
@@ -2606,13 +2594,13 @@
     </row>
     <row r="34" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B34" t="s">
         <v>40</v>
       </c>
       <c r="C34" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D34">
         <v>55.12</v>
@@ -2630,13 +2618,13 @@
         <v>62</v>
       </c>
       <c r="I34" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J34" t="s">
         <v>83</v>
       </c>
       <c r="K34" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L34" s="4" t="s">
         <v>140</v>
@@ -2649,13 +2637,13 @@
     </row>
     <row r="35" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B35" t="s">
         <v>41</v>
       </c>
       <c r="C35" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D35">
         <v>56.32</v>
@@ -2673,13 +2661,13 @@
         <v>62</v>
       </c>
       <c r="I35" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J35" t="s">
         <v>83</v>
       </c>
       <c r="K35" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L35" s="4" t="s">
         <v>140</v>
@@ -2692,13 +2680,13 @@
     </row>
     <row r="36" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B36" t="s">
         <v>42</v>
       </c>
       <c r="C36" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D36">
         <v>50.53</v>
@@ -2716,13 +2704,13 @@
         <v>62</v>
       </c>
       <c r="I36" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J36" t="s">
         <v>83</v>
       </c>
       <c r="K36" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L36" s="4" t="s">
         <v>140</v>
@@ -2735,13 +2723,13 @@
     </row>
     <row r="37" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B37" t="s">
         <v>43</v>
       </c>
       <c r="C37" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D37">
         <v>49.83</v>
@@ -2759,13 +2747,13 @@
         <v>62</v>
       </c>
       <c r="I37" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J37" t="s">
         <v>83</v>
       </c>
       <c r="K37" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L37" s="4" t="s">
         <v>140</v>
@@ -2778,13 +2766,13 @@
     </row>
     <row r="38" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B38" t="s">
         <v>44</v>
       </c>
       <c r="C38" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D38">
         <v>44.43</v>
@@ -2802,13 +2790,13 @@
         <v>62</v>
       </c>
       <c r="I38" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J38" t="s">
         <v>83</v>
       </c>
       <c r="K38" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L38" s="4" t="s">
         <v>140</v>
@@ -2821,13 +2809,13 @@
     </row>
     <row r="39" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B39" t="s">
         <v>45</v>
       </c>
       <c r="C39" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D39">
         <v>44.4</v>
@@ -2845,13 +2833,13 @@
         <v>62</v>
       </c>
       <c r="I39" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J39" t="s">
         <v>83</v>
       </c>
       <c r="K39" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L39" s="4" t="s">
         <v>140</v>
@@ -2864,13 +2852,13 @@
     </row>
     <row r="40" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B40" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C40" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="D40">
         <v>69.150000000000006</v>
@@ -2894,7 +2882,7 @@
         <v>83</v>
       </c>
       <c r="K40" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L40" s="4" t="s">
         <v>140</v>
@@ -2907,13 +2895,13 @@
     </row>
     <row r="41" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
       </c>
       <c r="C41" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D41">
         <v>69.83</v>
@@ -2937,7 +2925,7 @@
         <v>83</v>
       </c>
       <c r="K41" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L41" s="4" t="s">
         <v>140</v>
@@ -2950,10 +2938,10 @@
     </row>
     <row r="42" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B42" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C42" t="s">
         <v>162</v>
@@ -2980,7 +2968,7 @@
         <v>83</v>
       </c>
       <c r="K42" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L42" s="4" t="s">
         <v>140</v>
@@ -2993,13 +2981,13 @@
     </row>
     <row r="43" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B43" t="s">
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D43">
         <v>55.77</v>
@@ -3023,7 +3011,7 @@
         <v>83</v>
       </c>
       <c r="K43" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L43" s="4" t="s">
         <v>140</v>
@@ -3036,13 +3024,13 @@
     </row>
     <row r="44" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B44" t="s">
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D44">
         <v>59.33</v>
@@ -3066,7 +3054,7 @@
         <v>83</v>
       </c>
       <c r="K44" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L44" s="4" t="s">
         <v>140</v>
@@ -3079,13 +3067,13 @@
     </row>
     <row r="45" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C45" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D45">
         <v>57.18</v>
@@ -3109,7 +3097,7 @@
         <v>83</v>
       </c>
       <c r="K45" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L45" s="4" t="s">
         <v>140</v>
@@ -3122,13 +3110,13 @@
     </row>
     <row r="46" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B46" t="s">
         <v>49</v>
       </c>
       <c r="C46" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D46">
         <v>56.25</v>
@@ -3152,7 +3140,7 @@
         <v>83</v>
       </c>
       <c r="K46" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L46" s="4" t="s">
         <v>140</v>
@@ -3165,13 +3153,13 @@
     </row>
     <row r="47" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B47" t="s">
         <v>50</v>
       </c>
       <c r="C47" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D47">
         <v>54.67</v>
@@ -3195,7 +3183,7 @@
         <v>83</v>
       </c>
       <c r="K47" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L47" s="4" t="s">
         <v>140</v>
@@ -3208,13 +3196,13 @@
     </row>
     <row r="48" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B48" t="s">
         <v>51</v>
       </c>
       <c r="C48" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D48">
         <v>53.32</v>
@@ -3238,7 +3226,7 @@
         <v>83</v>
       </c>
       <c r="K48" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L48" s="4" t="s">
         <v>140</v>
@@ -3251,13 +3239,13 @@
     </row>
     <row r="49" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B49" t="s">
         <v>52</v>
       </c>
       <c r="C49" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D49">
         <v>53.58</v>
@@ -3281,7 +3269,7 @@
         <v>83</v>
       </c>
       <c r="K49" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L49" s="4" t="s">
         <v>140</v>
@@ -3294,13 +3282,13 @@
     </row>
     <row r="50" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B50" t="s">
         <v>53</v>
       </c>
       <c r="C50" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D50">
         <v>55.23</v>
@@ -3324,7 +3312,7 @@
         <v>83</v>
       </c>
       <c r="K50" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L50" s="4" t="s">
         <v>140</v>
@@ -3337,13 +3325,13 @@
     </row>
     <row r="51" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B51" t="s">
         <v>54</v>
       </c>
       <c r="C51" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D51">
         <v>50.93</v>
@@ -3367,7 +3355,7 @@
         <v>83</v>
       </c>
       <c r="K51" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L51" s="4" t="s">
         <v>140</v>
@@ -3380,13 +3368,13 @@
     </row>
     <row r="52" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B52" t="s">
         <v>55</v>
       </c>
       <c r="C52" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D52">
         <v>53.05</v>
@@ -3410,7 +3398,7 @@
         <v>83</v>
       </c>
       <c r="K52" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L52" s="4" t="s">
         <v>140</v>
@@ -3423,13 +3411,13 @@
     </row>
     <row r="53" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B53" t="s">
         <v>56</v>
       </c>
       <c r="C53" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D53">
         <v>46.68</v>
@@ -3453,7 +3441,7 @@
         <v>83</v>
       </c>
       <c r="K53" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L53" s="4" t="s">
         <v>140</v>
@@ -3466,13 +3454,13 @@
     </row>
     <row r="54" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B54" t="s">
         <v>57</v>
       </c>
       <c r="C54" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D54">
         <v>43.15</v>
@@ -3496,7 +3484,7 @@
         <v>83</v>
       </c>
       <c r="K54" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L54" s="4" t="s">
         <v>140</v>
@@ -3509,13 +3497,13 @@
     </row>
     <row r="55" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B55" t="s">
         <v>58</v>
       </c>
       <c r="C55" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D55">
         <v>43</v>
@@ -3539,7 +3527,7 @@
         <v>83</v>
       </c>
       <c r="K55" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L55" s="4" t="s">
         <v>140</v>
@@ -3552,13 +3540,13 @@
     </row>
     <row r="56" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B56" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C56" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D56">
         <v>59.92</v>
@@ -3573,16 +3561,16 @@
         <v>60</v>
       </c>
       <c r="I56" t="s">
-        <v>228</v>
+        <v>64</v>
       </c>
       <c r="J56" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="K56" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
@@ -3590,13 +3578,13 @@
     </row>
     <row r="57" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B57" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C57" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D57">
         <v>50.11</v>
@@ -3605,25 +3593,25 @@
         <v>14.45</v>
       </c>
       <c r="F57" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="G57" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="H57" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="I57" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="J57" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="K57" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khant Swe\OneDrive\桌面\全球腐蚀调研\Europe\Russia\russia-corrosion-map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3361C74C-2420-4339-8066-AB7DBF634DB4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC91B20-98CF-4A81-803B-27B4F21841EE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25135" windowHeight="10093" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="246">
   <si>
     <t>site_id</t>
   </si>
@@ -463,21 +463,6 @@
     <t>Viksjøfjell</t>
   </si>
   <si>
-    <t>coastal</t>
-  </si>
-  <si>
-    <t>island marine, rural</t>
-  </si>
-  <si>
-    <t>inland</t>
-  </si>
-  <si>
-    <t>inland, industrial</t>
-  </si>
-  <si>
-    <t>inland, rural</t>
-  </si>
-  <si>
     <t>site_type</t>
   </si>
   <si>
@@ -761,6 +746,18 @@
   </si>
   <si>
     <t>Town</t>
+  </si>
+  <si>
+    <t>Island marine, rural</t>
+  </si>
+  <si>
+    <t>Inland</t>
+  </si>
+  <si>
+    <t>Inland, industrial</t>
+  </si>
+  <si>
+    <t>Inland, rural</t>
   </si>
 </sst>
 </file>
@@ -1215,7 +1212,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -1242,13 +1239,13 @@
         <v>8</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="O1" s="3" t="s">
         <v>9</v>
@@ -1256,13 +1253,13 @@
     </row>
     <row r="2" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D2">
         <v>-77.52</v>
@@ -1277,13 +1274,13 @@
         <v>141</v>
       </c>
       <c r="I2" t="s">
-        <v>147</v>
+        <v>63</v>
       </c>
       <c r="J2" t="s">
         <v>65</v>
       </c>
       <c r="K2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>140</v>
@@ -1296,13 +1293,13 @@
     </row>
     <row r="3" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D3">
         <v>-77.63</v>
@@ -1317,13 +1314,13 @@
         <v>141</v>
       </c>
       <c r="I3" t="s">
-        <v>147</v>
+        <v>63</v>
       </c>
       <c r="J3" t="s">
         <v>66</v>
       </c>
       <c r="K3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="L3" s="4" t="s">
         <v>140</v>
@@ -1336,13 +1333,13 @@
     </row>
     <row r="4" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D4">
         <v>-66.55</v>
@@ -1360,7 +1357,7 @@
         <v>62</v>
       </c>
       <c r="I4" t="s">
-        <v>147</v>
+        <v>63</v>
       </c>
       <c r="J4" t="s">
         <v>67</v>
@@ -1379,13 +1376,13 @@
     </row>
     <row r="5" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D5">
         <v>-52.81</v>
@@ -1394,13 +1391,13 @@
         <v>158.44</v>
       </c>
       <c r="F5" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G5" t="s">
         <v>142</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>148</v>
+        <v>242</v>
       </c>
       <c r="J5" t="s">
         <v>68</v>
@@ -1419,13 +1416,13 @@
     </row>
     <row r="6" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D6">
         <v>-51.55</v>
@@ -1434,13 +1431,13 @@
         <v>80.3</v>
       </c>
       <c r="F6" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G6" t="s">
         <v>142</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>148</v>
+        <v>242</v>
       </c>
       <c r="J6" t="s">
         <v>69</v>
@@ -1459,13 +1456,13 @@
     </row>
     <row r="7" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D7">
         <v>-46.88</v>
@@ -1474,13 +1471,13 @@
         <v>37.86</v>
       </c>
       <c r="F7" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G7" t="s">
         <v>139</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>148</v>
+        <v>242</v>
       </c>
       <c r="J7" t="s">
         <v>70</v>
@@ -1499,13 +1496,13 @@
     </row>
     <row r="8" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D8">
         <v>-60.716999999999999</v>
@@ -1514,13 +1511,13 @@
         <v>-45.6</v>
       </c>
       <c r="F8" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G8" t="s">
         <v>142</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>148</v>
+        <v>242</v>
       </c>
       <c r="J8" t="s">
         <v>71</v>
@@ -1539,13 +1536,13 @@
     </row>
     <row r="9" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D9">
         <v>-67.566999999999993</v>
@@ -1560,7 +1557,7 @@
         <v>144</v>
       </c>
       <c r="I9" t="s">
-        <v>147</v>
+        <v>63</v>
       </c>
       <c r="J9" t="s">
         <v>71</v>
@@ -1579,13 +1576,13 @@
     </row>
     <row r="10" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B10" t="s">
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D10">
         <v>-67.599999999999994</v>
@@ -1600,7 +1597,7 @@
         <v>142</v>
       </c>
       <c r="I10" t="s">
-        <v>147</v>
+        <v>63</v>
       </c>
       <c r="J10" t="s">
         <v>72</v>
@@ -1619,13 +1616,13 @@
     </row>
     <row r="11" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D11">
         <v>-68.483000000000004</v>
@@ -1640,7 +1637,7 @@
         <v>139</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>149</v>
+        <v>243</v>
       </c>
       <c r="J11" t="s">
         <v>73</v>
@@ -1659,13 +1656,13 @@
     </row>
     <row r="12" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B12" t="s">
         <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D12">
         <v>-68.650000000000006</v>
@@ -1680,7 +1677,7 @@
         <v>142</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>149</v>
+        <v>243</v>
       </c>
       <c r="J12" t="s">
         <v>74</v>
@@ -1699,13 +1696,13 @@
     </row>
     <row r="13" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B13" t="s">
         <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D13">
         <v>-71.283000000000001</v>
@@ -1720,7 +1717,7 @@
         <v>142</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>149</v>
+        <v>243</v>
       </c>
       <c r="J13" t="s">
         <v>75</v>
@@ -1739,13 +1736,13 @@
     </row>
     <row r="14" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B14" t="s">
         <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D14">
         <v>-76.05</v>
@@ -1760,7 +1757,7 @@
         <v>142</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>149</v>
+        <v>243</v>
       </c>
       <c r="J14" t="s">
         <v>76</v>
@@ -1779,13 +1776,13 @@
     </row>
     <row r="15" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s">
         <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D15">
         <v>-78.45</v>
@@ -1803,7 +1800,7 @@
         <v>62</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>149</v>
+        <v>243</v>
       </c>
       <c r="J15" t="s">
         <v>77</v>
@@ -1822,13 +1819,13 @@
     </row>
     <row r="16" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B16" t="s">
         <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D16">
         <v>-90</v>
@@ -1843,7 +1840,7 @@
         <v>143</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>149</v>
+        <v>243</v>
       </c>
       <c r="J16" t="s">
         <v>78</v>
@@ -1862,13 +1859,13 @@
     </row>
     <row r="17" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B17" t="s">
         <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D17">
         <v>67.13</v>
@@ -1883,16 +1880,16 @@
         <v>60</v>
       </c>
       <c r="I17" t="s">
-        <v>150</v>
+        <v>244</v>
       </c>
       <c r="J17" t="s">
         <v>79</v>
       </c>
       <c r="K17" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
@@ -1902,13 +1899,13 @@
     </row>
     <row r="18" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D18">
         <v>68.760000000000005</v>
@@ -1923,16 +1920,16 @@
         <v>60</v>
       </c>
       <c r="I18" t="s">
-        <v>150</v>
+        <v>244</v>
       </c>
       <c r="J18" t="s">
         <v>79</v>
       </c>
       <c r="K18" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
@@ -1942,13 +1939,13 @@
     </row>
     <row r="19" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B19" t="s">
         <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D19">
         <v>67.13</v>
@@ -1963,16 +1960,16 @@
         <v>60</v>
       </c>
       <c r="I19" t="s">
-        <v>150</v>
+        <v>244</v>
       </c>
       <c r="J19" t="s">
         <v>80</v>
       </c>
       <c r="K19" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="M19" s="4"/>
       <c r="N19" s="4"/>
@@ -1982,13 +1979,13 @@
     </row>
     <row r="20" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B20" t="s">
         <v>146</v>
       </c>
       <c r="C20" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D20">
         <v>69.650000000000006</v>
@@ -2003,22 +2000,22 @@
         <v>60</v>
       </c>
       <c r="I20" t="s">
-        <v>150</v>
+        <v>244</v>
       </c>
       <c r="J20" t="s">
         <v>81</v>
       </c>
       <c r="K20" t="s">
+        <v>224</v>
+      </c>
+      <c r="L20" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="L20" s="4" t="s">
-        <v>234</v>
-      </c>
       <c r="M20" s="4" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>104</v>
@@ -2026,13 +2023,13 @@
     </row>
     <row r="21" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B21" t="s">
         <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D21">
         <v>69.650000000000006</v>
@@ -2047,22 +2044,22 @@
         <v>60</v>
       </c>
       <c r="I21" t="s">
-        <v>150</v>
+        <v>244</v>
       </c>
       <c r="J21" t="s">
         <v>82</v>
       </c>
       <c r="K21" t="s">
+        <v>224</v>
+      </c>
+      <c r="L21" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="L21" s="4" t="s">
-        <v>234</v>
-      </c>
       <c r="M21" s="4" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>105</v>
@@ -2070,13 +2067,13 @@
     </row>
     <row r="22" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B22" t="s">
         <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D22">
         <v>69.52</v>
@@ -2091,22 +2088,22 @@
         <v>60</v>
       </c>
       <c r="I22" t="s">
-        <v>150</v>
+        <v>244</v>
       </c>
       <c r="J22" t="s">
         <v>81</v>
       </c>
       <c r="K22" t="s">
+        <v>224</v>
+      </c>
+      <c r="L22" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="L22" s="4" t="s">
-        <v>234</v>
-      </c>
       <c r="M22" s="4" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>106</v>
@@ -2114,13 +2111,13 @@
     </row>
     <row r="23" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B23" t="s">
         <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D23">
         <v>69.19</v>
@@ -2135,22 +2132,22 @@
         <v>60</v>
       </c>
       <c r="I23" t="s">
-        <v>150</v>
+        <v>244</v>
       </c>
       <c r="J23" t="s">
         <v>82</v>
       </c>
       <c r="K23" t="s">
+        <v>224</v>
+      </c>
+      <c r="L23" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="L23" s="4" t="s">
-        <v>234</v>
-      </c>
       <c r="M23" s="4" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>107</v>
@@ -2158,13 +2155,13 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B24" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C24" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D24">
         <v>69.38</v>
@@ -2178,30 +2175,30 @@
       <c r="G24" t="s">
         <v>60</v>
       </c>
-      <c r="I24" t="s">
-        <v>149</v>
+      <c r="I24" s="2" t="s">
+        <v>243</v>
       </c>
       <c r="J24" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="K24" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
     </row>
     <row r="25" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
       </c>
       <c r="C25" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D25">
         <v>69.3</v>
@@ -2219,22 +2216,22 @@
         <v>62</v>
       </c>
       <c r="I25" t="s">
-        <v>150</v>
+        <v>244</v>
       </c>
       <c r="J25" t="s">
         <v>81</v>
       </c>
       <c r="K25" t="s">
+        <v>224</v>
+      </c>
+      <c r="L25" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="L25" s="4" t="s">
-        <v>234</v>
-      </c>
       <c r="M25" s="4" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>108</v>
@@ -2242,13 +2239,13 @@
     </row>
     <row r="26" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B26" t="s">
         <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D26">
         <v>69.510000000000005</v>
@@ -2266,22 +2263,22 @@
         <v>62</v>
       </c>
       <c r="I26" t="s">
-        <v>150</v>
+        <v>244</v>
       </c>
       <c r="J26" t="s">
         <v>81</v>
       </c>
       <c r="K26" t="s">
+        <v>224</v>
+      </c>
+      <c r="L26" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="L26" s="4" t="s">
-        <v>234</v>
-      </c>
       <c r="M26" s="4" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="N26" s="4" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>109</v>
@@ -2289,13 +2286,13 @@
     </row>
     <row r="27" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B27" t="s">
         <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D27">
         <v>69.56</v>
@@ -2313,22 +2310,22 @@
         <v>62</v>
       </c>
       <c r="I27" t="s">
-        <v>150</v>
+        <v>244</v>
       </c>
       <c r="J27" t="s">
         <v>81</v>
       </c>
       <c r="K27" t="s">
+        <v>224</v>
+      </c>
+      <c r="L27" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="L27" s="4" t="s">
-        <v>234</v>
-      </c>
       <c r="M27" s="4" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>110</v>
@@ -2336,13 +2333,13 @@
     </row>
     <row r="28" spans="1:15" ht="66.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B28" t="s">
         <v>34</v>
       </c>
       <c r="C28" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D28">
         <v>63.47</v>
@@ -2360,13 +2357,13 @@
         <v>62</v>
       </c>
       <c r="I28" t="s">
-        <v>151</v>
+        <v>245</v>
       </c>
       <c r="J28" t="s">
         <v>83</v>
       </c>
       <c r="K28" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L28" s="4" t="s">
         <v>140</v>
@@ -2379,13 +2376,13 @@
     </row>
     <row r="29" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B29" t="s">
         <v>35</v>
       </c>
       <c r="C29" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D29">
         <v>62.77</v>
@@ -2403,13 +2400,13 @@
         <v>62</v>
       </c>
       <c r="I29" t="s">
-        <v>151</v>
+        <v>245</v>
       </c>
       <c r="J29" t="s">
         <v>83</v>
       </c>
       <c r="K29" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L29" s="4" t="s">
         <v>140</v>
@@ -2422,13 +2419,13 @@
     </row>
     <row r="30" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B30" t="s">
         <v>36</v>
       </c>
       <c r="C30" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D30">
         <v>60.83</v>
@@ -2446,13 +2443,13 @@
         <v>62</v>
       </c>
       <c r="I30" t="s">
-        <v>151</v>
+        <v>245</v>
       </c>
       <c r="J30" t="s">
         <v>83</v>
       </c>
       <c r="K30" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L30" s="4" t="s">
         <v>140</v>
@@ -2465,13 +2462,13 @@
     </row>
     <row r="31" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
       </c>
       <c r="C31" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D31">
         <v>68.03</v>
@@ -2489,13 +2486,13 @@
         <v>62</v>
       </c>
       <c r="I31" t="s">
-        <v>151</v>
+        <v>245</v>
       </c>
       <c r="J31" t="s">
         <v>83</v>
       </c>
       <c r="K31" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L31" s="4" t="s">
         <v>140</v>
@@ -2508,13 +2505,13 @@
     </row>
     <row r="32" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B32" t="s">
         <v>38</v>
       </c>
       <c r="C32" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D32">
         <v>61.15</v>
@@ -2532,13 +2529,13 @@
         <v>62</v>
       </c>
       <c r="I32" t="s">
-        <v>151</v>
+        <v>245</v>
       </c>
       <c r="J32" t="s">
         <v>83</v>
       </c>
       <c r="K32" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L32" s="4" t="s">
         <v>140</v>
@@ -2551,13 +2548,13 @@
     </row>
     <row r="33" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B33" t="s">
         <v>39</v>
       </c>
       <c r="C33" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D33">
         <v>58.6</v>
@@ -2575,13 +2572,13 @@
         <v>62</v>
       </c>
       <c r="I33" t="s">
-        <v>151</v>
+        <v>245</v>
       </c>
       <c r="J33" t="s">
         <v>83</v>
       </c>
       <c r="K33" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L33" s="4" t="s">
         <v>140</v>
@@ -2594,13 +2591,13 @@
     </row>
     <row r="34" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B34" t="s">
         <v>40</v>
       </c>
       <c r="C34" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D34">
         <v>55.12</v>
@@ -2618,13 +2615,13 @@
         <v>62</v>
       </c>
       <c r="I34" t="s">
-        <v>151</v>
+        <v>245</v>
       </c>
       <c r="J34" t="s">
         <v>83</v>
       </c>
       <c r="K34" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L34" s="4" t="s">
         <v>140</v>
@@ -2637,13 +2634,13 @@
     </row>
     <row r="35" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B35" t="s">
         <v>41</v>
       </c>
       <c r="C35" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D35">
         <v>56.32</v>
@@ -2661,13 +2658,13 @@
         <v>62</v>
       </c>
       <c r="I35" t="s">
-        <v>151</v>
+        <v>245</v>
       </c>
       <c r="J35" t="s">
         <v>83</v>
       </c>
       <c r="K35" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L35" s="4" t="s">
         <v>140</v>
@@ -2680,13 +2677,13 @@
     </row>
     <row r="36" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B36" t="s">
         <v>42</v>
       </c>
       <c r="C36" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D36">
         <v>50.53</v>
@@ -2704,13 +2701,13 @@
         <v>62</v>
       </c>
       <c r="I36" t="s">
-        <v>151</v>
+        <v>245</v>
       </c>
       <c r="J36" t="s">
         <v>83</v>
       </c>
       <c r="K36" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L36" s="4" t="s">
         <v>140</v>
@@ -2723,13 +2720,13 @@
     </row>
     <row r="37" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B37" t="s">
         <v>43</v>
       </c>
       <c r="C37" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D37">
         <v>49.83</v>
@@ -2747,13 +2744,13 @@
         <v>62</v>
       </c>
       <c r="I37" t="s">
-        <v>151</v>
+        <v>245</v>
       </c>
       <c r="J37" t="s">
         <v>83</v>
       </c>
       <c r="K37" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L37" s="4" t="s">
         <v>140</v>
@@ -2766,13 +2763,13 @@
     </row>
     <row r="38" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B38" t="s">
         <v>44</v>
       </c>
       <c r="C38" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D38">
         <v>44.43</v>
@@ -2790,13 +2787,13 @@
         <v>62</v>
       </c>
       <c r="I38" t="s">
-        <v>151</v>
+        <v>245</v>
       </c>
       <c r="J38" t="s">
         <v>83</v>
       </c>
       <c r="K38" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L38" s="4" t="s">
         <v>140</v>
@@ -2809,13 +2806,13 @@
     </row>
     <row r="39" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B39" t="s">
         <v>45</v>
       </c>
       <c r="C39" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D39">
         <v>44.4</v>
@@ -2833,13 +2830,13 @@
         <v>62</v>
       </c>
       <c r="I39" t="s">
-        <v>151</v>
+        <v>245</v>
       </c>
       <c r="J39" t="s">
         <v>83</v>
       </c>
       <c r="K39" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L39" s="4" t="s">
         <v>140</v>
@@ -2852,13 +2849,13 @@
     </row>
     <row r="40" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B40" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C40" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D40">
         <v>69.150000000000006</v>
@@ -2882,7 +2879,7 @@
         <v>83</v>
       </c>
       <c r="K40" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L40" s="4" t="s">
         <v>140</v>
@@ -2895,13 +2892,13 @@
     </row>
     <row r="41" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
       </c>
       <c r="C41" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D41">
         <v>69.83</v>
@@ -2925,7 +2922,7 @@
         <v>83</v>
       </c>
       <c r="K41" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L41" s="4" t="s">
         <v>140</v>
@@ -2938,13 +2935,13 @@
     </row>
     <row r="42" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B42" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C42" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D42">
         <v>69.73</v>
@@ -2968,7 +2965,7 @@
         <v>83</v>
       </c>
       <c r="K42" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L42" s="4" t="s">
         <v>140</v>
@@ -2981,13 +2978,13 @@
     </row>
     <row r="43" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B43" t="s">
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D43">
         <v>55.77</v>
@@ -3011,7 +3008,7 @@
         <v>83</v>
       </c>
       <c r="K43" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L43" s="4" t="s">
         <v>140</v>
@@ -3024,13 +3021,13 @@
     </row>
     <row r="44" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B44" t="s">
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D44">
         <v>59.33</v>
@@ -3054,7 +3051,7 @@
         <v>83</v>
       </c>
       <c r="K44" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L44" s="4" t="s">
         <v>140</v>
@@ -3067,13 +3064,13 @@
     </row>
     <row r="45" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C45" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D45">
         <v>57.18</v>
@@ -3097,7 +3094,7 @@
         <v>83</v>
       </c>
       <c r="K45" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L45" s="4" t="s">
         <v>140</v>
@@ -3110,13 +3107,13 @@
     </row>
     <row r="46" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B46" t="s">
         <v>49</v>
       </c>
       <c r="C46" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D46">
         <v>56.25</v>
@@ -3140,7 +3137,7 @@
         <v>83</v>
       </c>
       <c r="K46" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L46" s="4" t="s">
         <v>140</v>
@@ -3153,13 +3150,13 @@
     </row>
     <row r="47" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B47" t="s">
         <v>50</v>
       </c>
       <c r="C47" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D47">
         <v>54.67</v>
@@ -3183,7 +3180,7 @@
         <v>83</v>
       </c>
       <c r="K47" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L47" s="4" t="s">
         <v>140</v>
@@ -3196,13 +3193,13 @@
     </row>
     <row r="48" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B48" t="s">
         <v>51</v>
       </c>
       <c r="C48" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D48">
         <v>53.32</v>
@@ -3226,7 +3223,7 @@
         <v>83</v>
       </c>
       <c r="K48" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L48" s="4" t="s">
         <v>140</v>
@@ -3239,13 +3236,13 @@
     </row>
     <row r="49" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B49" t="s">
         <v>52</v>
       </c>
       <c r="C49" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D49">
         <v>53.58</v>
@@ -3269,7 +3266,7 @@
         <v>83</v>
       </c>
       <c r="K49" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L49" s="4" t="s">
         <v>140</v>
@@ -3282,13 +3279,13 @@
     </row>
     <row r="50" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B50" t="s">
         <v>53</v>
       </c>
       <c r="C50" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D50">
         <v>55.23</v>
@@ -3312,7 +3309,7 @@
         <v>83</v>
       </c>
       <c r="K50" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L50" s="4" t="s">
         <v>140</v>
@@ -3325,13 +3322,13 @@
     </row>
     <row r="51" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B51" t="s">
         <v>54</v>
       </c>
       <c r="C51" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D51">
         <v>50.93</v>
@@ -3355,7 +3352,7 @@
         <v>83</v>
       </c>
       <c r="K51" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L51" s="4" t="s">
         <v>140</v>
@@ -3368,13 +3365,13 @@
     </row>
     <row r="52" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B52" t="s">
         <v>55</v>
       </c>
       <c r="C52" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D52">
         <v>53.05</v>
@@ -3398,7 +3395,7 @@
         <v>83</v>
       </c>
       <c r="K52" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L52" s="4" t="s">
         <v>140</v>
@@ -3411,13 +3408,13 @@
     </row>
     <row r="53" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B53" t="s">
         <v>56</v>
       </c>
       <c r="C53" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D53">
         <v>46.68</v>
@@ -3441,7 +3438,7 @@
         <v>83</v>
       </c>
       <c r="K53" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L53" s="4" t="s">
         <v>140</v>
@@ -3454,13 +3451,13 @@
     </row>
     <row r="54" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B54" t="s">
         <v>57</v>
       </c>
       <c r="C54" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D54">
         <v>43.15</v>
@@ -3484,7 +3481,7 @@
         <v>83</v>
       </c>
       <c r="K54" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L54" s="4" t="s">
         <v>140</v>
@@ -3497,13 +3494,13 @@
     </row>
     <row r="55" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B55" t="s">
         <v>58</v>
       </c>
       <c r="C55" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D55">
         <v>43</v>
@@ -3527,7 +3524,7 @@
         <v>83</v>
       </c>
       <c r="K55" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L55" s="4" t="s">
         <v>140</v>
@@ -3540,13 +3537,13 @@
     </row>
     <row r="56" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B56" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C56" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D56">
         <v>59.92</v>
@@ -3564,13 +3561,13 @@
         <v>64</v>
       </c>
       <c r="J56" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="K56" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
@@ -3578,13 +3575,13 @@
     </row>
     <row r="57" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B57" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C57" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D57">
         <v>50.11</v>
@@ -3593,25 +3590,25 @@
         <v>14.45</v>
       </c>
       <c r="F57" t="s">
+        <v>221</v>
+      </c>
+      <c r="G57" t="s">
+        <v>221</v>
+      </c>
+      <c r="H57" t="s">
+        <v>222</v>
+      </c>
+      <c r="I57" t="s">
+        <v>223</v>
+      </c>
+      <c r="J57" t="s">
+        <v>218</v>
+      </c>
+      <c r="K57" t="s">
         <v>226</v>
       </c>
-      <c r="G57" t="s">
-        <v>226</v>
-      </c>
-      <c r="H57" t="s">
-        <v>227</v>
-      </c>
-      <c r="I57" t="s">
-        <v>228</v>
-      </c>
-      <c r="J57" t="s">
-        <v>223</v>
-      </c>
-      <c r="K57" t="s">
-        <v>231</v>
-      </c>
       <c r="L57" s="6" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khant Swe\OneDrive\桌面\全球腐蚀调研\Europe\Russia\russia-corrosion-map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC91B20-98CF-4A81-803B-27B4F21841EE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE21D4EA-A647-460F-A867-F4A905FD4380}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25135" windowHeight="10093" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1385,10 +1385,10 @@
         <v>240</v>
       </c>
       <c r="D5">
-        <v>-52.81</v>
+        <v>-54.49</v>
       </c>
       <c r="E5">
-        <v>158.44</v>
+        <v>159.01</v>
       </c>
       <c r="F5" t="s">
         <v>240</v>
@@ -1425,10 +1425,10 @@
         <v>240</v>
       </c>
       <c r="D6">
-        <v>-51.55</v>
+        <v>-53.1</v>
       </c>
       <c r="E6">
-        <v>80.3</v>
+        <v>73.5</v>
       </c>
       <c r="F6" t="s">
         <v>240</v>
@@ -2772,10 +2772,10 @@
         <v>157</v>
       </c>
       <c r="D38">
-        <v>44.43</v>
+        <v>44.578180000000003</v>
       </c>
       <c r="E38">
-        <v>139.47999999999999</v>
+        <v>133.4555</v>
       </c>
       <c r="F38" t="s">
         <v>61</v>
@@ -2815,10 +2815,10 @@
         <v>157</v>
       </c>
       <c r="D39">
-        <v>44.4</v>
+        <v>44.429960000000001</v>
       </c>
       <c r="E39">
-        <v>131.15</v>
+        <v>131.50309999999999</v>
       </c>
       <c r="F39" t="s">
         <v>61</v>
@@ -3073,10 +3073,10 @@
         <v>156</v>
       </c>
       <c r="D45">
-        <v>57.18</v>
+        <v>57.102269999999997</v>
       </c>
       <c r="E45">
-        <v>165.75</v>
+        <v>156.76060000000001</v>
       </c>
       <c r="F45" t="s">
         <v>61</v>
@@ -3116,10 +3116,10 @@
         <v>157</v>
       </c>
       <c r="D46">
-        <v>56.25</v>
+        <v>56.52854</v>
       </c>
       <c r="E46">
-        <v>138.33000000000001</v>
+        <v>138.16</v>
       </c>
       <c r="F46" t="s">
         <v>61</v>
@@ -3460,10 +3460,10 @@
         <v>156</v>
       </c>
       <c r="D54">
-        <v>43.15</v>
+        <v>43.13</v>
       </c>
       <c r="E54">
-        <v>131.88</v>
+        <v>131.90469999999999</v>
       </c>
       <c r="F54" t="s">
         <v>61</v>
@@ -3503,10 +3503,10 @@
         <v>149</v>
       </c>
       <c r="D55">
-        <v>43</v>
+        <v>43.008099999999999</v>
       </c>
       <c r="E55">
-        <v>131</v>
+        <v>133.8013</v>
       </c>
       <c r="F55" t="s">
         <v>61</v>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khant Swe\OneDrive\桌面\全球腐蚀调研\Europe\Russia\russia-corrosion-map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE21D4EA-A647-460F-A867-F4A905FD4380}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14275E38-8E6A-49BD-81A6-A278FB11DD26}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25135" windowHeight="10093" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="271">
   <si>
     <t>site_id</t>
   </si>
@@ -758,6 +758,81 @@
   </si>
   <si>
     <t>Inland, rural</t>
+  </si>
+  <si>
+    <t>Gelendzhik</t>
+  </si>
+  <si>
+    <t>three 1-year exposures</t>
+  </si>
+  <si>
+    <t>s002.pdf</t>
+  </si>
+  <si>
+    <t>Sochi (CSNBR high-altitude station)</t>
+  </si>
+  <si>
+    <t>1-year exposure reported</t>
+  </si>
+  <si>
+    <t>Dalniye Zelentsy</t>
+  </si>
+  <si>
+    <t>Moscow</t>
+  </si>
+  <si>
+    <t>Zvenigorod</t>
+  </si>
+  <si>
+    <t>Yakutsk</t>
+  </si>
+  <si>
+    <t>RU-032</t>
+  </si>
+  <si>
+    <t>RU-033</t>
+  </si>
+  <si>
+    <t>RU-034</t>
+  </si>
+  <si>
+    <t>RU-035</t>
+  </si>
+  <si>
+    <t>RU-036</t>
+  </si>
+  <si>
+    <t>Inland, urban</t>
+  </si>
+  <si>
+    <t>Carbon steel, zinc; copper; aluminum</t>
+  </si>
+  <si>
+    <t>papers/s002.pdf</t>
+  </si>
+  <si>
+    <t>1982-1985; 3-year tests</t>
+  </si>
+  <si>
+    <t>s007.pdf</t>
+  </si>
+  <si>
+    <t>Batumi</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>Strekalov et al. (1990) primary field-test source for electric-motor constructional materials; row is distinct from other papers even where the station/city repeats. Black Sea station; open atmosphere.</t>
+  </si>
+  <si>
+    <t>papers/s007.pdf</t>
+  </si>
+  <si>
+    <t>GE001</t>
+  </si>
+  <si>
+    <t>Carbon steel, E14-12 electrical steel; SCh15 gray iron; aluminum alloy</t>
   </si>
 </sst>
 </file>
@@ -1189,11 +1264,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O57"/>
+  <dimension ref="A1:O64"/>
   <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.77734375" customWidth="1"/>
-    <col min="2" max="3" width="22.44140625" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" customWidth="1"/>
     <col min="6" max="6" width="25.44140625" customWidth="1"/>
     <col min="7" max="7" width="22.33203125" customWidth="1"/>
     <col min="8" max="8" width="12.88671875" customWidth="1"/>
@@ -2884,7 +2960,9 @@
       <c r="L40" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M40" s="4"/>
+      <c r="M40" s="4" t="s">
+        <v>268</v>
+      </c>
       <c r="N40" s="4"/>
       <c r="O40" s="2" t="s">
         <v>123</v>
@@ -3486,8 +3564,12 @@
       <c r="L54" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M54" s="4"/>
-      <c r="N54" s="4"/>
+      <c r="M54" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="N54" s="4" t="s">
+        <v>268</v>
+      </c>
       <c r="O54" s="2" t="s">
         <v>137</v>
       </c>
@@ -3613,6 +3695,284 @@
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
       <c r="O57"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>216</v>
+      </c>
+      <c r="B58" t="s">
+        <v>246</v>
+      </c>
+      <c r="C58" t="s">
+        <v>156</v>
+      </c>
+      <c r="D58">
+        <v>45.67</v>
+      </c>
+      <c r="E58">
+        <v>38.550600000000003</v>
+      </c>
+      <c r="F58" t="s">
+        <v>61</v>
+      </c>
+      <c r="G58" t="s">
+        <v>61</v>
+      </c>
+      <c r="H58" t="s">
+        <v>62</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J58" t="s">
+        <v>247</v>
+      </c>
+      <c r="K58" t="s">
+        <v>261</v>
+      </c>
+      <c r="L58" t="s">
+        <v>248</v>
+      </c>
+      <c r="O58"/>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>255</v>
+      </c>
+      <c r="B59" t="s">
+        <v>249</v>
+      </c>
+      <c r="C59" t="s">
+        <v>148</v>
+      </c>
+      <c r="D59">
+        <v>43.585299999999997</v>
+      </c>
+      <c r="E59">
+        <v>39.723300000000002</v>
+      </c>
+      <c r="F59" t="s">
+        <v>61</v>
+      </c>
+      <c r="G59" t="s">
+        <v>61</v>
+      </c>
+      <c r="H59" t="s">
+        <v>62</v>
+      </c>
+      <c r="I59" t="s">
+        <v>243</v>
+      </c>
+      <c r="J59" t="s">
+        <v>250</v>
+      </c>
+      <c r="K59" t="s">
+        <v>261</v>
+      </c>
+      <c r="L59" t="s">
+        <v>248</v>
+      </c>
+      <c r="O59"/>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>256</v>
+      </c>
+      <c r="B60" t="s">
+        <v>251</v>
+      </c>
+      <c r="C60" t="s">
+        <v>157</v>
+      </c>
+      <c r="D60">
+        <v>69.222449999999995</v>
+      </c>
+      <c r="E60">
+        <v>36.297600000000003</v>
+      </c>
+      <c r="F60" t="s">
+        <v>61</v>
+      </c>
+      <c r="G60" t="s">
+        <v>61</v>
+      </c>
+      <c r="H60" t="s">
+        <v>62</v>
+      </c>
+      <c r="I60" t="s">
+        <v>63</v>
+      </c>
+      <c r="J60" t="s">
+        <v>247</v>
+      </c>
+      <c r="K60" t="s">
+        <v>261</v>
+      </c>
+      <c r="L60" t="s">
+        <v>248</v>
+      </c>
+      <c r="O60"/>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>257</v>
+      </c>
+      <c r="B61" t="s">
+        <v>252</v>
+      </c>
+      <c r="C61" t="s">
+        <v>156</v>
+      </c>
+      <c r="D61">
+        <v>55.698321999999997</v>
+      </c>
+      <c r="E61">
+        <v>37.574019999999997</v>
+      </c>
+      <c r="F61" t="s">
+        <v>61</v>
+      </c>
+      <c r="G61" t="s">
+        <v>61</v>
+      </c>
+      <c r="H61" t="s">
+        <v>62</v>
+      </c>
+      <c r="I61" t="s">
+        <v>260</v>
+      </c>
+      <c r="J61" t="s">
+        <v>250</v>
+      </c>
+      <c r="K61" t="s">
+        <v>261</v>
+      </c>
+      <c r="L61" t="s">
+        <v>248</v>
+      </c>
+      <c r="O61"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>258</v>
+      </c>
+      <c r="B62" t="s">
+        <v>253</v>
+      </c>
+      <c r="C62" t="s">
+        <v>156</v>
+      </c>
+      <c r="D62">
+        <v>55.729900000000001</v>
+      </c>
+      <c r="E62">
+        <v>36.8553</v>
+      </c>
+      <c r="F62" t="s">
+        <v>61</v>
+      </c>
+      <c r="G62" t="s">
+        <v>61</v>
+      </c>
+      <c r="H62" t="s">
+        <v>62</v>
+      </c>
+      <c r="I62" t="s">
+        <v>245</v>
+      </c>
+      <c r="J62" t="s">
+        <v>247</v>
+      </c>
+      <c r="K62" t="s">
+        <v>261</v>
+      </c>
+      <c r="L62" t="s">
+        <v>262</v>
+      </c>
+      <c r="M62" t="s">
+        <v>268</v>
+      </c>
+      <c r="O62"/>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>259</v>
+      </c>
+      <c r="B63" t="s">
+        <v>254</v>
+      </c>
+      <c r="C63" t="s">
+        <v>156</v>
+      </c>
+      <c r="D63">
+        <v>62.035499999999999</v>
+      </c>
+      <c r="E63">
+        <v>129.6755</v>
+      </c>
+      <c r="F63" t="s">
+        <v>61</v>
+      </c>
+      <c r="G63" t="s">
+        <v>61</v>
+      </c>
+      <c r="H63" t="s">
+        <v>62</v>
+      </c>
+      <c r="I63" t="s">
+        <v>243</v>
+      </c>
+      <c r="J63" t="s">
+        <v>250</v>
+      </c>
+      <c r="K63" t="s">
+        <v>261</v>
+      </c>
+      <c r="L63" t="s">
+        <v>248</v>
+      </c>
+      <c r="O63"/>
+    </row>
+    <row r="64" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>269</v>
+      </c>
+      <c r="B64" t="s">
+        <v>265</v>
+      </c>
+      <c r="C64" t="s">
+        <v>156</v>
+      </c>
+      <c r="D64">
+        <v>41.663499999999999</v>
+      </c>
+      <c r="E64">
+        <v>41.797699999999999</v>
+      </c>
+      <c r="F64" t="s">
+        <v>266</v>
+      </c>
+      <c r="G64" t="s">
+        <v>266</v>
+      </c>
+      <c r="H64" t="s">
+        <v>62</v>
+      </c>
+      <c r="I64" t="s">
+        <v>64</v>
+      </c>
+      <c r="J64" t="s">
+        <v>263</v>
+      </c>
+      <c r="K64" t="s">
+        <v>270</v>
+      </c>
+      <c r="L64" t="s">
+        <v>264</v>
+      </c>
+      <c r="O64" s="2" t="s">
+        <v>267</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khant Swe\OneDrive\桌面\全球腐蚀调研\Europe\Russia\russia-corrosion-map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14275E38-8E6A-49BD-81A6-A278FB11DD26}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{630E3FA9-86C8-4DF3-8D52-FF129E62F3A9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25135" windowHeight="10093" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="283">
   <si>
     <t>site_id</t>
   </si>
@@ -766,9 +766,6 @@
     <t>three 1-year exposures</t>
   </si>
   <si>
-    <t>s002.pdf</t>
-  </si>
-  <si>
     <t>Sochi (CSNBR high-altitude station)</t>
   </si>
   <si>
@@ -814,9 +811,6 @@
     <t>1982-1985; 3-year tests</t>
   </si>
   <si>
-    <t>s007.pdf</t>
-  </si>
-  <si>
     <t>Batumi</t>
   </si>
   <si>
@@ -833,6 +827,48 @@
   </si>
   <si>
     <t>Carbon steel, E14-12 electrical steel; SCh15 gray iron; aluminum alloy</t>
+  </si>
+  <si>
+    <t>1-3 years</t>
+  </si>
+  <si>
+    <t>Cape Schmidt</t>
+  </si>
+  <si>
+    <t>Cape Chaplin</t>
+  </si>
+  <si>
+    <t>Pogranichnyy</t>
+  </si>
+  <si>
+    <t>Carbon steel, zinc, copper, aluminium, cadmium, AMts alloy</t>
+  </si>
+  <si>
+    <t>papers/s008.pdf</t>
+  </si>
+  <si>
+    <t>source_4</t>
+  </si>
+  <si>
+    <t>Not specified in source 1, 1-3years in source 2</t>
+  </si>
+  <si>
+    <t>Not specified in source 1, 1-3years in source 4</t>
+  </si>
+  <si>
+    <t>Carbon steel, copper, zinc, cadmium, aluminum, AMts alloy</t>
+  </si>
+  <si>
+    <t>RU-037</t>
+  </si>
+  <si>
+    <t>RU-038</t>
+  </si>
+  <si>
+    <t>RU-041</t>
+  </si>
+  <si>
+    <t>RU-042</t>
   </si>
 </sst>
 </file>
@@ -1264,7 +1300,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:P68"/>
   <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.77734375" customWidth="1"/>
@@ -1274,13 +1310,13 @@
     <col min="7" max="7" width="22.33203125" customWidth="1"/>
     <col min="8" max="8" width="12.88671875" customWidth="1"/>
     <col min="9" max="9" width="23.77734375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="19.88671875" customWidth="1"/>
+    <col min="10" max="10" width="29.77734375" customWidth="1"/>
     <col min="11" max="11" width="25.33203125" customWidth="1"/>
-    <col min="12" max="14" width="25.88671875" customWidth="1"/>
-    <col min="15" max="15" width="60.77734375" style="2" customWidth="1"/>
+    <col min="12" max="15" width="25.88671875" customWidth="1"/>
+    <col min="16" max="16" width="60.77734375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1323,11 +1359,14 @@
       <c r="N1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>163</v>
       </c>
@@ -1363,11 +1402,12 @@
       </c>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="4"/>
+      <c r="P2" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>166</v>
       </c>
@@ -1403,11 +1443,12 @@
       </c>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
-      <c r="O3" s="2" t="s">
+      <c r="O3" s="4"/>
+      <c r="P3" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>167</v>
       </c>
@@ -1446,11 +1487,12 @@
       </c>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
-      <c r="O4" s="2" t="s">
+      <c r="O4" s="4"/>
+      <c r="P4" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>168</v>
       </c>
@@ -1486,11 +1528,12 @@
       </c>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
-      <c r="O5" s="2" t="s">
+      <c r="O5" s="4"/>
+      <c r="P5" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>178</v>
       </c>
@@ -1526,11 +1569,12 @@
       </c>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
-      <c r="O6" s="2" t="s">
+      <c r="O6" s="4"/>
+      <c r="P6" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>181</v>
       </c>
@@ -1566,11 +1610,12 @@
       </c>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
-      <c r="O7" s="2" t="s">
+      <c r="O7" s="4"/>
+      <c r="P7" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>179</v>
       </c>
@@ -1606,11 +1651,12 @@
       </c>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
-      <c r="O8" s="2" t="s">
+      <c r="O8" s="4"/>
+      <c r="P8" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>164</v>
       </c>
@@ -1646,11 +1692,12 @@
       </c>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
-      <c r="O9" s="2" t="s">
+      <c r="O9" s="4"/>
+      <c r="P9" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>180</v>
       </c>
@@ -1686,11 +1733,12 @@
       </c>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
-      <c r="O10" s="2" t="s">
+      <c r="O10" s="4"/>
+      <c r="P10" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>182</v>
       </c>
@@ -1726,11 +1774,12 @@
       </c>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
-      <c r="O11" s="2" t="s">
+      <c r="O11" s="4"/>
+      <c r="P11" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>183</v>
       </c>
@@ -1766,11 +1815,12 @@
       </c>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
-      <c r="O12" s="2" t="s">
+      <c r="O12" s="4"/>
+      <c r="P12" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>184</v>
       </c>
@@ -1806,11 +1856,12 @@
       </c>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
-      <c r="O13" s="2" t="s">
+      <c r="O13" s="4"/>
+      <c r="P13" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>185</v>
       </c>
@@ -1846,11 +1897,12 @@
       </c>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
-      <c r="O14" s="2" t="s">
+      <c r="O14" s="4"/>
+      <c r="P14" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>169</v>
       </c>
@@ -1889,11 +1941,12 @@
       </c>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
-      <c r="O15" s="2" t="s">
+      <c r="O15" s="4"/>
+      <c r="P15" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>165</v>
       </c>
@@ -1929,11 +1982,12 @@
       </c>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
-      <c r="O16" s="2" t="s">
+      <c r="O16" s="4"/>
+      <c r="P16" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>170</v>
       </c>
@@ -1969,11 +2023,12 @@
       </c>
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
-      <c r="O17" s="2" t="s">
+      <c r="O17" s="4"/>
+      <c r="P17" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>171</v>
       </c>
@@ -2009,11 +2064,12 @@
       </c>
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
-      <c r="O18" s="2" t="s">
+      <c r="O18" s="4"/>
+      <c r="P18" s="2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>172</v>
       </c>
@@ -2049,11 +2105,12 @@
       </c>
       <c r="M19" s="4"/>
       <c r="N19" s="4"/>
-      <c r="O19" s="2" t="s">
+      <c r="O19" s="4"/>
+      <c r="P19" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>173</v>
       </c>
@@ -2093,11 +2150,12 @@
       <c r="N20" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="O20" s="2" t="s">
+      <c r="O20" s="4"/>
+      <c r="P20" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>174</v>
       </c>
@@ -2137,11 +2195,12 @@
       <c r="N21" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="O21" s="2" t="s">
+      <c r="O21" s="4"/>
+      <c r="P21" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>175</v>
       </c>
@@ -2181,11 +2240,12 @@
       <c r="N22" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="O22" s="2" t="s">
+      <c r="O22" s="4"/>
+      <c r="P22" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>176</v>
       </c>
@@ -2225,11 +2285,12 @@
       <c r="N23" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="O23" s="2" t="s">
+      <c r="O23" s="4"/>
+      <c r="P23" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>233</v>
       </c>
@@ -2265,8 +2326,9 @@
       </c>
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
-    </row>
-    <row r="25" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="O24" s="4"/>
+    </row>
+    <row r="25" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>186</v>
       </c>
@@ -2309,11 +2371,12 @@
       <c r="N25" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="O25" s="2" t="s">
+      <c r="O25" s="4"/>
+      <c r="P25" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>187</v>
       </c>
@@ -2356,11 +2419,12 @@
       <c r="N26" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="O26" s="2" t="s">
+      <c r="O26" s="4"/>
+      <c r="P26" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>188</v>
       </c>
@@ -2403,11 +2467,12 @@
       <c r="N27" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="O27" s="2" t="s">
+      <c r="O27" s="4"/>
+      <c r="P27" s="2" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="66.3" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" ht="66.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>189</v>
       </c>
@@ -2435,22 +2500,25 @@
       <c r="I28" t="s">
         <v>245</v>
       </c>
-      <c r="J28" t="s">
-        <v>83</v>
-      </c>
-      <c r="K28" t="s">
-        <v>226</v>
+      <c r="J28" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L28" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M28" s="4"/>
+      <c r="M28" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="N28" s="4"/>
-      <c r="O28" s="2" t="s">
+      <c r="O28" s="4"/>
+      <c r="P28" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>190</v>
       </c>
@@ -2478,22 +2546,25 @@
       <c r="I29" t="s">
         <v>245</v>
       </c>
-      <c r="J29" t="s">
-        <v>83</v>
-      </c>
-      <c r="K29" t="s">
-        <v>226</v>
+      <c r="J29" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L29" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M29" s="4"/>
+      <c r="M29" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="N29" s="4"/>
-      <c r="O29" s="2" t="s">
+      <c r="O29" s="4"/>
+      <c r="P29" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>191</v>
       </c>
@@ -2521,22 +2592,25 @@
       <c r="I30" t="s">
         <v>245</v>
       </c>
-      <c r="J30" t="s">
-        <v>83</v>
-      </c>
-      <c r="K30" t="s">
-        <v>226</v>
+      <c r="J30" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L30" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M30" s="4"/>
+      <c r="M30" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="N30" s="4"/>
-      <c r="O30" s="2" t="s">
+      <c r="O30" s="4"/>
+      <c r="P30" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>192</v>
       </c>
@@ -2575,11 +2649,12 @@
       </c>
       <c r="M31" s="4"/>
       <c r="N31" s="4"/>
-      <c r="O31" s="2" t="s">
+      <c r="O31" s="4"/>
+      <c r="P31" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>193</v>
       </c>
@@ -2607,22 +2682,25 @@
       <c r="I32" t="s">
         <v>245</v>
       </c>
-      <c r="J32" t="s">
-        <v>83</v>
-      </c>
-      <c r="K32" t="s">
-        <v>226</v>
+      <c r="J32" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L32" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M32" s="4"/>
+      <c r="M32" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="N32" s="4"/>
-      <c r="O32" s="2" t="s">
+      <c r="O32" s="4"/>
+      <c r="P32" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>194</v>
       </c>
@@ -2650,22 +2728,25 @@
       <c r="I33" t="s">
         <v>245</v>
       </c>
-      <c r="J33" t="s">
-        <v>83</v>
-      </c>
-      <c r="K33" t="s">
-        <v>226</v>
+      <c r="J33" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L33" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M33" s="4"/>
+      <c r="M33" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="N33" s="4"/>
-      <c r="O33" s="2" t="s">
+      <c r="O33" s="4"/>
+      <c r="P33" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>195</v>
       </c>
@@ -2693,22 +2774,25 @@
       <c r="I34" t="s">
         <v>245</v>
       </c>
-      <c r="J34" t="s">
-        <v>83</v>
-      </c>
-      <c r="K34" t="s">
-        <v>226</v>
+      <c r="J34" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L34" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M34" s="4"/>
+      <c r="M34" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="N34" s="4"/>
-      <c r="O34" s="2" t="s">
+      <c r="O34" s="4"/>
+      <c r="P34" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>196</v>
       </c>
@@ -2736,22 +2820,25 @@
       <c r="I35" t="s">
         <v>245</v>
       </c>
-      <c r="J35" t="s">
-        <v>83</v>
-      </c>
-      <c r="K35" t="s">
-        <v>226</v>
+      <c r="J35" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L35" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M35" s="4"/>
+      <c r="M35" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="N35" s="4"/>
-      <c r="O35" s="2" t="s">
+      <c r="O35" s="4"/>
+      <c r="P35" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>197</v>
       </c>
@@ -2779,22 +2866,25 @@
       <c r="I36" t="s">
         <v>245</v>
       </c>
-      <c r="J36" t="s">
-        <v>83</v>
-      </c>
-      <c r="K36" t="s">
-        <v>226</v>
+      <c r="J36" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L36" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M36" s="4"/>
+      <c r="M36" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="N36" s="4"/>
-      <c r="O36" s="2" t="s">
+      <c r="O36" s="4"/>
+      <c r="P36" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>198</v>
       </c>
@@ -2822,22 +2912,25 @@
       <c r="I37" t="s">
         <v>245</v>
       </c>
-      <c r="J37" t="s">
-        <v>83</v>
-      </c>
-      <c r="K37" t="s">
-        <v>226</v>
+      <c r="J37" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L37" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M37" s="4"/>
+      <c r="M37" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="N37" s="4"/>
-      <c r="O37" s="2" t="s">
+      <c r="O37" s="4"/>
+      <c r="P37" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>199</v>
       </c>
@@ -2865,22 +2958,25 @@
       <c r="I38" t="s">
         <v>245</v>
       </c>
-      <c r="J38" t="s">
-        <v>83</v>
-      </c>
-      <c r="K38" t="s">
-        <v>226</v>
+      <c r="J38" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L38" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M38" s="4"/>
+      <c r="M38" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="N38" s="4"/>
-      <c r="O38" s="2" t="s">
+      <c r="O38" s="4"/>
+      <c r="P38" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>200</v>
       </c>
@@ -2908,22 +3004,25 @@
       <c r="I39" t="s">
         <v>245</v>
       </c>
-      <c r="J39" t="s">
-        <v>83</v>
-      </c>
-      <c r="K39" t="s">
-        <v>226</v>
+      <c r="J39" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L39" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M39" s="4"/>
+      <c r="M39" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="N39" s="4"/>
-      <c r="O39" s="2" t="s">
+      <c r="O39" s="4"/>
+      <c r="P39" s="2" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>201</v>
       </c>
@@ -2961,14 +3060,15 @@
         <v>140</v>
       </c>
       <c r="M40" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="N40" s="4"/>
-      <c r="O40" s="2" t="s">
+      <c r="O40" s="4"/>
+      <c r="P40" s="2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>202</v>
       </c>
@@ -2996,22 +3096,25 @@
       <c r="I41" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="J41" t="s">
-        <v>83</v>
-      </c>
-      <c r="K41" t="s">
-        <v>226</v>
+      <c r="J41" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L41" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M41" s="4"/>
+      <c r="M41" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="N41" s="4"/>
-      <c r="O41" s="2" t="s">
+      <c r="O41" s="4"/>
+      <c r="P41" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>203</v>
       </c>
@@ -3039,22 +3142,25 @@
       <c r="I42" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="J42" t="s">
-        <v>83</v>
-      </c>
-      <c r="K42" t="s">
-        <v>226</v>
+      <c r="J42" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L42" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M42" s="4"/>
+      <c r="M42" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="N42" s="4"/>
-      <c r="O42" s="2" t="s">
+      <c r="O42" s="4"/>
+      <c r="P42" s="2" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>204</v>
       </c>
@@ -3082,22 +3188,25 @@
       <c r="I43" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="J43" t="s">
-        <v>83</v>
-      </c>
-      <c r="K43" t="s">
-        <v>226</v>
+      <c r="J43" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L43" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M43" s="4"/>
+      <c r="M43" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="N43" s="4"/>
-      <c r="O43" s="2" t="s">
+      <c r="O43" s="4"/>
+      <c r="P43" s="2" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>205</v>
       </c>
@@ -3125,22 +3234,25 @@
       <c r="I44" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="J44" t="s">
-        <v>83</v>
-      </c>
-      <c r="K44" t="s">
-        <v>226</v>
+      <c r="J44" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L44" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M44" s="4"/>
+      <c r="M44" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="N44" s="4"/>
-      <c r="O44" s="2" t="s">
+      <c r="O44" s="4"/>
+      <c r="P44" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>206</v>
       </c>
@@ -3168,22 +3280,25 @@
       <c r="I45" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="J45" t="s">
-        <v>83</v>
-      </c>
-      <c r="K45" t="s">
-        <v>226</v>
+      <c r="J45" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L45" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M45" s="4"/>
+      <c r="M45" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="N45" s="4"/>
-      <c r="O45" s="2" t="s">
+      <c r="O45" s="4"/>
+      <c r="P45" s="2" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>207</v>
       </c>
@@ -3211,22 +3326,25 @@
       <c r="I46" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="J46" t="s">
-        <v>83</v>
-      </c>
-      <c r="K46" t="s">
-        <v>226</v>
+      <c r="J46" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L46" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M46" s="4"/>
+      <c r="M46" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="N46" s="4"/>
-      <c r="O46" s="2" t="s">
+      <c r="O46" s="4"/>
+      <c r="P46" s="2" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>208</v>
       </c>
@@ -3254,22 +3372,25 @@
       <c r="I47" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="J47" t="s">
-        <v>83</v>
-      </c>
-      <c r="K47" t="s">
-        <v>226</v>
+      <c r="J47" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L47" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M47" s="4"/>
+      <c r="M47" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="N47" s="4"/>
-      <c r="O47" s="2" t="s">
+      <c r="O47" s="4"/>
+      <c r="P47" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>209</v>
       </c>
@@ -3297,22 +3418,25 @@
       <c r="I48" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="J48" t="s">
-        <v>83</v>
-      </c>
-      <c r="K48" t="s">
-        <v>226</v>
+      <c r="J48" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L48" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M48" s="4"/>
+      <c r="M48" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="N48" s="4"/>
-      <c r="O48" s="2" t="s">
+      <c r="O48" s="4"/>
+      <c r="P48" s="2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>210</v>
       </c>
@@ -3340,22 +3464,25 @@
       <c r="I49" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="J49" t="s">
-        <v>83</v>
-      </c>
-      <c r="K49" t="s">
-        <v>226</v>
+      <c r="J49" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L49" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M49" s="4"/>
+      <c r="M49" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="N49" s="4"/>
-      <c r="O49" s="2" t="s">
+      <c r="O49" s="4"/>
+      <c r="P49" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>211</v>
       </c>
@@ -3383,22 +3510,25 @@
       <c r="I50" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="J50" t="s">
-        <v>83</v>
-      </c>
-      <c r="K50" t="s">
-        <v>226</v>
+      <c r="J50" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L50" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M50" s="4"/>
+      <c r="M50" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="N50" s="4"/>
-      <c r="O50" s="2" t="s">
+      <c r="O50" s="4"/>
+      <c r="P50" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>212</v>
       </c>
@@ -3426,22 +3556,25 @@
       <c r="I51" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="J51" t="s">
-        <v>83</v>
-      </c>
-      <c r="K51" t="s">
-        <v>226</v>
+      <c r="J51" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L51" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M51" s="4"/>
+      <c r="M51" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="N51" s="4"/>
-      <c r="O51" s="2" t="s">
+      <c r="O51" s="4"/>
+      <c r="P51" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>213</v>
       </c>
@@ -3469,22 +3602,25 @@
       <c r="I52" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="J52" t="s">
-        <v>83</v>
-      </c>
-      <c r="K52" t="s">
-        <v>226</v>
+      <c r="J52" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L52" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M52" s="4"/>
+      <c r="M52" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="N52" s="4"/>
-      <c r="O52" s="2" t="s">
+      <c r="O52" s="4"/>
+      <c r="P52" s="2" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>214</v>
       </c>
@@ -3512,22 +3648,25 @@
       <c r="I53" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="J53" t="s">
-        <v>83</v>
-      </c>
-      <c r="K53" t="s">
-        <v>226</v>
+      <c r="J53" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L53" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M53" s="4"/>
+      <c r="M53" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="N53" s="4"/>
-      <c r="O53" s="2" t="s">
+      <c r="O53" s="4"/>
+      <c r="P53" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>215</v>
       </c>
@@ -3555,26 +3694,29 @@
       <c r="I54" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="J54" t="s">
-        <v>83</v>
-      </c>
-      <c r="K54" t="s">
-        <v>226</v>
+      <c r="J54" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L54" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M54" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N54" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="O54" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="O54" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="P54" s="2" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>216</v>
       </c>
@@ -3602,22 +3744,25 @@
       <c r="I55" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="J55" t="s">
-        <v>83</v>
-      </c>
-      <c r="K55" t="s">
-        <v>226</v>
+      <c r="J55" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="L55" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="M55" s="4"/>
+      <c r="M55" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="N55" s="4"/>
-      <c r="O55" s="2" t="s">
+      <c r="O55" s="4"/>
+      <c r="P55" s="2" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>234</v>
       </c>
@@ -3653,9 +3798,10 @@
       </c>
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
-      <c r="O56"/>
-    </row>
-    <row r="57" spans="1:15" ht="30.15" x14ac:dyDescent="0.3">
+      <c r="O56" s="6"/>
+      <c r="P56"/>
+    </row>
+    <row r="57" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>235</v>
       </c>
@@ -3694,9 +3840,10 @@
       </c>
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
-      <c r="O57"/>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O57" s="6"/>
+      <c r="P57"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>216</v>
       </c>
@@ -3728,19 +3875,19 @@
         <v>247</v>
       </c>
       <c r="K58" t="s">
+        <v>260</v>
+      </c>
+      <c r="L58" t="s">
         <v>261</v>
       </c>
-      <c r="L58" t="s">
+      <c r="P58"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>254</v>
+      </c>
+      <c r="B59" t="s">
         <v>248</v>
-      </c>
-      <c r="O58"/>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>255</v>
-      </c>
-      <c r="B59" t="s">
-        <v>249</v>
       </c>
       <c r="C59" t="s">
         <v>148</v>
@@ -3764,22 +3911,22 @@
         <v>243</v>
       </c>
       <c r="J59" t="s">
+        <v>249</v>
+      </c>
+      <c r="K59" t="s">
+        <v>260</v>
+      </c>
+      <c r="L59" t="s">
+        <v>261</v>
+      </c>
+      <c r="P59"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>255</v>
+      </c>
+      <c r="B60" t="s">
         <v>250</v>
-      </c>
-      <c r="K59" t="s">
-        <v>261</v>
-      </c>
-      <c r="L59" t="s">
-        <v>248</v>
-      </c>
-      <c r="O59"/>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>256</v>
-      </c>
-      <c r="B60" t="s">
-        <v>251</v>
       </c>
       <c r="C60" t="s">
         <v>157</v>
@@ -3806,19 +3953,19 @@
         <v>247</v>
       </c>
       <c r="K60" t="s">
+        <v>260</v>
+      </c>
+      <c r="L60" t="s">
         <v>261</v>
       </c>
-      <c r="L60" t="s">
-        <v>248</v>
-      </c>
-      <c r="O60"/>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P60"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B61" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C61" t="s">
         <v>156</v>
@@ -3839,25 +3986,25 @@
         <v>62</v>
       </c>
       <c r="I61" t="s">
+        <v>259</v>
+      </c>
+      <c r="J61" t="s">
+        <v>249</v>
+      </c>
+      <c r="K61" t="s">
         <v>260</v>
       </c>
-      <c r="J61" t="s">
-        <v>250</v>
-      </c>
-      <c r="K61" t="s">
+      <c r="L61" t="s">
         <v>261</v>
       </c>
-      <c r="L61" t="s">
-        <v>248</v>
-      </c>
-      <c r="O61"/>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P61"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B62" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C62" t="s">
         <v>156</v>
@@ -3884,22 +4031,22 @@
         <v>247</v>
       </c>
       <c r="K62" t="s">
+        <v>260</v>
+      </c>
+      <c r="L62" t="s">
         <v>261</v>
       </c>
-      <c r="L62" t="s">
-        <v>262</v>
-      </c>
       <c r="M62" t="s">
-        <v>268</v>
-      </c>
-      <c r="O62"/>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+      <c r="P62"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B63" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C63" t="s">
         <v>156</v>
@@ -3923,22 +4070,22 @@
         <v>243</v>
       </c>
       <c r="J63" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K63" t="s">
+        <v>260</v>
+      </c>
+      <c r="L63" t="s">
         <v>261</v>
       </c>
-      <c r="L63" t="s">
-        <v>248</v>
-      </c>
-      <c r="O63"/>
-    </row>
-    <row r="64" spans="1:15" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="P63"/>
+    </row>
+    <row r="64" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B64" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C64" t="s">
         <v>156</v>
@@ -3950,10 +4097,10 @@
         <v>41.797699999999999</v>
       </c>
       <c r="F64" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G64" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H64" t="s">
         <v>62</v>
@@ -3962,17 +4109,173 @@
         <v>64</v>
       </c>
       <c r="J64" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K64" t="s">
+        <v>268</v>
+      </c>
+      <c r="L64" t="s">
+        <v>266</v>
+      </c>
+      <c r="P64" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>279</v>
+      </c>
+      <c r="B65" t="s">
         <v>270</v>
       </c>
-      <c r="L64" t="s">
-        <v>264</v>
-      </c>
-      <c r="O64" s="2" t="s">
-        <v>267</v>
-      </c>
+      <c r="C65" t="s">
+        <v>149</v>
+      </c>
+      <c r="D65">
+        <v>69.997799999999998</v>
+      </c>
+      <c r="E65">
+        <v>-172.03854000000001</v>
+      </c>
+      <c r="F65" t="s">
+        <v>61</v>
+      </c>
+      <c r="G65" t="s">
+        <v>61</v>
+      </c>
+      <c r="H65" t="s">
+        <v>62</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J65" t="s">
+        <v>269</v>
+      </c>
+      <c r="K65" t="s">
+        <v>278</v>
+      </c>
+      <c r="L65" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="P65"/>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>280</v>
+      </c>
+      <c r="B66" t="s">
+        <v>271</v>
+      </c>
+      <c r="C66" t="s">
+        <v>149</v>
+      </c>
+      <c r="D66">
+        <v>65.086730000000003</v>
+      </c>
+      <c r="E66">
+        <v>-167.62527</v>
+      </c>
+      <c r="F66" t="s">
+        <v>61</v>
+      </c>
+      <c r="G66" t="s">
+        <v>61</v>
+      </c>
+      <c r="H66" t="s">
+        <v>62</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J66" t="s">
+        <v>269</v>
+      </c>
+      <c r="K66" t="s">
+        <v>278</v>
+      </c>
+      <c r="L66" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="P66"/>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>281</v>
+      </c>
+      <c r="B67" t="s">
+        <v>37</v>
+      </c>
+      <c r="C67" t="s">
+        <v>241</v>
+      </c>
+      <c r="D67">
+        <v>68.252960000000002</v>
+      </c>
+      <c r="E67">
+        <v>166.28658999999999</v>
+      </c>
+      <c r="F67" t="s">
+        <v>61</v>
+      </c>
+      <c r="G67" t="s">
+        <v>61</v>
+      </c>
+      <c r="H67" t="s">
+        <v>62</v>
+      </c>
+      <c r="I67" t="s">
+        <v>243</v>
+      </c>
+      <c r="J67" t="s">
+        <v>269</v>
+      </c>
+      <c r="K67" t="s">
+        <v>278</v>
+      </c>
+      <c r="L67" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="P67"/>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>282</v>
+      </c>
+      <c r="B68" t="s">
+        <v>272</v>
+      </c>
+      <c r="C68" t="s">
+        <v>241</v>
+      </c>
+      <c r="D68">
+        <v>44.407859000000002</v>
+      </c>
+      <c r="E68">
+        <v>131.38207</v>
+      </c>
+      <c r="F68" t="s">
+        <v>61</v>
+      </c>
+      <c r="G68" t="s">
+        <v>61</v>
+      </c>
+      <c r="H68" t="s">
+        <v>62</v>
+      </c>
+      <c r="I68" t="s">
+        <v>243</v>
+      </c>
+      <c r="J68" t="s">
+        <v>269</v>
+      </c>
+      <c r="K68" t="s">
+        <v>278</v>
+      </c>
+      <c r="L68" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="P68"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khant Swe\OneDrive\桌面\全球腐蚀调研\Europe\Russia\russia-corrosion-map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{630E3FA9-86C8-4DF3-8D52-FF129E62F3A9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82A6AA3-8050-4C35-8486-FA50DB7B034A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25135" windowHeight="10093" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="385">
   <si>
     <t>site_id</t>
   </si>
@@ -514,9 +514,6 @@
     <t>AQ-NZ-001</t>
   </si>
   <si>
-    <t>AQ-UK-001</t>
-  </si>
-  <si>
     <t>AQ-US-001</t>
   </si>
   <si>
@@ -823,9 +820,6 @@
     <t>papers/s007.pdf</t>
   </si>
   <si>
-    <t>GE001</t>
-  </si>
-  <si>
     <t>Carbon steel, E14-12 electrical steel; SCh15 gray iron; aluminum alloy</t>
   </si>
   <si>
@@ -869,6 +863,318 @@
   </si>
   <si>
     <t>RU-042</t>
+  </si>
+  <si>
+    <t>1987-1989 (1-2 years); 1987-1991 (4 years); 1987-1995 (8 years); repeated 1-year periods 1987-88, 1992-93, 1994-95</t>
+  </si>
+  <si>
+    <t>Carbon steel, weathering steel, zinc, aluminium</t>
+  </si>
+  <si>
+    <t>papers/s009.pdf</t>
+  </si>
+  <si>
+    <t>papers/s010.pdf</t>
+  </si>
+  <si>
+    <t>papers/s011.pdf</t>
+  </si>
+  <si>
+    <t>papers/s012.pdf</t>
+  </si>
+  <si>
+    <t>Kasperske Hory</t>
+  </si>
+  <si>
+    <t>Kopisty</t>
+  </si>
+  <si>
+    <t>Industrial Locality</t>
+  </si>
+  <si>
+    <t>Espoo</t>
+  </si>
+  <si>
+    <t>Finland</t>
+  </si>
+  <si>
+    <t>Ahtari</t>
+  </si>
+  <si>
+    <t>Helsinki</t>
+  </si>
+  <si>
+    <t>Waldhof-Langenbrugge</t>
+  </si>
+  <si>
+    <t>Monitoring site</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Aschaffenburg</t>
+  </si>
+  <si>
+    <t>Langenfeld-Reusrath</t>
+  </si>
+  <si>
+    <t>Bottrop</t>
+  </si>
+  <si>
+    <t>Garmisch-Partenkirchen</t>
+  </si>
+  <si>
+    <t>Rome</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>Casaccia</t>
+  </si>
+  <si>
+    <t>Milan</t>
+  </si>
+  <si>
+    <t>Venice</t>
+  </si>
+  <si>
+    <t>Vlaardingen</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>Eibergen</t>
+  </si>
+  <si>
+    <t>Vredepeel</t>
+  </si>
+  <si>
+    <t>Wijnandsrade</t>
+  </si>
+  <si>
+    <t>Borregaard (Sarpsborg)</t>
+  </si>
+  <si>
+    <t>Birkenes</t>
+  </si>
+  <si>
+    <t>Stockholm South</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>Stockholm Centre</t>
+  </si>
+  <si>
+    <t>Aspvreten</t>
+  </si>
+  <si>
+    <t>Lincoln Cathedral</t>
+  </si>
+  <si>
+    <t>Wells Cathedral</t>
+  </si>
+  <si>
+    <t>Clatteringshaws Loch</t>
+  </si>
+  <si>
+    <t>Stoke Orchard</t>
+  </si>
+  <si>
+    <t>Madrid</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Bilbao</t>
+  </si>
+  <si>
+    <t>Toledo</t>
+  </si>
+  <si>
+    <t>Lahemaa</t>
+  </si>
+  <si>
+    <t>Estonia</t>
+  </si>
+  <si>
+    <t>Portugal</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>Steubenville</t>
+  </si>
+  <si>
+    <t>Cathedral</t>
+  </si>
+  <si>
+    <t>National Park</t>
+  </si>
+  <si>
+    <t>Research Park</t>
+  </si>
+  <si>
+    <t>Lisbon</t>
+  </si>
+  <si>
+    <t>Dorset</t>
+  </si>
+  <si>
+    <t>Rural monitoring site</t>
+  </si>
+  <si>
+    <t>Industrial site</t>
+  </si>
+  <si>
+    <t>Port city</t>
+  </si>
+  <si>
+    <t>Research centre</t>
+  </si>
+  <si>
+    <t>Essen</t>
+  </si>
+  <si>
+    <t>Rural</t>
+  </si>
+  <si>
+    <t>Industrial</t>
+  </si>
+  <si>
+    <t>Urban, industrial</t>
+  </si>
+  <si>
+    <t>GE-001</t>
+  </si>
+  <si>
+    <t>CZ-002</t>
+  </si>
+  <si>
+    <t>CZ-003</t>
+  </si>
+  <si>
+    <t>FI-001</t>
+  </si>
+  <si>
+    <t>FI-002</t>
+  </si>
+  <si>
+    <t>FI-003</t>
+  </si>
+  <si>
+    <t>DE-001</t>
+  </si>
+  <si>
+    <t>DE-002</t>
+  </si>
+  <si>
+    <t>DE-003</t>
+  </si>
+  <si>
+    <t>DE-004</t>
+  </si>
+  <si>
+    <t>DE-005</t>
+  </si>
+  <si>
+    <t>DE-006</t>
+  </si>
+  <si>
+    <t>IT-001</t>
+  </si>
+  <si>
+    <t>IT-002</t>
+  </si>
+  <si>
+    <t>IT-003</t>
+  </si>
+  <si>
+    <t>IT-004</t>
+  </si>
+  <si>
+    <t>NL-001</t>
+  </si>
+  <si>
+    <t>NL-002</t>
+  </si>
+  <si>
+    <t>NL-003</t>
+  </si>
+  <si>
+    <t>NL-004</t>
+  </si>
+  <si>
+    <t>NO-010</t>
+  </si>
+  <si>
+    <t>NO-011</t>
+  </si>
+  <si>
+    <t>SE-001</t>
+  </si>
+  <si>
+    <t>SE-002</t>
+  </si>
+  <si>
+    <t>SE-003</t>
+  </si>
+  <si>
+    <t>GB-001</t>
+  </si>
+  <si>
+    <t>GB-002</t>
+  </si>
+  <si>
+    <t>GB-003</t>
+  </si>
+  <si>
+    <t>GB-004</t>
+  </si>
+  <si>
+    <t>AQ-GB-001</t>
+  </si>
+  <si>
+    <t>ES-001</t>
+  </si>
+  <si>
+    <t>ES-002</t>
+  </si>
+  <si>
+    <t>ES-003</t>
+  </si>
+  <si>
+    <t>EE-001</t>
+  </si>
+  <si>
+    <t>PT-001</t>
+  </si>
+  <si>
+    <t>CA-001</t>
+  </si>
+  <si>
+    <t>US-001</t>
+  </si>
+  <si>
+    <t>US-002</t>
+  </si>
+  <si>
+    <t>source_5</t>
+  </si>
+  <si>
+    <t>source_6</t>
+  </si>
+  <si>
+    <t>source_7</t>
+  </si>
+  <si>
+    <t>Research Triangle Park, North Carolina</t>
   </si>
 </sst>
 </file>
@@ -943,7 +1249,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -959,6 +1265,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1300,7 +1609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P68"/>
+  <dimension ref="A1:S104"/>
   <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.77734375" customWidth="1"/>
@@ -1310,13 +1619,13 @@
     <col min="7" max="7" width="22.33203125" customWidth="1"/>
     <col min="8" max="8" width="12.88671875" customWidth="1"/>
     <col min="9" max="9" width="23.77734375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="29.77734375" customWidth="1"/>
+    <col min="10" max="10" width="33.77734375" customWidth="1"/>
     <col min="11" max="11" width="25.33203125" customWidth="1"/>
-    <col min="12" max="15" width="25.88671875" customWidth="1"/>
-    <col min="16" max="16" width="60.77734375" style="2" customWidth="1"/>
+    <col min="12" max="18" width="25.88671875" customWidth="1"/>
+    <col min="19" max="19" width="60.77734375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1351,22 +1660,31 @@
         <v>8</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="O1" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="P1" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="S1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>163</v>
       </c>
@@ -1395,7 +1713,7 @@
         <v>65</v>
       </c>
       <c r="K2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>140</v>
@@ -1403,13 +1721,16 @@
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
@@ -1436,7 +1757,7 @@
         <v>66</v>
       </c>
       <c r="K3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L3" s="4" t="s">
         <v>140</v>
@@ -1444,13 +1765,16 @@
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
-      <c r="P3" s="2" t="s">
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -1488,19 +1812,22 @@
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
-      <c r="P4" s="2" t="s">
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D5">
         <v>-54.49</v>
@@ -1509,13 +1836,13 @@
         <v>159.01</v>
       </c>
       <c r="F5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G5" t="s">
         <v>142</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J5" t="s">
         <v>68</v>
@@ -1529,19 +1856,22 @@
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
-      <c r="P5" s="2" t="s">
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D6">
         <v>-53.1</v>
@@ -1550,13 +1880,13 @@
         <v>73.5</v>
       </c>
       <c r="F6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G6" t="s">
         <v>142</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J6" t="s">
         <v>69</v>
@@ -1570,19 +1900,22 @@
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
-      <c r="P6" s="2" t="s">
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D7">
         <v>-46.88</v>
@@ -1591,13 +1924,13 @@
         <v>37.86</v>
       </c>
       <c r="F7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G7" t="s">
         <v>139</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J7" t="s">
         <v>70</v>
@@ -1611,19 +1944,22 @@
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
-      <c r="P7" s="2" t="s">
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D8">
         <v>-60.716999999999999</v>
@@ -1632,13 +1968,13 @@
         <v>-45.6</v>
       </c>
       <c r="F8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G8" t="s">
         <v>142</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J8" t="s">
         <v>71</v>
@@ -1652,13 +1988,16 @@
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
-      <c r="P8" s="2" t="s">
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>164</v>
+        <v>372</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
@@ -1693,13 +2032,16 @@
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
-      <c r="P9" s="2" t="s">
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B10" t="s">
         <v>18</v>
@@ -1734,13 +2076,16 @@
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
-      <c r="P10" s="2" t="s">
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
@@ -1761,7 +2106,7 @@
         <v>139</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J11" t="s">
         <v>73</v>
@@ -1775,13 +2120,16 @@
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
-      <c r="P11" s="2" t="s">
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B12" t="s">
         <v>20</v>
@@ -1802,7 +2150,7 @@
         <v>142</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J12" t="s">
         <v>74</v>
@@ -1816,13 +2164,16 @@
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
-      <c r="P12" s="2" t="s">
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B13" t="s">
         <v>21</v>
@@ -1843,7 +2194,7 @@
         <v>142</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J13" t="s">
         <v>75</v>
@@ -1857,13 +2208,16 @@
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
-      <c r="P13" s="2" t="s">
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B14" t="s">
         <v>22</v>
@@ -1884,7 +2238,7 @@
         <v>142</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J14" t="s">
         <v>76</v>
@@ -1898,13 +2252,16 @@
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
-      <c r="P14" s="2" t="s">
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s">
         <v>23</v>
@@ -1928,7 +2285,7 @@
         <v>62</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J15" t="s">
         <v>77</v>
@@ -1942,13 +2299,16 @@
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
-      <c r="P15" s="2" t="s">
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B16" t="s">
         <v>24</v>
@@ -1969,7 +2329,7 @@
         <v>143</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J16" t="s">
         <v>78</v>
@@ -1983,19 +2343,22 @@
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
-      <c r="P16" s="2" t="s">
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B17" t="s">
         <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D17">
         <v>67.13</v>
@@ -2010,33 +2373,36 @@
         <v>60</v>
       </c>
       <c r="I17" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J17" t="s">
         <v>79</v>
       </c>
       <c r="K17" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
-      <c r="P17" s="2" t="s">
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D18">
         <v>68.760000000000005</v>
@@ -2051,33 +2417,36 @@
         <v>60</v>
       </c>
       <c r="I18" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J18" t="s">
         <v>79</v>
       </c>
       <c r="K18" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
-      <c r="P18" s="2" t="s">
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B19" t="s">
         <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D19">
         <v>67.13</v>
@@ -2092,27 +2461,30 @@
         <v>60</v>
       </c>
       <c r="I19" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J19" t="s">
         <v>80</v>
       </c>
       <c r="K19" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M19" s="4"/>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
-      <c r="P19" s="2" t="s">
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B20" t="s">
         <v>146</v>
@@ -2133,31 +2505,34 @@
         <v>60</v>
       </c>
       <c r="I20" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J20" t="s">
         <v>81</v>
       </c>
       <c r="K20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L20" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="N20" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="M20" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="N20" s="4" t="s">
-        <v>230</v>
-      </c>
       <c r="O20" s="4"/>
-      <c r="P20" s="2" t="s">
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B21" t="s">
         <v>28</v>
@@ -2178,31 +2553,34 @@
         <v>60</v>
       </c>
       <c r="I21" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J21" t="s">
         <v>82</v>
       </c>
       <c r="K21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L21" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="N21" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="M21" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="N21" s="4" t="s">
-        <v>230</v>
-      </c>
       <c r="O21" s="4"/>
-      <c r="P21" s="2" t="s">
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B22" t="s">
         <v>29</v>
@@ -2223,31 +2601,34 @@
         <v>60</v>
       </c>
       <c r="I22" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J22" t="s">
         <v>81</v>
       </c>
       <c r="K22" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L22" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="N22" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="M22" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="N22" s="4" t="s">
-        <v>230</v>
-      </c>
       <c r="O22" s="4"/>
-      <c r="P22" s="2" t="s">
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4"/>
+      <c r="R22" s="4"/>
+      <c r="S22" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B23" t="s">
         <v>30</v>
@@ -2268,37 +2649,40 @@
         <v>60</v>
       </c>
       <c r="I23" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J23" t="s">
         <v>82</v>
       </c>
       <c r="K23" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L23" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="N23" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="M23" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="N23" s="4" t="s">
+      <c r="O23" s="4"/>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>232</v>
+      </c>
+      <c r="B24" t="s">
         <v>230</v>
       </c>
-      <c r="O23" s="4"/>
-      <c r="P23" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>233</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>231</v>
-      </c>
-      <c r="C24" t="s">
-        <v>232</v>
       </c>
       <c r="D24">
         <v>69.38</v>
@@ -2313,24 +2697,27 @@
         <v>60</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J24" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K24" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
       <c r="O24" s="4"/>
-    </row>
-    <row r="25" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
+    </row>
+    <row r="25" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
@@ -2354,31 +2741,34 @@
         <v>62</v>
       </c>
       <c r="I25" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J25" t="s">
         <v>81</v>
       </c>
       <c r="K25" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L25" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="N25" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="M25" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="N25" s="4" t="s">
-        <v>230</v>
-      </c>
       <c r="O25" s="4"/>
-      <c r="P25" s="2" t="s">
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="4"/>
+      <c r="S25" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B26" t="s">
         <v>32</v>
@@ -2402,37 +2792,40 @@
         <v>62</v>
       </c>
       <c r="I26" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J26" t="s">
         <v>81</v>
       </c>
       <c r="K26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L26" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="N26" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="M26" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="N26" s="4" t="s">
-        <v>230</v>
-      </c>
       <c r="O26" s="4"/>
-      <c r="P26" s="2" t="s">
+      <c r="P26" s="4"/>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
+      <c r="S26" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B27" t="s">
         <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D27">
         <v>69.56</v>
@@ -2450,31 +2843,34 @@
         <v>62</v>
       </c>
       <c r="I27" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J27" t="s">
         <v>81</v>
       </c>
       <c r="K27" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L27" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="N27" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="M27" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="N27" s="4" t="s">
-        <v>230</v>
-      </c>
       <c r="O27" s="4"/>
-      <c r="P27" s="2" t="s">
+      <c r="P27" s="4"/>
+      <c r="Q27" s="4"/>
+      <c r="R27" s="4"/>
+      <c r="S27" s="2" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="66.3" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" ht="66.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B28" t="s">
         <v>34</v>
@@ -2498,29 +2894,32 @@
         <v>62</v>
       </c>
       <c r="I28" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L28" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N28" s="4"/>
       <c r="O28" s="4"/>
-      <c r="P28" s="2" t="s">
+      <c r="P28" s="4"/>
+      <c r="Q28" s="4"/>
+      <c r="R28" s="4"/>
+      <c r="S28" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B29" t="s">
         <v>35</v>
@@ -2544,29 +2943,32 @@
         <v>62</v>
       </c>
       <c r="I29" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L29" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N29" s="4"/>
       <c r="O29" s="4"/>
-      <c r="P29" s="2" t="s">
+      <c r="P29" s="4"/>
+      <c r="Q29" s="4"/>
+      <c r="R29" s="4"/>
+      <c r="S29" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B30" t="s">
         <v>36</v>
@@ -2590,29 +2992,32 @@
         <v>62</v>
       </c>
       <c r="I30" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L30" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N30" s="4"/>
       <c r="O30" s="4"/>
-      <c r="P30" s="2" t="s">
+      <c r="P30" s="4"/>
+      <c r="Q30" s="4"/>
+      <c r="R30" s="4"/>
+      <c r="S30" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
@@ -2636,13 +3041,13 @@
         <v>62</v>
       </c>
       <c r="I31" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J31" t="s">
         <v>83</v>
       </c>
       <c r="K31" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L31" s="4" t="s">
         <v>140</v>
@@ -2650,13 +3055,16 @@
       <c r="M31" s="4"/>
       <c r="N31" s="4"/>
       <c r="O31" s="4"/>
-      <c r="P31" s="2" t="s">
+      <c r="P31" s="4"/>
+      <c r="Q31" s="4"/>
+      <c r="R31" s="4"/>
+      <c r="S31" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B32" t="s">
         <v>38</v>
@@ -2680,29 +3088,32 @@
         <v>62</v>
       </c>
       <c r="I32" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L32" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N32" s="4"/>
       <c r="O32" s="4"/>
-      <c r="P32" s="2" t="s">
+      <c r="P32" s="4"/>
+      <c r="Q32" s="4"/>
+      <c r="R32" s="4"/>
+      <c r="S32" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B33" t="s">
         <v>39</v>
@@ -2726,29 +3137,32 @@
         <v>62</v>
       </c>
       <c r="I33" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L33" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N33" s="4"/>
       <c r="O33" s="4"/>
-      <c r="P33" s="2" t="s">
+      <c r="P33" s="4"/>
+      <c r="Q33" s="4"/>
+      <c r="R33" s="4"/>
+      <c r="S33" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B34" t="s">
         <v>40</v>
@@ -2772,29 +3186,32 @@
         <v>62</v>
       </c>
       <c r="I34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L34" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M34" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N34" s="4"/>
       <c r="O34" s="4"/>
-      <c r="P34" s="2" t="s">
+      <c r="P34" s="4"/>
+      <c r="Q34" s="4"/>
+      <c r="R34" s="4"/>
+      <c r="S34" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B35" t="s">
         <v>41</v>
@@ -2818,29 +3235,32 @@
         <v>62</v>
       </c>
       <c r="I35" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L35" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M35" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N35" s="4"/>
       <c r="O35" s="4"/>
-      <c r="P35" s="2" t="s">
+      <c r="P35" s="4"/>
+      <c r="Q35" s="4"/>
+      <c r="R35" s="4"/>
+      <c r="S35" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B36" t="s">
         <v>42</v>
@@ -2864,29 +3284,32 @@
         <v>62</v>
       </c>
       <c r="I36" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L36" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
-      <c r="P36" s="2" t="s">
+      <c r="P36" s="4"/>
+      <c r="Q36" s="4"/>
+      <c r="R36" s="4"/>
+      <c r="S36" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B37" t="s">
         <v>43</v>
@@ -2910,29 +3333,32 @@
         <v>62</v>
       </c>
       <c r="I37" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L37" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
-      <c r="P37" s="2" t="s">
+      <c r="P37" s="4"/>
+      <c r="Q37" s="4"/>
+      <c r="R37" s="4"/>
+      <c r="S37" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B38" t="s">
         <v>44</v>
@@ -2956,29 +3382,32 @@
         <v>62</v>
       </c>
       <c r="I38" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L38" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M38" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N38" s="4"/>
       <c r="O38" s="4"/>
-      <c r="P38" s="2" t="s">
+      <c r="P38" s="4"/>
+      <c r="Q38" s="4"/>
+      <c r="R38" s="4"/>
+      <c r="S38" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B39" t="s">
         <v>45</v>
@@ -3002,29 +3431,32 @@
         <v>62</v>
       </c>
       <c r="I39" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L39" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M39" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N39" s="4"/>
       <c r="O39" s="4"/>
-      <c r="P39" s="2" t="s">
+      <c r="P39" s="4"/>
+      <c r="Q39" s="4"/>
+      <c r="R39" s="4"/>
+      <c r="S39" s="2" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B40" t="s">
         <v>159</v>
@@ -3054,23 +3486,26 @@
         <v>83</v>
       </c>
       <c r="K40" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L40" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M40" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
-      <c r="P40" s="2" t="s">
+      <c r="P40" s="4"/>
+      <c r="Q40" s="4"/>
+      <c r="R40" s="4"/>
+      <c r="S40" s="2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
@@ -3097,26 +3532,29 @@
         <v>63</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L41" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M41" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N41" s="4"/>
       <c r="O41" s="4"/>
-      <c r="P41" s="2" t="s">
+      <c r="P41" s="4"/>
+      <c r="Q41" s="4"/>
+      <c r="R41" s="4"/>
+      <c r="S41" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B42" t="s">
         <v>160</v>
@@ -3143,26 +3581,29 @@
         <v>63</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L42" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M42" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
-      <c r="P42" s="2" t="s">
+      <c r="P42" s="4"/>
+      <c r="Q42" s="4"/>
+      <c r="R42" s="4"/>
+      <c r="S42" s="2" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B43" t="s">
         <v>47</v>
@@ -3189,26 +3630,29 @@
         <v>63</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L43" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
-      <c r="P43" s="2" t="s">
+      <c r="P43" s="4"/>
+      <c r="Q43" s="4"/>
+      <c r="R43" s="4"/>
+      <c r="S43" s="2" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B44" t="s">
         <v>48</v>
@@ -3235,26 +3679,29 @@
         <v>63</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L44" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
-      <c r="P44" s="2" t="s">
+      <c r="P44" s="4"/>
+      <c r="Q44" s="4"/>
+      <c r="R44" s="4"/>
+      <c r="S44" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>161</v>
@@ -3281,26 +3728,29 @@
         <v>63</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L45" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N45" s="4"/>
       <c r="O45" s="4"/>
-      <c r="P45" s="2" t="s">
+      <c r="P45" s="4"/>
+      <c r="Q45" s="4"/>
+      <c r="R45" s="4"/>
+      <c r="S45" s="2" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B46" t="s">
         <v>49</v>
@@ -3327,26 +3777,29 @@
         <v>63</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L46" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N46" s="4"/>
       <c r="O46" s="4"/>
-      <c r="P46" s="2" t="s">
+      <c r="P46" s="4"/>
+      <c r="Q46" s="4"/>
+      <c r="R46" s="4"/>
+      <c r="S46" s="2" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B47" t="s">
         <v>50</v>
@@ -3373,26 +3826,29 @@
         <v>63</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L47" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N47" s="4"/>
       <c r="O47" s="4"/>
-      <c r="P47" s="2" t="s">
+      <c r="P47" s="4"/>
+      <c r="Q47" s="4"/>
+      <c r="R47" s="4"/>
+      <c r="S47" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B48" t="s">
         <v>51</v>
@@ -3419,26 +3875,29 @@
         <v>63</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L48" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
-      <c r="P48" s="2" t="s">
+      <c r="P48" s="4"/>
+      <c r="Q48" s="4"/>
+      <c r="R48" s="4"/>
+      <c r="S48" s="2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B49" t="s">
         <v>52</v>
@@ -3465,26 +3924,29 @@
         <v>63</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L49" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N49" s="4"/>
       <c r="O49" s="4"/>
-      <c r="P49" s="2" t="s">
+      <c r="P49" s="4"/>
+      <c r="Q49" s="4"/>
+      <c r="R49" s="4"/>
+      <c r="S49" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B50" t="s">
         <v>53</v>
@@ -3511,26 +3973,29 @@
         <v>63</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L50" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
-      <c r="P50" s="2" t="s">
+      <c r="P50" s="4"/>
+      <c r="Q50" s="4"/>
+      <c r="R50" s="4"/>
+      <c r="S50" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B51" t="s">
         <v>54</v>
@@ -3557,26 +4022,29 @@
         <v>63</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L51" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M51" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N51" s="4"/>
       <c r="O51" s="4"/>
-      <c r="P51" s="2" t="s">
+      <c r="P51" s="4"/>
+      <c r="Q51" s="4"/>
+      <c r="R51" s="4"/>
+      <c r="S51" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B52" t="s">
         <v>55</v>
@@ -3603,26 +4071,29 @@
         <v>64</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L52" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M52" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
-      <c r="P52" s="2" t="s">
+      <c r="P52" s="4"/>
+      <c r="Q52" s="4"/>
+      <c r="R52" s="4"/>
+      <c r="S52" s="2" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="53" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B53" t="s">
         <v>56</v>
@@ -3649,26 +4120,29 @@
         <v>63</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L53" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M53" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N53" s="4"/>
       <c r="O53" s="4"/>
-      <c r="P53" s="2" t="s">
+      <c r="P53" s="4"/>
+      <c r="Q53" s="4"/>
+      <c r="R53" s="4"/>
+      <c r="S53" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B54" t="s">
         <v>57</v>
@@ -3695,30 +4169,33 @@
         <v>64</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L54" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M54" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N54" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="P54" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="P54" s="4"/>
+      <c r="Q54" s="4"/>
+      <c r="R54" s="4"/>
+      <c r="S54" s="2" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B55" t="s">
         <v>58</v>
@@ -3745,29 +4222,32 @@
         <v>63</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L55" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M55" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N55" s="4"/>
       <c r="O55" s="4"/>
-      <c r="P55" s="2" t="s">
+      <c r="P55" s="4"/>
+      <c r="Q55" s="4"/>
+      <c r="R55" s="4"/>
+      <c r="S55" s="2" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B56" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C56" t="s">
         <v>156</v>
@@ -3788,25 +4268,36 @@
         <v>64</v>
       </c>
       <c r="J56" t="s">
+        <v>217</v>
+      </c>
+      <c r="K56" t="s">
+        <v>225</v>
+      </c>
+      <c r="L56" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="K56" t="s">
-        <v>226</v>
-      </c>
-      <c r="L56" s="6" t="s">
+      <c r="M56" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="N56" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="O56" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="P56" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q56" s="6"/>
+      <c r="R56" s="6"/>
+      <c r="S56"/>
+    </row>
+    <row r="57" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>234</v>
+      </c>
+      <c r="B57" t="s">
         <v>219</v>
-      </c>
-      <c r="M56" s="6"/>
-      <c r="N56" s="6"/>
-      <c r="O56" s="6"/>
-      <c r="P56"/>
-    </row>
-    <row r="57" spans="1:16" ht="30.15" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>235</v>
-      </c>
-      <c r="B57" t="s">
-        <v>220</v>
       </c>
       <c r="C57" t="s">
         <v>156</v>
@@ -3818,37 +4309,48 @@
         <v>14.45</v>
       </c>
       <c r="F57" t="s">
+        <v>220</v>
+      </c>
+      <c r="G57" t="s">
+        <v>220</v>
+      </c>
+      <c r="H57" t="s">
         <v>221</v>
       </c>
-      <c r="G57" t="s">
-        <v>221</v>
-      </c>
-      <c r="H57" t="s">
+      <c r="I57" t="s">
         <v>222</v>
       </c>
-      <c r="I57" t="s">
-        <v>223</v>
-      </c>
       <c r="J57" t="s">
+        <v>217</v>
+      </c>
+      <c r="K57" t="s">
+        <v>225</v>
+      </c>
+      <c r="L57" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="K57" t="s">
-        <v>226</v>
-      </c>
-      <c r="L57" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="M57" s="6"/>
-      <c r="N57" s="6"/>
-      <c r="O57" s="6"/>
-      <c r="P57"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M57" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="N57" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="O57" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="P57" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q57" s="6"/>
+      <c r="R57" s="6"/>
+      <c r="S57"/>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B58" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C58" t="s">
         <v>156</v>
@@ -3872,22 +4374,22 @@
         <v>63</v>
       </c>
       <c r="J58" t="s">
+        <v>246</v>
+      </c>
+      <c r="K58" t="s">
+        <v>259</v>
+      </c>
+      <c r="L58" t="s">
+        <v>260</v>
+      </c>
+      <c r="S58"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>253</v>
+      </c>
+      <c r="B59" t="s">
         <v>247</v>
-      </c>
-      <c r="K58" t="s">
-        <v>260</v>
-      </c>
-      <c r="L58" t="s">
-        <v>261</v>
-      </c>
-      <c r="P58"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>254</v>
-      </c>
-      <c r="B59" t="s">
-        <v>248</v>
       </c>
       <c r="C59" t="s">
         <v>148</v>
@@ -3908,25 +4410,25 @@
         <v>62</v>
       </c>
       <c r="I59" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J59" t="s">
+        <v>248</v>
+      </c>
+      <c r="K59" t="s">
+        <v>259</v>
+      </c>
+      <c r="L59" t="s">
+        <v>260</v>
+      </c>
+      <c r="S59"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>254</v>
+      </c>
+      <c r="B60" t="s">
         <v>249</v>
-      </c>
-      <c r="K59" t="s">
-        <v>260</v>
-      </c>
-      <c r="L59" t="s">
-        <v>261</v>
-      </c>
-      <c r="P59"/>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>255</v>
-      </c>
-      <c r="B60" t="s">
-        <v>250</v>
       </c>
       <c r="C60" t="s">
         <v>157</v>
@@ -3950,22 +4452,22 @@
         <v>63</v>
       </c>
       <c r="J60" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K60" t="s">
+        <v>259</v>
+      </c>
+      <c r="L60" t="s">
         <v>260</v>
       </c>
-      <c r="L60" t="s">
-        <v>261</v>
-      </c>
-      <c r="P60"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="S60"/>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B61" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C61" t="s">
         <v>156</v>
@@ -3986,25 +4488,37 @@
         <v>62</v>
       </c>
       <c r="I61" t="s">
+        <v>258</v>
+      </c>
+      <c r="J61" t="s">
+        <v>248</v>
+      </c>
+      <c r="K61" t="s">
         <v>259</v>
       </c>
-      <c r="J61" t="s">
-        <v>249</v>
-      </c>
-      <c r="K61" t="s">
+      <c r="L61" t="s">
         <v>260</v>
       </c>
-      <c r="L61" t="s">
-        <v>261</v>
-      </c>
-      <c r="P61"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M61" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="N61" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="O61" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="P61" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="S61"/>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B62" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C62" t="s">
         <v>156</v>
@@ -4025,28 +4539,28 @@
         <v>62</v>
       </c>
       <c r="I62" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J62" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K62" t="s">
+        <v>259</v>
+      </c>
+      <c r="L62" t="s">
         <v>260</v>
       </c>
-      <c r="L62" t="s">
-        <v>261</v>
-      </c>
       <c r="M62" t="s">
-        <v>266</v>
-      </c>
-      <c r="P62"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+        <v>265</v>
+      </c>
+      <c r="S62"/>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B63" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C63" t="s">
         <v>156</v>
@@ -4067,25 +4581,25 @@
         <v>62</v>
       </c>
       <c r="I63" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J63" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K63" t="s">
+        <v>259</v>
+      </c>
+      <c r="L63" t="s">
         <v>260</v>
       </c>
-      <c r="L63" t="s">
-        <v>261</v>
-      </c>
-      <c r="P63"/>
-    </row>
-    <row r="64" spans="1:16" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="S63"/>
+    </row>
+    <row r="64" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>267</v>
+        <v>343</v>
       </c>
       <c r="B64" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C64" t="s">
         <v>156</v>
@@ -4097,10 +4611,10 @@
         <v>41.797699999999999</v>
       </c>
       <c r="F64" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G64" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H64" t="s">
         <v>62</v>
@@ -4109,24 +4623,24 @@
         <v>64</v>
       </c>
       <c r="J64" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K64" t="s">
+        <v>266</v>
+      </c>
+      <c r="L64" t="s">
+        <v>265</v>
+      </c>
+      <c r="S64" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>277</v>
+      </c>
+      <c r="B65" t="s">
         <v>268</v>
-      </c>
-      <c r="L64" t="s">
-        <v>266</v>
-      </c>
-      <c r="P64" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>279</v>
-      </c>
-      <c r="B65" t="s">
-        <v>270</v>
       </c>
       <c r="C65" t="s">
         <v>149</v>
@@ -4150,22 +4664,22 @@
         <v>63</v>
       </c>
       <c r="J65" t="s">
+        <v>267</v>
+      </c>
+      <c r="K65" t="s">
+        <v>276</v>
+      </c>
+      <c r="L65" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="S65"/>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>278</v>
+      </c>
+      <c r="B66" t="s">
         <v>269</v>
-      </c>
-      <c r="K65" t="s">
-        <v>278</v>
-      </c>
-      <c r="L65" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="P65"/>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>280</v>
-      </c>
-      <c r="B66" t="s">
-        <v>271</v>
       </c>
       <c r="C66" t="s">
         <v>149</v>
@@ -4189,25 +4703,25 @@
         <v>63</v>
       </c>
       <c r="J66" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="K66" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="P66"/>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+        <v>272</v>
+      </c>
+      <c r="S66"/>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B67" t="s">
         <v>37</v>
       </c>
       <c r="C67" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D67">
         <v>68.252960000000002</v>
@@ -4225,28 +4739,28 @@
         <v>62</v>
       </c>
       <c r="I67" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J67" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="K67" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="P67"/>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+        <v>272</v>
+      </c>
+      <c r="S67"/>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B68" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C68" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D68">
         <v>44.407859000000002</v>
@@ -4264,18 +4778,1647 @@
         <v>62</v>
       </c>
       <c r="I68" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J68" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="K68" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="P68"/>
+        <v>272</v>
+      </c>
+      <c r="S68"/>
+    </row>
+    <row r="69" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>344</v>
+      </c>
+      <c r="B69" t="s">
+        <v>287</v>
+      </c>
+      <c r="C69" t="s">
+        <v>240</v>
+      </c>
+      <c r="D69">
+        <v>49.142899999999997</v>
+      </c>
+      <c r="E69">
+        <v>13.556100000000001</v>
+      </c>
+      <c r="F69" t="s">
+        <v>220</v>
+      </c>
+      <c r="G69" t="s">
+        <v>220</v>
+      </c>
+      <c r="H69" t="s">
+        <v>221</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L69" t="s">
+        <v>283</v>
+      </c>
+      <c r="M69" t="s">
+        <v>284</v>
+      </c>
+      <c r="N69" t="s">
+        <v>285</v>
+      </c>
+      <c r="O69" t="s">
+        <v>286</v>
+      </c>
+      <c r="S69"/>
+    </row>
+    <row r="70" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>345</v>
+      </c>
+      <c r="B70" t="s">
+        <v>288</v>
+      </c>
+      <c r="C70" t="s">
+        <v>289</v>
+      </c>
+      <c r="D70">
+        <v>50.533000000000001</v>
+      </c>
+      <c r="E70">
+        <v>13.616</v>
+      </c>
+      <c r="F70" t="s">
+        <v>220</v>
+      </c>
+      <c r="G70" t="s">
+        <v>220</v>
+      </c>
+      <c r="H70" t="s">
+        <v>221</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L70" t="s">
+        <v>283</v>
+      </c>
+      <c r="M70" t="s">
+        <v>284</v>
+      </c>
+      <c r="N70" t="s">
+        <v>285</v>
+      </c>
+      <c r="O70" t="s">
+        <v>286</v>
+      </c>
+      <c r="S70"/>
+    </row>
+    <row r="71" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>346</v>
+      </c>
+      <c r="B71" t="s">
+        <v>290</v>
+      </c>
+      <c r="C71" t="s">
+        <v>156</v>
+      </c>
+      <c r="D71">
+        <v>60.205500000000001</v>
+      </c>
+      <c r="E71">
+        <v>24.655899999999999</v>
+      </c>
+      <c r="F71" t="s">
+        <v>291</v>
+      </c>
+      <c r="G71" t="s">
+        <v>291</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L71" t="s">
+        <v>283</v>
+      </c>
+      <c r="M71" t="s">
+        <v>284</v>
+      </c>
+      <c r="N71" t="s">
+        <v>285</v>
+      </c>
+      <c r="O71" t="s">
+        <v>286</v>
+      </c>
+      <c r="S71"/>
+    </row>
+    <row r="72" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>347</v>
+      </c>
+      <c r="B72" t="s">
+        <v>292</v>
+      </c>
+      <c r="C72" t="s">
+        <v>240</v>
+      </c>
+      <c r="D72">
+        <v>62.554000000000002</v>
+      </c>
+      <c r="E72">
+        <v>24.061900000000001</v>
+      </c>
+      <c r="F72" t="s">
+        <v>291</v>
+      </c>
+      <c r="G72" t="s">
+        <v>291</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L72" t="s">
+        <v>283</v>
+      </c>
+      <c r="M72" t="s">
+        <v>284</v>
+      </c>
+      <c r="N72" t="s">
+        <v>285</v>
+      </c>
+      <c r="O72" t="s">
+        <v>286</v>
+      </c>
+      <c r="S72"/>
+    </row>
+    <row r="73" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>348</v>
+      </c>
+      <c r="B73" t="s">
+        <v>293</v>
+      </c>
+      <c r="C73" t="s">
+        <v>156</v>
+      </c>
+      <c r="D73">
+        <v>60.1935</v>
+      </c>
+      <c r="E73">
+        <v>24.954999999999998</v>
+      </c>
+      <c r="F73" t="s">
+        <v>291</v>
+      </c>
+      <c r="G73" t="s">
+        <v>291</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L73" t="s">
+        <v>283</v>
+      </c>
+      <c r="M73" t="s">
+        <v>284</v>
+      </c>
+      <c r="N73" t="s">
+        <v>285</v>
+      </c>
+      <c r="O73" t="s">
+        <v>286</v>
+      </c>
+      <c r="S73"/>
+    </row>
+    <row r="74" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>349</v>
+      </c>
+      <c r="B74" t="s">
+        <v>294</v>
+      </c>
+      <c r="C74" t="s">
+        <v>295</v>
+      </c>
+      <c r="D74">
+        <v>52.800866999999997</v>
+      </c>
+      <c r="E74">
+        <v>10.75623</v>
+      </c>
+      <c r="F74" t="s">
+        <v>296</v>
+      </c>
+      <c r="G74" t="s">
+        <v>296</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L74" t="s">
+        <v>283</v>
+      </c>
+      <c r="M74" t="s">
+        <v>284</v>
+      </c>
+      <c r="N74" t="s">
+        <v>285</v>
+      </c>
+      <c r="O74" t="s">
+        <v>286</v>
+      </c>
+      <c r="S74"/>
+    </row>
+    <row r="75" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>350</v>
+      </c>
+      <c r="B75" t="s">
+        <v>297</v>
+      </c>
+      <c r="C75" t="s">
+        <v>156</v>
+      </c>
+      <c r="D75">
+        <v>49.976999999999997</v>
+      </c>
+      <c r="E75">
+        <v>9.1521000000000008</v>
+      </c>
+      <c r="F75" t="s">
+        <v>296</v>
+      </c>
+      <c r="G75" t="s">
+        <v>296</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L75" t="s">
+        <v>283</v>
+      </c>
+      <c r="M75" t="s">
+        <v>284</v>
+      </c>
+      <c r="N75" t="s">
+        <v>285</v>
+      </c>
+      <c r="O75" t="s">
+        <v>286</v>
+      </c>
+      <c r="S75"/>
+    </row>
+    <row r="76" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>351</v>
+      </c>
+      <c r="B76" t="s">
+        <v>298</v>
+      </c>
+      <c r="C76" t="s">
+        <v>340</v>
+      </c>
+      <c r="D76">
+        <v>51.083863999999998</v>
+      </c>
+      <c r="E76">
+        <v>6.9210539999999998</v>
+      </c>
+      <c r="F76" t="s">
+        <v>296</v>
+      </c>
+      <c r="G76" t="s">
+        <v>296</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L76" t="s">
+        <v>283</v>
+      </c>
+      <c r="M76" t="s">
+        <v>284</v>
+      </c>
+      <c r="N76" t="s">
+        <v>285</v>
+      </c>
+      <c r="O76" t="s">
+        <v>286</v>
+      </c>
+      <c r="S76"/>
+    </row>
+    <row r="77" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>352</v>
+      </c>
+      <c r="B77" t="s">
+        <v>299</v>
+      </c>
+      <c r="C77" t="s">
+        <v>156</v>
+      </c>
+      <c r="D77">
+        <v>51.523899999999998</v>
+      </c>
+      <c r="E77">
+        <v>6.9284999999999997</v>
+      </c>
+      <c r="F77" t="s">
+        <v>296</v>
+      </c>
+      <c r="G77" t="s">
+        <v>296</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L77" t="s">
+        <v>283</v>
+      </c>
+      <c r="M77" t="s">
+        <v>284</v>
+      </c>
+      <c r="N77" t="s">
+        <v>285</v>
+      </c>
+      <c r="O77" t="s">
+        <v>286</v>
+      </c>
+      <c r="S77"/>
+    </row>
+    <row r="78" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>353</v>
+      </c>
+      <c r="B78" t="s">
+        <v>339</v>
+      </c>
+      <c r="C78" t="s">
+        <v>156</v>
+      </c>
+      <c r="D78">
+        <v>51.463000000000001</v>
+      </c>
+      <c r="E78">
+        <v>7.0810000000000004</v>
+      </c>
+      <c r="F78" t="s">
+        <v>296</v>
+      </c>
+      <c r="G78" t="s">
+        <v>296</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L78" t="s">
+        <v>283</v>
+      </c>
+      <c r="M78" t="s">
+        <v>284</v>
+      </c>
+      <c r="N78" t="s">
+        <v>285</v>
+      </c>
+      <c r="O78" t="s">
+        <v>286</v>
+      </c>
+      <c r="S78"/>
+    </row>
+    <row r="79" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>354</v>
+      </c>
+      <c r="B79" t="s">
+        <v>300</v>
+      </c>
+      <c r="C79" t="s">
+        <v>240</v>
+      </c>
+      <c r="D79">
+        <v>47.491999999999997</v>
+      </c>
+      <c r="E79">
+        <v>11.095499999999999</v>
+      </c>
+      <c r="F79" t="s">
+        <v>296</v>
+      </c>
+      <c r="G79" t="s">
+        <v>296</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L79" t="s">
+        <v>283</v>
+      </c>
+      <c r="M79" t="s">
+        <v>284</v>
+      </c>
+      <c r="N79" t="s">
+        <v>285</v>
+      </c>
+      <c r="O79" t="s">
+        <v>286</v>
+      </c>
+      <c r="S79"/>
+    </row>
+    <row r="80" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>355</v>
+      </c>
+      <c r="B80" t="s">
+        <v>301</v>
+      </c>
+      <c r="C80" t="s">
+        <v>156</v>
+      </c>
+      <c r="D80">
+        <v>41.902799999999999</v>
+      </c>
+      <c r="E80">
+        <v>12.4964</v>
+      </c>
+      <c r="F80" t="s">
+        <v>302</v>
+      </c>
+      <c r="G80" t="s">
+        <v>302</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L80" t="s">
+        <v>283</v>
+      </c>
+      <c r="M80" t="s">
+        <v>284</v>
+      </c>
+      <c r="N80" t="s">
+        <v>285</v>
+      </c>
+      <c r="O80" t="s">
+        <v>286</v>
+      </c>
+      <c r="S80"/>
+    </row>
+    <row r="81" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>356</v>
+      </c>
+      <c r="B81" t="s">
+        <v>303</v>
+      </c>
+      <c r="C81" t="s">
+        <v>338</v>
+      </c>
+      <c r="D81">
+        <v>42.05</v>
+      </c>
+      <c r="E81">
+        <v>12.3</v>
+      </c>
+      <c r="F81" t="s">
+        <v>302</v>
+      </c>
+      <c r="G81" t="s">
+        <v>302</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L81" t="s">
+        <v>283</v>
+      </c>
+      <c r="M81" t="s">
+        <v>284</v>
+      </c>
+      <c r="N81" t="s">
+        <v>285</v>
+      </c>
+      <c r="O81" t="s">
+        <v>286</v>
+      </c>
+      <c r="S81"/>
+    </row>
+    <row r="82" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>357</v>
+      </c>
+      <c r="B82" t="s">
+        <v>304</v>
+      </c>
+      <c r="C82" t="s">
+        <v>156</v>
+      </c>
+      <c r="D82">
+        <v>45.464199999999998</v>
+      </c>
+      <c r="E82">
+        <v>9.19</v>
+      </c>
+      <c r="F82" t="s">
+        <v>302</v>
+      </c>
+      <c r="G82" t="s">
+        <v>302</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L82" t="s">
+        <v>283</v>
+      </c>
+      <c r="M82" t="s">
+        <v>284</v>
+      </c>
+      <c r="N82" t="s">
+        <v>285</v>
+      </c>
+      <c r="O82" t="s">
+        <v>286</v>
+      </c>
+      <c r="S82"/>
+    </row>
+    <row r="83" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>358</v>
+      </c>
+      <c r="B83" t="s">
+        <v>305</v>
+      </c>
+      <c r="C83" t="s">
+        <v>156</v>
+      </c>
+      <c r="D83">
+        <v>45.440800000000003</v>
+      </c>
+      <c r="E83">
+        <v>12.3155</v>
+      </c>
+      <c r="F83" t="s">
+        <v>302</v>
+      </c>
+      <c r="G83" t="s">
+        <v>302</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L83" t="s">
+        <v>283</v>
+      </c>
+      <c r="M83" t="s">
+        <v>284</v>
+      </c>
+      <c r="N83" t="s">
+        <v>285</v>
+      </c>
+      <c r="O83" t="s">
+        <v>286</v>
+      </c>
+      <c r="S83"/>
+    </row>
+    <row r="84" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>359</v>
+      </c>
+      <c r="B84" t="s">
+        <v>306</v>
+      </c>
+      <c r="C84" t="s">
+        <v>337</v>
+      </c>
+      <c r="D84">
+        <v>51.912500000000001</v>
+      </c>
+      <c r="E84">
+        <v>4.3417000000000003</v>
+      </c>
+      <c r="F84" t="s">
+        <v>307</v>
+      </c>
+      <c r="G84" t="s">
+        <v>307</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L84" t="s">
+        <v>283</v>
+      </c>
+      <c r="M84" t="s">
+        <v>284</v>
+      </c>
+      <c r="N84" t="s">
+        <v>285</v>
+      </c>
+      <c r="O84" t="s">
+        <v>286</v>
+      </c>
+      <c r="S84"/>
+    </row>
+    <row r="85" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>360</v>
+      </c>
+      <c r="B85" t="s">
+        <v>308</v>
+      </c>
+      <c r="C85" t="s">
+        <v>240</v>
+      </c>
+      <c r="D85">
+        <v>52.1</v>
+      </c>
+      <c r="E85">
+        <v>6.6612</v>
+      </c>
+      <c r="F85" t="s">
+        <v>307</v>
+      </c>
+      <c r="G85" t="s">
+        <v>307</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L85" t="s">
+        <v>283</v>
+      </c>
+      <c r="M85" t="s">
+        <v>284</v>
+      </c>
+      <c r="N85" t="s">
+        <v>285</v>
+      </c>
+      <c r="O85" t="s">
+        <v>286</v>
+      </c>
+      <c r="S85"/>
+    </row>
+    <row r="86" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>361</v>
+      </c>
+      <c r="B86" t="s">
+        <v>309</v>
+      </c>
+      <c r="C86" t="s">
+        <v>157</v>
+      </c>
+      <c r="D86">
+        <v>51.5383</v>
+      </c>
+      <c r="E86">
+        <v>5.8678999999999997</v>
+      </c>
+      <c r="F86" t="s">
+        <v>307</v>
+      </c>
+      <c r="G86" t="s">
+        <v>307</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L86" t="s">
+        <v>283</v>
+      </c>
+      <c r="M86" t="s">
+        <v>284</v>
+      </c>
+      <c r="N86" t="s">
+        <v>285</v>
+      </c>
+      <c r="O86" t="s">
+        <v>286</v>
+      </c>
+      <c r="S86"/>
+    </row>
+    <row r="87" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>362</v>
+      </c>
+      <c r="B87" t="s">
+        <v>310</v>
+      </c>
+      <c r="C87" t="s">
+        <v>157</v>
+      </c>
+      <c r="D87">
+        <v>50.9054</v>
+      </c>
+      <c r="E87">
+        <v>5.8836000000000004</v>
+      </c>
+      <c r="F87" t="s">
+        <v>307</v>
+      </c>
+      <c r="G87" t="s">
+        <v>307</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L87" t="s">
+        <v>283</v>
+      </c>
+      <c r="M87" t="s">
+        <v>284</v>
+      </c>
+      <c r="N87" t="s">
+        <v>285</v>
+      </c>
+      <c r="O87" t="s">
+        <v>286</v>
+      </c>
+      <c r="S87"/>
+    </row>
+    <row r="88" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>363</v>
+      </c>
+      <c r="B88" t="s">
+        <v>311</v>
+      </c>
+      <c r="C88" t="s">
+        <v>336</v>
+      </c>
+      <c r="D88">
+        <v>59.276499999999999</v>
+      </c>
+      <c r="E88">
+        <v>11.1305</v>
+      </c>
+      <c r="F88" t="s">
+        <v>60</v>
+      </c>
+      <c r="G88" t="s">
+        <v>60</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L88" t="s">
+        <v>283</v>
+      </c>
+      <c r="M88" t="s">
+        <v>284</v>
+      </c>
+      <c r="N88" t="s">
+        <v>285</v>
+      </c>
+      <c r="O88" t="s">
+        <v>286</v>
+      </c>
+      <c r="S88"/>
+    </row>
+    <row r="89" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>364</v>
+      </c>
+      <c r="B89" t="s">
+        <v>312</v>
+      </c>
+      <c r="C89" t="s">
+        <v>335</v>
+      </c>
+      <c r="D89">
+        <v>58.383333</v>
+      </c>
+      <c r="E89">
+        <v>8.25</v>
+      </c>
+      <c r="F89" t="s">
+        <v>60</v>
+      </c>
+      <c r="G89" t="s">
+        <v>60</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L89" t="s">
+        <v>283</v>
+      </c>
+      <c r="M89" t="s">
+        <v>284</v>
+      </c>
+      <c r="N89" t="s">
+        <v>285</v>
+      </c>
+      <c r="O89" t="s">
+        <v>286</v>
+      </c>
+      <c r="S89"/>
+    </row>
+    <row r="90" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>365</v>
+      </c>
+      <c r="B90" t="s">
+        <v>313</v>
+      </c>
+      <c r="C90" t="s">
+        <v>156</v>
+      </c>
+      <c r="D90">
+        <v>59.311999999999998</v>
+      </c>
+      <c r="E90">
+        <v>18.082999999999998</v>
+      </c>
+      <c r="F90" t="s">
+        <v>314</v>
+      </c>
+      <c r="G90" t="s">
+        <v>314</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K90" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L90" t="s">
+        <v>283</v>
+      </c>
+      <c r="M90" t="s">
+        <v>284</v>
+      </c>
+      <c r="N90" t="s">
+        <v>285</v>
+      </c>
+      <c r="O90" t="s">
+        <v>286</v>
+      </c>
+      <c r="S90"/>
+    </row>
+    <row r="91" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>366</v>
+      </c>
+      <c r="B91" t="s">
+        <v>315</v>
+      </c>
+      <c r="C91" t="s">
+        <v>156</v>
+      </c>
+      <c r="D91">
+        <v>59.329300000000003</v>
+      </c>
+      <c r="E91">
+        <v>18.0686</v>
+      </c>
+      <c r="F91" t="s">
+        <v>314</v>
+      </c>
+      <c r="G91" t="s">
+        <v>314</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K91" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L91" t="s">
+        <v>283</v>
+      </c>
+      <c r="M91" t="s">
+        <v>284</v>
+      </c>
+      <c r="N91" t="s">
+        <v>285</v>
+      </c>
+      <c r="O91" t="s">
+        <v>286</v>
+      </c>
+      <c r="S91"/>
+    </row>
+    <row r="92" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>367</v>
+      </c>
+      <c r="B92" t="s">
+        <v>316</v>
+      </c>
+      <c r="C92" t="s">
+        <v>335</v>
+      </c>
+      <c r="D92">
+        <v>58.8</v>
+      </c>
+      <c r="E92">
+        <v>17.383333</v>
+      </c>
+      <c r="F92" t="s">
+        <v>314</v>
+      </c>
+      <c r="G92" t="s">
+        <v>314</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L92" t="s">
+        <v>283</v>
+      </c>
+      <c r="M92" t="s">
+        <v>284</v>
+      </c>
+      <c r="N92" t="s">
+        <v>285</v>
+      </c>
+      <c r="O92" t="s">
+        <v>286</v>
+      </c>
+      <c r="S92"/>
+    </row>
+    <row r="93" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>368</v>
+      </c>
+      <c r="B93" t="s">
+        <v>317</v>
+      </c>
+      <c r="C93" t="s">
+        <v>330</v>
+      </c>
+      <c r="D93">
+        <v>53.234000000000002</v>
+      </c>
+      <c r="E93">
+        <v>-0.54169999999999996</v>
+      </c>
+      <c r="F93" t="s">
+        <v>144</v>
+      </c>
+      <c r="G93" t="s">
+        <v>144</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="J93" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K93" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L93" t="s">
+        <v>283</v>
+      </c>
+      <c r="M93" t="s">
+        <v>284</v>
+      </c>
+      <c r="N93" t="s">
+        <v>285</v>
+      </c>
+      <c r="O93" t="s">
+        <v>286</v>
+      </c>
+      <c r="S93"/>
+    </row>
+    <row r="94" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>369</v>
+      </c>
+      <c r="B94" t="s">
+        <v>318</v>
+      </c>
+      <c r="C94" t="s">
+        <v>330</v>
+      </c>
+      <c r="D94">
+        <v>51.210700000000003</v>
+      </c>
+      <c r="E94">
+        <v>-2.6475</v>
+      </c>
+      <c r="F94" t="s">
+        <v>144</v>
+      </c>
+      <c r="G94" t="s">
+        <v>144</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K94" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L94" t="s">
+        <v>283</v>
+      </c>
+      <c r="M94" t="s">
+        <v>284</v>
+      </c>
+      <c r="N94" t="s">
+        <v>285</v>
+      </c>
+      <c r="O94" t="s">
+        <v>286</v>
+      </c>
+      <c r="S94"/>
+    </row>
+    <row r="95" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>370</v>
+      </c>
+      <c r="B95" t="s">
+        <v>319</v>
+      </c>
+      <c r="C95" t="s">
+        <v>154</v>
+      </c>
+      <c r="D95">
+        <v>55.066000000000003</v>
+      </c>
+      <c r="E95">
+        <v>-4.2839999999999998</v>
+      </c>
+      <c r="F95" t="s">
+        <v>144</v>
+      </c>
+      <c r="G95" t="s">
+        <v>144</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K95" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L95" t="s">
+        <v>283</v>
+      </c>
+      <c r="M95" t="s">
+        <v>284</v>
+      </c>
+      <c r="N95" t="s">
+        <v>285</v>
+      </c>
+      <c r="O95" t="s">
+        <v>286</v>
+      </c>
+      <c r="S95"/>
+    </row>
+    <row r="96" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>371</v>
+      </c>
+      <c r="B96" t="s">
+        <v>320</v>
+      </c>
+      <c r="C96" t="s">
+        <v>157</v>
+      </c>
+      <c r="D96">
+        <v>51.947000000000003</v>
+      </c>
+      <c r="E96">
+        <v>-2.1080000000000001</v>
+      </c>
+      <c r="F96" t="s">
+        <v>144</v>
+      </c>
+      <c r="G96" t="s">
+        <v>144</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K96" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L96" t="s">
+        <v>283</v>
+      </c>
+      <c r="M96" t="s">
+        <v>284</v>
+      </c>
+      <c r="N96" t="s">
+        <v>285</v>
+      </c>
+      <c r="O96" t="s">
+        <v>286</v>
+      </c>
+      <c r="S96"/>
+    </row>
+    <row r="97" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>373</v>
+      </c>
+      <c r="B97" t="s">
+        <v>321</v>
+      </c>
+      <c r="C97" t="s">
+        <v>156</v>
+      </c>
+      <c r="D97">
+        <v>40.416800000000002</v>
+      </c>
+      <c r="E97">
+        <v>-3.7038000000000002</v>
+      </c>
+      <c r="F97" t="s">
+        <v>322</v>
+      </c>
+      <c r="G97" t="s">
+        <v>322</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K97" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L97" t="s">
+        <v>283</v>
+      </c>
+      <c r="M97" t="s">
+        <v>284</v>
+      </c>
+      <c r="N97" t="s">
+        <v>285</v>
+      </c>
+      <c r="O97" t="s">
+        <v>286</v>
+      </c>
+      <c r="S97"/>
+    </row>
+    <row r="98" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>374</v>
+      </c>
+      <c r="B98" t="s">
+        <v>323</v>
+      </c>
+      <c r="C98" t="s">
+        <v>156</v>
+      </c>
+      <c r="D98">
+        <v>43.262999999999998</v>
+      </c>
+      <c r="E98">
+        <v>-2.9350000000000001</v>
+      </c>
+      <c r="F98" t="s">
+        <v>322</v>
+      </c>
+      <c r="G98" t="s">
+        <v>322</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K98" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L98" t="s">
+        <v>283</v>
+      </c>
+      <c r="M98" t="s">
+        <v>284</v>
+      </c>
+      <c r="N98" t="s">
+        <v>285</v>
+      </c>
+      <c r="O98" t="s">
+        <v>286</v>
+      </c>
+      <c r="S98"/>
+    </row>
+    <row r="99" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>375</v>
+      </c>
+      <c r="B99" t="s">
+        <v>324</v>
+      </c>
+      <c r="C99" t="s">
+        <v>156</v>
+      </c>
+      <c r="D99">
+        <v>39.8628</v>
+      </c>
+      <c r="E99">
+        <v>-4.0273000000000003</v>
+      </c>
+      <c r="F99" t="s">
+        <v>322</v>
+      </c>
+      <c r="G99" t="s">
+        <v>322</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J99" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K99" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L99" t="s">
+        <v>283</v>
+      </c>
+      <c r="M99" t="s">
+        <v>284</v>
+      </c>
+      <c r="N99" t="s">
+        <v>285</v>
+      </c>
+      <c r="O99" t="s">
+        <v>286</v>
+      </c>
+      <c r="S99"/>
+    </row>
+    <row r="100" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>376</v>
+      </c>
+      <c r="B100" t="s">
+        <v>325</v>
+      </c>
+      <c r="C100" t="s">
+        <v>331</v>
+      </c>
+      <c r="D100">
+        <v>59.576000000000001</v>
+      </c>
+      <c r="E100">
+        <v>25.8</v>
+      </c>
+      <c r="F100" t="s">
+        <v>326</v>
+      </c>
+      <c r="G100" t="s">
+        <v>326</v>
+      </c>
+      <c r="H100" t="s">
+        <v>62</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K100" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L100" t="s">
+        <v>283</v>
+      </c>
+      <c r="M100" t="s">
+        <v>284</v>
+      </c>
+      <c r="N100" t="s">
+        <v>285</v>
+      </c>
+      <c r="O100" t="s">
+        <v>286</v>
+      </c>
+      <c r="S100"/>
+    </row>
+    <row r="101" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>377</v>
+      </c>
+      <c r="B101" t="s">
+        <v>333</v>
+      </c>
+      <c r="C101" t="s">
+        <v>156</v>
+      </c>
+      <c r="D101">
+        <v>38.697899999999997</v>
+      </c>
+      <c r="E101">
+        <v>-9.2063000000000006</v>
+      </c>
+      <c r="F101" t="s">
+        <v>327</v>
+      </c>
+      <c r="G101" t="s">
+        <v>327</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="J101" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K101" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L101" t="s">
+        <v>283</v>
+      </c>
+      <c r="M101" t="s">
+        <v>284</v>
+      </c>
+      <c r="N101" t="s">
+        <v>285</v>
+      </c>
+      <c r="O101" t="s">
+        <v>286</v>
+      </c>
+      <c r="S101"/>
+    </row>
+    <row r="102" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>378</v>
+      </c>
+      <c r="B102" t="s">
+        <v>334</v>
+      </c>
+      <c r="C102" t="s">
+        <v>240</v>
+      </c>
+      <c r="D102">
+        <v>45.232999999999997</v>
+      </c>
+      <c r="E102">
+        <v>-78.882999999999996</v>
+      </c>
+      <c r="F102" t="s">
+        <v>328</v>
+      </c>
+      <c r="G102" t="s">
+        <v>328</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L102" t="s">
+        <v>283</v>
+      </c>
+      <c r="M102" t="s">
+        <v>284</v>
+      </c>
+      <c r="N102" t="s">
+        <v>285</v>
+      </c>
+      <c r="O102" t="s">
+        <v>286</v>
+      </c>
+      <c r="S102"/>
+    </row>
+    <row r="103" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>379</v>
+      </c>
+      <c r="B103" t="s">
+        <v>384</v>
+      </c>
+      <c r="C103" t="s">
+        <v>332</v>
+      </c>
+      <c r="D103">
+        <v>35.907899999999998</v>
+      </c>
+      <c r="E103">
+        <v>-78.875</v>
+      </c>
+      <c r="F103" t="s">
+        <v>143</v>
+      </c>
+      <c r="G103" t="s">
+        <v>143</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J103" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K103" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L103" t="s">
+        <v>283</v>
+      </c>
+      <c r="M103" t="s">
+        <v>284</v>
+      </c>
+      <c r="N103" t="s">
+        <v>285</v>
+      </c>
+      <c r="O103" t="s">
+        <v>286</v>
+      </c>
+      <c r="S103"/>
+    </row>
+    <row r="104" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>380</v>
+      </c>
+      <c r="B104" t="s">
+        <v>329</v>
+      </c>
+      <c r="C104" t="s">
+        <v>156</v>
+      </c>
+      <c r="D104">
+        <v>40.369799999999998</v>
+      </c>
+      <c r="E104">
+        <v>-80.633899999999997</v>
+      </c>
+      <c r="F104" t="s">
+        <v>143</v>
+      </c>
+      <c r="G104" t="s">
+        <v>143</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K104" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L104" t="s">
+        <v>283</v>
+      </c>
+      <c r="M104" t="s">
+        <v>284</v>
+      </c>
+      <c r="N104" t="s">
+        <v>285</v>
+      </c>
+      <c r="O104" t="s">
+        <v>286</v>
+      </c>
+      <c r="S104"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khant Swe\OneDrive\桌面\全球腐蚀调研\Europe\Russia\russia-corrosion-map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82A6AA3-8050-4C35-8486-FA50DB7B034A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4E9001-E9FF-404D-9B35-EDDC67D09000}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25135" windowHeight="10093" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="443">
   <si>
     <t>site_id</t>
   </si>
@@ -673,9 +673,6 @@
     <t>Oslo</t>
   </si>
   <si>
-    <t>1980-2026</t>
-  </si>
-  <si>
     <t>https://www.corrosion-sites.com/index.php</t>
   </si>
   <si>
@@ -1126,21 +1123,6 @@
     <t>SE-003</t>
   </si>
   <si>
-    <t>GB-001</t>
-  </si>
-  <si>
-    <t>GB-002</t>
-  </si>
-  <si>
-    <t>GB-003</t>
-  </si>
-  <si>
-    <t>GB-004</t>
-  </si>
-  <si>
-    <t>AQ-GB-001</t>
-  </si>
-  <si>
     <t>ES-001</t>
   </si>
   <si>
@@ -1175,6 +1157,198 @@
   </si>
   <si>
     <t>Research Triangle Park, North Carolina</t>
+  </si>
+  <si>
+    <t>papers/s013.pdf</t>
+  </si>
+  <si>
+    <t>papers/s014.pdf</t>
+  </si>
+  <si>
+    <t>papers/s015.pdf</t>
+  </si>
+  <si>
+    <t>papers/s016.pdf</t>
+  </si>
+  <si>
+    <t>1997-2001 (1, 2, 4 years multipollutant); 2005-06 (1-year multipollutant); 2008-09 (1-year trend exposure); 2011-12</t>
+  </si>
+  <si>
+    <t>1997-2001 (1, 2, 4 years multipollutant)</t>
+  </si>
+  <si>
+    <t>carbon steel</t>
+  </si>
+  <si>
+    <t>Paris</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Berlin</t>
+  </si>
+  <si>
+    <t>Tel Aviv</t>
+  </si>
+  <si>
+    <t>Israel</t>
+  </si>
+  <si>
+    <t>Chaumont</t>
+  </si>
+  <si>
+    <t>Switzerland</t>
+  </si>
+  <si>
+    <t>London</t>
+  </si>
+  <si>
+    <t>Los Angeles</t>
+  </si>
+  <si>
+    <t>Antwerp</t>
+  </si>
+  <si>
+    <t>Belgium</t>
+  </si>
+  <si>
+    <t>Katowice</t>
+  </si>
+  <si>
+    <t>Poland</t>
+  </si>
+  <si>
+    <t>2005-06 (1-year multipollutant); 2008-09 (1-year trend exposure); 2011-12</t>
+  </si>
+  <si>
+    <t>Athens</t>
+  </si>
+  <si>
+    <t>Greece</t>
+  </si>
+  <si>
+    <t>2005-06 (1-year multipollutant); 2008-09 (1-year trend exposure); 2011-13</t>
+  </si>
+  <si>
+    <t>Riga</t>
+  </si>
+  <si>
+    <t>Latvia</t>
+  </si>
+  <si>
+    <t>2005-06 (1-year multipollutant); 2008-09 (1-year trend exposure); 2011-14</t>
+  </si>
+  <si>
+    <t>Vienna</t>
+  </si>
+  <si>
+    <t>Austria</t>
+  </si>
+  <si>
+    <t>2008-09 (1-year trend exposure); 2011-14</t>
+  </si>
+  <si>
+    <t>Sofia</t>
+  </si>
+  <si>
+    <t>Bulgaria</t>
+  </si>
+  <si>
+    <t>2005-06 (1-year multipollutant); 2008-09 (1-year trend exposure)</t>
+  </si>
+  <si>
+    <t>St Petersburg</t>
+  </si>
+  <si>
+    <t>2011-12 (1-year trend exposure)</t>
+  </si>
+  <si>
+    <t>1980-2026; 1997-2001 (1, 2, 4 years multipollutant); 2005-06 (1-year multipollutant); 2008-09 (1-year trend exposure); 2011-12 (1-year trend exposure)</t>
+  </si>
+  <si>
+    <t>1987-1989 (1-2 years); 1987-1991 (4 years); 1987-1995 (8 years); repeated 1-year periods 1987-88, 1992-93, 1994-95; 1997-2001 (1, 2, 4 years multipollutant)</t>
+  </si>
+  <si>
+    <t>Carbon steel, weathering steel, zinc, aluminium, limestone, modern glass</t>
+  </si>
+  <si>
+    <t>Carbon steel, zinc, copper, aluminium, limestone, modern glass</t>
+  </si>
+  <si>
+    <t>1987-1989 (1-2 years); 1987-1991 (4 years); 1987-1995 (8 years); repeated 1-year periods 1987-88, 1992-93, 1994-95; 1997-2001 (1, 2, 4 years multipollutant); 2005-06 (1-year multipollutant); 2008-09 (1-year trend exposure); 2011-12</t>
+  </si>
+  <si>
+    <t>1987-1989 (1-2 years); 1987-1991 (4 years); 1987-1995 (8 years); repeated 1-year periods 1987-88, 1992-93, 1994-95; 1997-2001 (1, 2, 4 years multipollutant); 2005-06 (1-year multipollutant); 2008-09 (1-year trend exposure); 2011-13</t>
+  </si>
+  <si>
+    <t>1-year exposures</t>
+  </si>
+  <si>
+    <t>1987-1989 (1-2 years); 1987-1991 (4 years); 1987-1995 (8 years); repeated 1-year periods 1987-88, 1992-93, 1994-95; 1997-2001 (1, 2, 4 years multipollutant); 2005-06 (1-year multipollutant); 2008-09 (1-year trend exposure)</t>
+  </si>
+  <si>
+    <t>FR-001</t>
+  </si>
+  <si>
+    <t>DE-007</t>
+  </si>
+  <si>
+    <t>IL-001</t>
+  </si>
+  <si>
+    <t>Carbon steel, zinc, copper, weathering steel, limestone, modern glass</t>
+  </si>
+  <si>
+    <t>CH-001</t>
+  </si>
+  <si>
+    <t>US-003</t>
+  </si>
+  <si>
+    <t>UK-005</t>
+  </si>
+  <si>
+    <t>UK-004</t>
+  </si>
+  <si>
+    <t>UK-003</t>
+  </si>
+  <si>
+    <t>UK-002</t>
+  </si>
+  <si>
+    <t>UK-001</t>
+  </si>
+  <si>
+    <t>AQ-UK-001</t>
+  </si>
+  <si>
+    <t>BE-001</t>
+  </si>
+  <si>
+    <t>PL-001</t>
+  </si>
+  <si>
+    <t>GR-001</t>
+  </si>
+  <si>
+    <t>Urban, marine</t>
+  </si>
+  <si>
+    <t>LV-001</t>
+  </si>
+  <si>
+    <t>AT-001</t>
+  </si>
+  <si>
+    <t>BG-001</t>
+  </si>
+  <si>
+    <t>RU-043</t>
+  </si>
+  <si>
+    <t>Carbon steel, zinc, limestone, modern glass, teflon filter</t>
   </si>
 </sst>
 </file>
@@ -1609,7 +1783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S104"/>
+  <dimension ref="A1:U117"/>
   <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.77734375" customWidth="1"/>
@@ -1619,13 +1793,13 @@
     <col min="7" max="7" width="22.33203125" customWidth="1"/>
     <col min="8" max="8" width="12.88671875" customWidth="1"/>
     <col min="9" max="9" width="23.77734375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="33.77734375" customWidth="1"/>
+    <col min="10" max="10" width="44.33203125" customWidth="1"/>
     <col min="11" max="11" width="25.33203125" customWidth="1"/>
-    <col min="12" max="18" width="25.88671875" customWidth="1"/>
-    <col min="19" max="19" width="60.77734375" style="2" customWidth="1"/>
+    <col min="12" max="20" width="25.88671875" customWidth="1"/>
+    <col min="21" max="21" width="60.77734375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1660,31 +1834,33 @@
         <v>8</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="O1" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="S1" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>163</v>
       </c>
@@ -1713,7 +1889,7 @@
         <v>65</v>
       </c>
       <c r="K2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>140</v>
@@ -1724,11 +1900,13 @@
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
-      <c r="S2" s="2" t="s">
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>165</v>
       </c>
@@ -1757,7 +1935,7 @@
         <v>66</v>
       </c>
       <c r="K3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L3" s="4" t="s">
         <v>140</v>
@@ -1768,11 +1946,13 @@
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
-      <c r="S3" s="2" t="s">
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>166</v>
       </c>
@@ -1815,11 +1995,13 @@
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
-      <c r="S4" s="2" t="s">
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>167</v>
       </c>
@@ -1827,7 +2009,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D5">
         <v>-54.49</v>
@@ -1836,13 +2018,13 @@
         <v>159.01</v>
       </c>
       <c r="F5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G5" t="s">
         <v>142</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J5" t="s">
         <v>68</v>
@@ -1859,11 +2041,13 @@
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
-      <c r="S5" s="2" t="s">
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>177</v>
       </c>
@@ -1871,7 +2055,7 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D6">
         <v>-53.1</v>
@@ -1880,13 +2064,13 @@
         <v>73.5</v>
       </c>
       <c r="F6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G6" t="s">
         <v>142</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J6" t="s">
         <v>69</v>
@@ -1903,11 +2087,13 @@
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
-      <c r="S6" s="2" t="s">
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>180</v>
       </c>
@@ -1915,7 +2101,7 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D7">
         <v>-46.88</v>
@@ -1924,13 +2110,13 @@
         <v>37.86</v>
       </c>
       <c r="F7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G7" t="s">
         <v>139</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J7" t="s">
         <v>70</v>
@@ -1947,11 +2133,13 @@
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
-      <c r="S7" s="2" t="s">
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>178</v>
       </c>
@@ -1959,7 +2147,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D8">
         <v>-60.716999999999999</v>
@@ -1968,13 +2156,13 @@
         <v>-45.6</v>
       </c>
       <c r="F8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G8" t="s">
         <v>142</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J8" t="s">
         <v>71</v>
@@ -1991,13 +2179,15 @@
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
-      <c r="S8" s="2" t="s">
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>372</v>
+        <v>433</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
@@ -2035,11 +2225,13 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
-      <c r="S9" s="2" t="s">
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>179</v>
       </c>
@@ -2079,11 +2271,13 @@
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
-      <c r="S10" s="2" t="s">
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>181</v>
       </c>
@@ -2106,7 +2300,7 @@
         <v>139</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J11" t="s">
         <v>73</v>
@@ -2123,11 +2317,13 @@
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
-      <c r="S11" s="2" t="s">
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>182</v>
       </c>
@@ -2150,7 +2346,7 @@
         <v>142</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J12" t="s">
         <v>74</v>
@@ -2167,11 +2363,13 @@
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
-      <c r="S12" s="2" t="s">
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>183</v>
       </c>
@@ -2194,7 +2392,7 @@
         <v>142</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J13" t="s">
         <v>75</v>
@@ -2211,11 +2409,13 @@
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
-      <c r="S13" s="2" t="s">
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>184</v>
       </c>
@@ -2238,7 +2438,7 @@
         <v>142</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J14" t="s">
         <v>76</v>
@@ -2255,11 +2455,13 @@
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
-      <c r="S14" s="2" t="s">
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>168</v>
       </c>
@@ -2285,7 +2487,7 @@
         <v>62</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J15" t="s">
         <v>77</v>
@@ -2302,11 +2504,13 @@
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
-      <c r="S15" s="2" t="s">
+      <c r="S15" s="4"/>
+      <c r="T15" s="4"/>
+      <c r="U15" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>164</v>
       </c>
@@ -2329,7 +2533,7 @@
         <v>143</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J16" t="s">
         <v>78</v>
@@ -2346,11 +2550,13 @@
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
-      <c r="S16" s="2" t="s">
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>169</v>
       </c>
@@ -2369,20 +2575,17 @@
       <c r="F17" t="s">
         <v>60</v>
       </c>
-      <c r="G17" t="s">
-        <v>60</v>
-      </c>
       <c r="I17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J17" t="s">
         <v>79</v>
       </c>
       <c r="K17" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
@@ -2390,11 +2593,13 @@
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
-      <c r="S17" s="2" t="s">
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>170</v>
       </c>
@@ -2413,20 +2618,17 @@
       <c r="F18" t="s">
         <v>60</v>
       </c>
-      <c r="G18" t="s">
-        <v>60</v>
-      </c>
       <c r="I18" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J18" t="s">
         <v>79</v>
       </c>
       <c r="K18" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
@@ -2434,11 +2636,13 @@
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
-      <c r="S18" s="2" t="s">
+      <c r="S18" s="4"/>
+      <c r="T18" s="4"/>
+      <c r="U18" s="2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>171</v>
       </c>
@@ -2457,20 +2661,17 @@
       <c r="F19" t="s">
         <v>60</v>
       </c>
-      <c r="G19" t="s">
-        <v>60</v>
-      </c>
       <c r="I19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J19" t="s">
         <v>80</v>
       </c>
       <c r="K19" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M19" s="4"/>
       <c r="N19" s="4"/>
@@ -2478,11 +2679,13 @@
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
-      <c r="S19" s="2" t="s">
+      <c r="S19" s="4"/>
+      <c r="T19" s="4"/>
+      <c r="U19" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>172</v>
       </c>
@@ -2501,36 +2704,35 @@
       <c r="F20" t="s">
         <v>60</v>
       </c>
-      <c r="G20" t="s">
-        <v>60</v>
-      </c>
       <c r="I20" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J20" t="s">
         <v>81</v>
       </c>
       <c r="K20" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L20" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="N20" s="4" t="s">
         <v>228</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="N20" s="4" t="s">
-        <v>229</v>
       </c>
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
-      <c r="S20" s="2" t="s">
+      <c r="S20" s="4"/>
+      <c r="T20" s="4"/>
+      <c r="U20" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>173</v>
       </c>
@@ -2549,36 +2751,35 @@
       <c r="F21" t="s">
         <v>60</v>
       </c>
-      <c r="G21" t="s">
-        <v>60</v>
-      </c>
       <c r="I21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J21" t="s">
         <v>82</v>
       </c>
       <c r="K21" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L21" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="N21" s="4" t="s">
         <v>228</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="N21" s="4" t="s">
-        <v>229</v>
       </c>
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
-      <c r="S21" s="2" t="s">
+      <c r="S21" s="4"/>
+      <c r="T21" s="4"/>
+      <c r="U21" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>174</v>
       </c>
@@ -2597,36 +2798,39 @@
       <c r="F22" t="s">
         <v>60</v>
       </c>
-      <c r="G22" t="s">
-        <v>60</v>
-      </c>
       <c r="I22" t="s">
-        <v>243</v>
-      </c>
-      <c r="J22" t="s">
-        <v>81</v>
-      </c>
-      <c r="K22" t="s">
-        <v>223</v>
+        <v>242</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>425</v>
       </c>
       <c r="L22" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="N22" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="M22" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="N22" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="4"/>
-      <c r="S22" s="2" t="s">
+      <c r="O22" t="s">
+        <v>379</v>
+      </c>
+      <c r="P22" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>381</v>
+      </c>
+      <c r="R22" t="s">
+        <v>382</v>
+      </c>
+      <c r="T22" s="4"/>
+      <c r="U22" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" ht="30.15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>175</v>
       </c>
@@ -2645,44 +2849,43 @@
       <c r="F23" t="s">
         <v>60</v>
       </c>
-      <c r="G23" t="s">
-        <v>60</v>
-      </c>
       <c r="I23" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J23" t="s">
         <v>82</v>
       </c>
       <c r="K23" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L23" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="N23" s="4" t="s">
         <v>228</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="N23" s="4" t="s">
-        <v>229</v>
       </c>
       <c r="O23" s="4"/>
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
       <c r="R23" s="4"/>
-      <c r="S23" s="2" t="s">
+      <c r="S23" s="4"/>
+      <c r="T23" s="4"/>
+      <c r="U23" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s">
+        <v>229</v>
+      </c>
+      <c r="C24" t="s">
         <v>230</v>
-      </c>
-      <c r="C24" t="s">
-        <v>231</v>
       </c>
       <c r="D24">
         <v>69.38</v>
@@ -2693,20 +2896,17 @@
       <c r="F24" t="s">
         <v>60</v>
       </c>
-      <c r="G24" t="s">
-        <v>60</v>
-      </c>
       <c r="I24" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J24" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K24" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
@@ -2714,8 +2914,10 @@
       <c r="P24" s="4"/>
       <c r="Q24" s="4"/>
       <c r="R24" s="4"/>
-    </row>
-    <row r="25" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="S24" s="4"/>
+      <c r="T24" s="4"/>
+    </row>
+    <row r="25" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>185</v>
       </c>
@@ -2734,39 +2936,38 @@
       <c r="F25" t="s">
         <v>61</v>
       </c>
-      <c r="G25" t="s">
-        <v>61</v>
-      </c>
       <c r="H25" t="s">
         <v>62</v>
       </c>
       <c r="I25" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J25" t="s">
         <v>81</v>
       </c>
       <c r="K25" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L25" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="N25" s="4" t="s">
         <v>228</v>
-      </c>
-      <c r="M25" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="N25" s="4" t="s">
-        <v>229</v>
       </c>
       <c r="O25" s="4"/>
       <c r="P25" s="4"/>
       <c r="Q25" s="4"/>
       <c r="R25" s="4"/>
-      <c r="S25" s="2" t="s">
+      <c r="S25" s="4"/>
+      <c r="T25" s="4"/>
+      <c r="U25" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>186</v>
       </c>
@@ -2785,39 +2986,38 @@
       <c r="F26" t="s">
         <v>61</v>
       </c>
-      <c r="G26" t="s">
-        <v>61</v>
-      </c>
       <c r="H26" t="s">
         <v>62</v>
       </c>
       <c r="I26" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J26" t="s">
         <v>81</v>
       </c>
       <c r="K26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L26" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="N26" s="4" t="s">
         <v>228</v>
-      </c>
-      <c r="M26" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="N26" s="4" t="s">
-        <v>229</v>
       </c>
       <c r="O26" s="4"/>
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
-      <c r="S26" s="2" t="s">
+      <c r="S26" s="4"/>
+      <c r="T26" s="4"/>
+      <c r="U26" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>187</v>
       </c>
@@ -2825,7 +3025,7 @@
         <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D27">
         <v>69.56</v>
@@ -2836,39 +3036,38 @@
       <c r="F27" t="s">
         <v>61</v>
       </c>
-      <c r="G27" t="s">
-        <v>61</v>
-      </c>
       <c r="H27" t="s">
         <v>62</v>
       </c>
       <c r="I27" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J27" t="s">
         <v>81</v>
       </c>
       <c r="K27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L27" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="N27" s="4" t="s">
         <v>228</v>
-      </c>
-      <c r="M27" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="N27" s="4" t="s">
-        <v>229</v>
       </c>
       <c r="O27" s="4"/>
       <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
       <c r="R27" s="4"/>
-      <c r="S27" s="2" t="s">
+      <c r="S27" s="4"/>
+      <c r="T27" s="4"/>
+      <c r="U27" s="2" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="66.3" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" ht="66.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>188</v>
       </c>
@@ -2887,37 +3086,36 @@
       <c r="F28" t="s">
         <v>61</v>
       </c>
-      <c r="G28" t="s">
-        <v>61</v>
-      </c>
       <c r="H28" t="s">
         <v>62</v>
       </c>
       <c r="I28" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L28" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N28" s="4"/>
       <c r="O28" s="4"/>
       <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
       <c r="R28" s="4"/>
-      <c r="S28" s="2" t="s">
+      <c r="S28" s="4"/>
+      <c r="T28" s="4"/>
+      <c r="U28" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>189</v>
       </c>
@@ -2936,37 +3134,36 @@
       <c r="F29" t="s">
         <v>61</v>
       </c>
-      <c r="G29" t="s">
-        <v>61</v>
-      </c>
       <c r="H29" t="s">
         <v>62</v>
       </c>
       <c r="I29" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L29" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N29" s="4"/>
       <c r="O29" s="4"/>
       <c r="P29" s="4"/>
       <c r="Q29" s="4"/>
       <c r="R29" s="4"/>
-      <c r="S29" s="2" t="s">
+      <c r="S29" s="4"/>
+      <c r="T29" s="4"/>
+      <c r="U29" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>190</v>
       </c>
@@ -2985,37 +3182,36 @@
       <c r="F30" t="s">
         <v>61</v>
       </c>
-      <c r="G30" t="s">
-        <v>61</v>
-      </c>
       <c r="H30" t="s">
         <v>62</v>
       </c>
       <c r="I30" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L30" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N30" s="4"/>
       <c r="O30" s="4"/>
       <c r="P30" s="4"/>
       <c r="Q30" s="4"/>
       <c r="R30" s="4"/>
-      <c r="S30" s="2" t="s">
+      <c r="S30" s="4"/>
+      <c r="T30" s="4"/>
+      <c r="U30" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>191</v>
       </c>
@@ -3034,20 +3230,17 @@
       <c r="F31" t="s">
         <v>61</v>
       </c>
-      <c r="G31" t="s">
-        <v>61</v>
-      </c>
       <c r="H31" t="s">
         <v>62</v>
       </c>
       <c r="I31" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J31" t="s">
         <v>83</v>
       </c>
       <c r="K31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L31" s="4" t="s">
         <v>140</v>
@@ -3058,11 +3251,13 @@
       <c r="P31" s="4"/>
       <c r="Q31" s="4"/>
       <c r="R31" s="4"/>
-      <c r="S31" s="2" t="s">
+      <c r="S31" s="4"/>
+      <c r="T31" s="4"/>
+      <c r="U31" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>192</v>
       </c>
@@ -3081,37 +3276,36 @@
       <c r="F32" t="s">
         <v>61</v>
       </c>
-      <c r="G32" t="s">
-        <v>61</v>
-      </c>
       <c r="H32" t="s">
         <v>62</v>
       </c>
       <c r="I32" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L32" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N32" s="4"/>
       <c r="O32" s="4"/>
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
       <c r="R32" s="4"/>
-      <c r="S32" s="2" t="s">
+      <c r="S32" s="4"/>
+      <c r="T32" s="4"/>
+      <c r="U32" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>193</v>
       </c>
@@ -3130,37 +3324,36 @@
       <c r="F33" t="s">
         <v>61</v>
       </c>
-      <c r="G33" t="s">
-        <v>61</v>
-      </c>
       <c r="H33" t="s">
         <v>62</v>
       </c>
       <c r="I33" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L33" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N33" s="4"/>
       <c r="O33" s="4"/>
       <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
       <c r="R33" s="4"/>
-      <c r="S33" s="2" t="s">
+      <c r="S33" s="4"/>
+      <c r="T33" s="4"/>
+      <c r="U33" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>194</v>
       </c>
@@ -3179,37 +3372,36 @@
       <c r="F34" t="s">
         <v>61</v>
       </c>
-      <c r="G34" t="s">
-        <v>61</v>
-      </c>
       <c r="H34" t="s">
         <v>62</v>
       </c>
       <c r="I34" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L34" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M34" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N34" s="4"/>
       <c r="O34" s="4"/>
       <c r="P34" s="4"/>
       <c r="Q34" s="4"/>
       <c r="R34" s="4"/>
-      <c r="S34" s="2" t="s">
+      <c r="S34" s="4"/>
+      <c r="T34" s="4"/>
+      <c r="U34" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:21" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>195</v>
       </c>
@@ -3228,37 +3420,36 @@
       <c r="F35" t="s">
         <v>61</v>
       </c>
-      <c r="G35" t="s">
-        <v>61</v>
-      </c>
       <c r="H35" t="s">
         <v>62</v>
       </c>
       <c r="I35" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L35" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M35" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N35" s="4"/>
       <c r="O35" s="4"/>
       <c r="P35" s="4"/>
       <c r="Q35" s="4"/>
       <c r="R35" s="4"/>
-      <c r="S35" s="2" t="s">
+      <c r="S35" s="4"/>
+      <c r="T35" s="4"/>
+      <c r="U35" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>196</v>
       </c>
@@ -3277,37 +3468,36 @@
       <c r="F36" t="s">
         <v>61</v>
       </c>
-      <c r="G36" t="s">
-        <v>61</v>
-      </c>
       <c r="H36" t="s">
         <v>62</v>
       </c>
       <c r="I36" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L36" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
       <c r="P36" s="4"/>
       <c r="Q36" s="4"/>
       <c r="R36" s="4"/>
-      <c r="S36" s="2" t="s">
+      <c r="S36" s="4"/>
+      <c r="T36" s="4"/>
+      <c r="U36" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>197</v>
       </c>
@@ -3326,37 +3516,36 @@
       <c r="F37" t="s">
         <v>61</v>
       </c>
-      <c r="G37" t="s">
-        <v>61</v>
-      </c>
       <c r="H37" t="s">
         <v>62</v>
       </c>
       <c r="I37" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L37" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
       <c r="P37" s="4"/>
       <c r="Q37" s="4"/>
       <c r="R37" s="4"/>
-      <c r="S37" s="2" t="s">
+      <c r="S37" s="4"/>
+      <c r="T37" s="4"/>
+      <c r="U37" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>198</v>
       </c>
@@ -3375,37 +3564,36 @@
       <c r="F38" t="s">
         <v>61</v>
       </c>
-      <c r="G38" t="s">
-        <v>61</v>
-      </c>
       <c r="H38" t="s">
         <v>62</v>
       </c>
       <c r="I38" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L38" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M38" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N38" s="4"/>
       <c r="O38" s="4"/>
       <c r="P38" s="4"/>
       <c r="Q38" s="4"/>
       <c r="R38" s="4"/>
-      <c r="S38" s="2" t="s">
+      <c r="S38" s="4"/>
+      <c r="T38" s="4"/>
+      <c r="U38" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>199</v>
       </c>
@@ -3424,37 +3612,36 @@
       <c r="F39" t="s">
         <v>61</v>
       </c>
-      <c r="G39" t="s">
-        <v>61</v>
-      </c>
       <c r="H39" t="s">
         <v>62</v>
       </c>
       <c r="I39" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L39" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M39" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N39" s="4"/>
       <c r="O39" s="4"/>
       <c r="P39" s="4"/>
       <c r="Q39" s="4"/>
       <c r="R39" s="4"/>
-      <c r="S39" s="2" t="s">
+      <c r="S39" s="4"/>
+      <c r="T39" s="4"/>
+      <c r="U39" s="2" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:21" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>200</v>
       </c>
@@ -3473,9 +3660,6 @@
       <c r="F40" t="s">
         <v>61</v>
       </c>
-      <c r="G40" t="s">
-        <v>61</v>
-      </c>
       <c r="H40" t="s">
         <v>62</v>
       </c>
@@ -3486,24 +3670,26 @@
         <v>83</v>
       </c>
       <c r="K40" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L40" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M40" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
       <c r="P40" s="4"/>
       <c r="Q40" s="4"/>
       <c r="R40" s="4"/>
-      <c r="S40" s="2" t="s">
+      <c r="S40" s="4"/>
+      <c r="T40" s="4"/>
+      <c r="U40" s="2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:21" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>201</v>
       </c>
@@ -3522,9 +3708,6 @@
       <c r="F41" t="s">
         <v>61</v>
       </c>
-      <c r="G41" t="s">
-        <v>61</v>
-      </c>
       <c r="H41" t="s">
         <v>62</v>
       </c>
@@ -3532,27 +3715,29 @@
         <v>63</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L41" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M41" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N41" s="4"/>
       <c r="O41" s="4"/>
       <c r="P41" s="4"/>
       <c r="Q41" s="4"/>
       <c r="R41" s="4"/>
-      <c r="S41" s="2" t="s">
+      <c r="S41" s="4"/>
+      <c r="T41" s="4"/>
+      <c r="U41" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:21" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>202</v>
       </c>
@@ -3571,9 +3756,6 @@
       <c r="F42" t="s">
         <v>61</v>
       </c>
-      <c r="G42" t="s">
-        <v>61</v>
-      </c>
       <c r="H42" t="s">
         <v>62</v>
       </c>
@@ -3581,27 +3763,29 @@
         <v>63</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L42" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M42" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
       <c r="P42" s="4"/>
       <c r="Q42" s="4"/>
       <c r="R42" s="4"/>
-      <c r="S42" s="2" t="s">
+      <c r="S42" s="4"/>
+      <c r="T42" s="4"/>
+      <c r="U42" s="2" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:21" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>203</v>
       </c>
@@ -3620,9 +3804,6 @@
       <c r="F43" t="s">
         <v>61</v>
       </c>
-      <c r="G43" t="s">
-        <v>61</v>
-      </c>
       <c r="H43" t="s">
         <v>62</v>
       </c>
@@ -3630,27 +3811,29 @@
         <v>63</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L43" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
       <c r="P43" s="4"/>
       <c r="Q43" s="4"/>
       <c r="R43" s="4"/>
-      <c r="S43" s="2" t="s">
+      <c r="S43" s="4"/>
+      <c r="T43" s="4"/>
+      <c r="U43" s="2" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:21" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>204</v>
       </c>
@@ -3669,9 +3852,6 @@
       <c r="F44" t="s">
         <v>61</v>
       </c>
-      <c r="G44" t="s">
-        <v>61</v>
-      </c>
       <c r="H44" t="s">
         <v>62</v>
       </c>
@@ -3679,27 +3859,29 @@
         <v>63</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L44" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
       <c r="P44" s="4"/>
       <c r="Q44" s="4"/>
       <c r="R44" s="4"/>
-      <c r="S44" s="2" t="s">
+      <c r="S44" s="4"/>
+      <c r="T44" s="4"/>
+      <c r="U44" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:21" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>205</v>
       </c>
@@ -3718,9 +3900,6 @@
       <c r="F45" t="s">
         <v>61</v>
       </c>
-      <c r="G45" t="s">
-        <v>61</v>
-      </c>
       <c r="H45" t="s">
         <v>62</v>
       </c>
@@ -3728,27 +3907,29 @@
         <v>63</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L45" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N45" s="4"/>
       <c r="O45" s="4"/>
       <c r="P45" s="4"/>
       <c r="Q45" s="4"/>
       <c r="R45" s="4"/>
-      <c r="S45" s="2" t="s">
+      <c r="S45" s="4"/>
+      <c r="T45" s="4"/>
+      <c r="U45" s="2" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:21" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>206</v>
       </c>
@@ -3767,9 +3948,6 @@
       <c r="F46" t="s">
         <v>61</v>
       </c>
-      <c r="G46" t="s">
-        <v>61</v>
-      </c>
       <c r="H46" t="s">
         <v>62</v>
       </c>
@@ -3777,27 +3955,29 @@
         <v>63</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L46" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N46" s="4"/>
       <c r="O46" s="4"/>
       <c r="P46" s="4"/>
       <c r="Q46" s="4"/>
       <c r="R46" s="4"/>
-      <c r="S46" s="2" t="s">
+      <c r="S46" s="4"/>
+      <c r="T46" s="4"/>
+      <c r="U46" s="2" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="47" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:21" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>207</v>
       </c>
@@ -3816,9 +3996,6 @@
       <c r="F47" t="s">
         <v>61</v>
       </c>
-      <c r="G47" t="s">
-        <v>61</v>
-      </c>
       <c r="H47" t="s">
         <v>62</v>
       </c>
@@ -3826,27 +4003,29 @@
         <v>63</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L47" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N47" s="4"/>
       <c r="O47" s="4"/>
       <c r="P47" s="4"/>
       <c r="Q47" s="4"/>
       <c r="R47" s="4"/>
-      <c r="S47" s="2" t="s">
+      <c r="S47" s="4"/>
+      <c r="T47" s="4"/>
+      <c r="U47" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:21" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>208</v>
       </c>
@@ -3865,9 +4044,6 @@
       <c r="F48" t="s">
         <v>61</v>
       </c>
-      <c r="G48" t="s">
-        <v>61</v>
-      </c>
       <c r="H48" t="s">
         <v>62</v>
       </c>
@@ -3875,27 +4051,29 @@
         <v>63</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L48" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
       <c r="P48" s="4"/>
       <c r="Q48" s="4"/>
       <c r="R48" s="4"/>
-      <c r="S48" s="2" t="s">
+      <c r="S48" s="4"/>
+      <c r="T48" s="4"/>
+      <c r="U48" s="2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="49" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:21" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>209</v>
       </c>
@@ -3914,9 +4092,6 @@
       <c r="F49" t="s">
         <v>61</v>
       </c>
-      <c r="G49" t="s">
-        <v>61</v>
-      </c>
       <c r="H49" t="s">
         <v>62</v>
       </c>
@@ -3924,27 +4099,29 @@
         <v>63</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L49" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N49" s="4"/>
       <c r="O49" s="4"/>
       <c r="P49" s="4"/>
       <c r="Q49" s="4"/>
       <c r="R49" s="4"/>
-      <c r="S49" s="2" t="s">
+      <c r="S49" s="4"/>
+      <c r="T49" s="4"/>
+      <c r="U49" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:21" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>210</v>
       </c>
@@ -3963,9 +4140,6 @@
       <c r="F50" t="s">
         <v>61</v>
       </c>
-      <c r="G50" t="s">
-        <v>61</v>
-      </c>
       <c r="H50" t="s">
         <v>62</v>
       </c>
@@ -3973,27 +4147,29 @@
         <v>63</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L50" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
       <c r="P50" s="4"/>
       <c r="Q50" s="4"/>
       <c r="R50" s="4"/>
-      <c r="S50" s="2" t="s">
+      <c r="S50" s="4"/>
+      <c r="T50" s="4"/>
+      <c r="U50" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="51" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:21" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>211</v>
       </c>
@@ -4012,9 +4188,6 @@
       <c r="F51" t="s">
         <v>61</v>
       </c>
-      <c r="G51" t="s">
-        <v>61</v>
-      </c>
       <c r="H51" t="s">
         <v>62</v>
       </c>
@@ -4022,27 +4195,29 @@
         <v>63</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L51" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M51" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N51" s="4"/>
       <c r="O51" s="4"/>
       <c r="P51" s="4"/>
       <c r="Q51" s="4"/>
       <c r="R51" s="4"/>
-      <c r="S51" s="2" t="s">
+      <c r="S51" s="4"/>
+      <c r="T51" s="4"/>
+      <c r="U51" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:21" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>212</v>
       </c>
@@ -4061,9 +4236,6 @@
       <c r="F52" t="s">
         <v>61</v>
       </c>
-      <c r="G52" t="s">
-        <v>61</v>
-      </c>
       <c r="H52" t="s">
         <v>62</v>
       </c>
@@ -4071,27 +4243,29 @@
         <v>64</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L52" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M52" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
       <c r="P52" s="4"/>
       <c r="Q52" s="4"/>
       <c r="R52" s="4"/>
-      <c r="S52" s="2" t="s">
+      <c r="S52" s="4"/>
+      <c r="T52" s="4"/>
+      <c r="U52" s="2" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="53" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:21" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>213</v>
       </c>
@@ -4110,9 +4284,6 @@
       <c r="F53" t="s">
         <v>61</v>
       </c>
-      <c r="G53" t="s">
-        <v>61</v>
-      </c>
       <c r="H53" t="s">
         <v>62</v>
       </c>
@@ -4120,27 +4291,29 @@
         <v>63</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L53" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M53" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N53" s="4"/>
       <c r="O53" s="4"/>
       <c r="P53" s="4"/>
       <c r="Q53" s="4"/>
       <c r="R53" s="4"/>
-      <c r="S53" s="2" t="s">
+      <c r="S53" s="4"/>
+      <c r="T53" s="4"/>
+      <c r="U53" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:21" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>214</v>
       </c>
@@ -4159,9 +4332,6 @@
       <c r="F54" t="s">
         <v>61</v>
       </c>
-      <c r="G54" t="s">
-        <v>61</v>
-      </c>
       <c r="H54" t="s">
         <v>62</v>
       </c>
@@ -4169,31 +4339,33 @@
         <v>64</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L54" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M54" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="N54" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P54" s="4"/>
       <c r="Q54" s="4"/>
       <c r="R54" s="4"/>
-      <c r="S54" s="2" t="s">
+      <c r="S54" s="4"/>
+      <c r="T54" s="4"/>
+      <c r="U54" s="2" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="55" spans="1:19" ht="60.25" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:21" ht="60.25" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>215</v>
       </c>
@@ -4212,9 +4384,6 @@
       <c r="F55" t="s">
         <v>61</v>
       </c>
-      <c r="G55" t="s">
-        <v>61</v>
-      </c>
       <c r="H55" t="s">
         <v>62</v>
       </c>
@@ -4222,29 +4391,31 @@
         <v>63</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L55" s="4" t="s">
         <v>140</v>
       </c>
       <c r="M55" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N55" s="4"/>
       <c r="O55" s="4"/>
       <c r="P55" s="4"/>
       <c r="Q55" s="4"/>
       <c r="R55" s="4"/>
-      <c r="S55" s="2" t="s">
+      <c r="S55" s="4"/>
+      <c r="T55" s="4"/>
+      <c r="U55" s="2" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="56" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B56" t="s">
         <v>216</v>
@@ -4261,43 +4432,50 @@
       <c r="F56" t="s">
         <v>60</v>
       </c>
-      <c r="G56" t="s">
-        <v>60</v>
-      </c>
       <c r="I56" t="s">
         <v>64</v>
       </c>
-      <c r="J56" t="s">
+      <c r="J56" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="L56" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="K56" t="s">
-        <v>225</v>
-      </c>
-      <c r="L56" s="6" t="s">
+      <c r="M56" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="N56" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="O56" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="P56" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>379</v>
+      </c>
+      <c r="R56" t="s">
+        <v>380</v>
+      </c>
+      <c r="S56" t="s">
+        <v>381</v>
+      </c>
+      <c r="T56" t="s">
+        <v>382</v>
+      </c>
+      <c r="U56"/>
+    </row>
+    <row r="57" spans="1:21" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>233</v>
+      </c>
+      <c r="B57" t="s">
         <v>218</v>
-      </c>
-      <c r="M56" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="N56" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="O56" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="P56" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="Q56" s="6"/>
-      <c r="R56" s="6"/>
-      <c r="S56"/>
-    </row>
-    <row r="57" spans="1:19" ht="30.15" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>234</v>
-      </c>
-      <c r="B57" t="s">
-        <v>219</v>
       </c>
       <c r="C57" t="s">
         <v>156</v>
@@ -4309,48 +4487,55 @@
         <v>14.45</v>
       </c>
       <c r="F57" t="s">
+        <v>219</v>
+      </c>
+      <c r="H57" t="s">
         <v>220</v>
       </c>
-      <c r="G57" t="s">
-        <v>220</v>
-      </c>
-      <c r="H57" t="s">
+      <c r="I57" t="s">
         <v>221</v>
       </c>
-      <c r="I57" t="s">
-        <v>222</v>
-      </c>
-      <c r="J57" t="s">
+      <c r="J57" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="L57" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="K57" t="s">
-        <v>225</v>
-      </c>
-      <c r="L57" s="6" t="s">
-        <v>218</v>
-      </c>
       <c r="M57" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="N57" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="N57" s="7" t="s">
+      <c r="O57" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="O57" s="7" t="s">
+      <c r="P57" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="P57" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="Q57" s="6"/>
-      <c r="R57" s="6"/>
-      <c r="S57"/>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="Q57" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="R57" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="S57" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="T57" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="U57"/>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>215</v>
       </c>
       <c r="B58" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C58" t="s">
         <v>156</v>
@@ -4364,9 +4549,6 @@
       <c r="F58" t="s">
         <v>61</v>
       </c>
-      <c r="G58" t="s">
-        <v>61</v>
-      </c>
       <c r="H58" t="s">
         <v>62</v>
       </c>
@@ -4374,22 +4556,22 @@
         <v>63</v>
       </c>
       <c r="J58" t="s">
+        <v>245</v>
+      </c>
+      <c r="K58" t="s">
+        <v>258</v>
+      </c>
+      <c r="L58" t="s">
+        <v>259</v>
+      </c>
+      <c r="U58"/>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>252</v>
+      </c>
+      <c r="B59" t="s">
         <v>246</v>
-      </c>
-      <c r="K58" t="s">
-        <v>259</v>
-      </c>
-      <c r="L58" t="s">
-        <v>260</v>
-      </c>
-      <c r="S58"/>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>253</v>
-      </c>
-      <c r="B59" t="s">
-        <v>247</v>
       </c>
       <c r="C59" t="s">
         <v>148</v>
@@ -4403,32 +4585,29 @@
       <c r="F59" t="s">
         <v>61</v>
       </c>
-      <c r="G59" t="s">
-        <v>61</v>
-      </c>
       <c r="H59" t="s">
         <v>62</v>
       </c>
       <c r="I59" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J59" t="s">
+        <v>247</v>
+      </c>
+      <c r="K59" t="s">
+        <v>258</v>
+      </c>
+      <c r="L59" t="s">
+        <v>259</v>
+      </c>
+      <c r="U59"/>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>253</v>
+      </c>
+      <c r="B60" t="s">
         <v>248</v>
-      </c>
-      <c r="K59" t="s">
-        <v>259</v>
-      </c>
-      <c r="L59" t="s">
-        <v>260</v>
-      </c>
-      <c r="S59"/>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>254</v>
-      </c>
-      <c r="B60" t="s">
-        <v>249</v>
       </c>
       <c r="C60" t="s">
         <v>157</v>
@@ -4442,9 +4621,6 @@
       <c r="F60" t="s">
         <v>61</v>
       </c>
-      <c r="G60" t="s">
-        <v>61</v>
-      </c>
       <c r="H60" t="s">
         <v>62</v>
       </c>
@@ -4452,22 +4628,22 @@
         <v>63</v>
       </c>
       <c r="J60" t="s">
-        <v>246</v>
+        <v>420</v>
       </c>
       <c r="K60" t="s">
+        <v>258</v>
+      </c>
+      <c r="L60" t="s">
         <v>259</v>
       </c>
-      <c r="L60" t="s">
-        <v>260</v>
-      </c>
-      <c r="S60"/>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="U60"/>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B61" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C61" t="s">
         <v>156</v>
@@ -4481,44 +4657,44 @@
       <c r="F61" t="s">
         <v>61</v>
       </c>
-      <c r="G61" t="s">
-        <v>61</v>
-      </c>
       <c r="H61" t="s">
         <v>62</v>
       </c>
       <c r="I61" t="s">
+        <v>257</v>
+      </c>
+      <c r="J61" t="s">
+        <v>247</v>
+      </c>
+      <c r="K61" t="s">
         <v>258</v>
       </c>
-      <c r="J61" t="s">
-        <v>248</v>
-      </c>
-      <c r="K61" t="s">
+      <c r="L61" t="s">
         <v>259</v>
       </c>
-      <c r="L61" t="s">
-        <v>260</v>
-      </c>
       <c r="M61" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="N61" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="N61" s="7" t="s">
+      <c r="O61" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="O61" s="7" t="s">
+      <c r="P61" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="P61" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="S61"/>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="Q61" t="s">
+        <v>379</v>
+      </c>
+      <c r="U61"/>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B62" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C62" t="s">
         <v>156</v>
@@ -4532,35 +4708,32 @@
       <c r="F62" t="s">
         <v>61</v>
       </c>
-      <c r="G62" t="s">
-        <v>61</v>
-      </c>
       <c r="H62" t="s">
         <v>62</v>
       </c>
       <c r="I62" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J62" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K62" t="s">
+        <v>258</v>
+      </c>
+      <c r="L62" t="s">
         <v>259</v>
       </c>
-      <c r="L62" t="s">
-        <v>260</v>
-      </c>
       <c r="M62" t="s">
-        <v>265</v>
-      </c>
-      <c r="S62"/>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
+        <v>264</v>
+      </c>
+      <c r="U62"/>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B63" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C63" t="s">
         <v>156</v>
@@ -4574,32 +4747,29 @@
       <c r="F63" t="s">
         <v>61</v>
       </c>
-      <c r="G63" t="s">
-        <v>61</v>
-      </c>
       <c r="H63" t="s">
         <v>62</v>
       </c>
       <c r="I63" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J63" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K63" t="s">
+        <v>258</v>
+      </c>
+      <c r="L63" t="s">
         <v>259</v>
       </c>
-      <c r="L63" t="s">
-        <v>260</v>
-      </c>
-      <c r="S63"/>
-    </row>
-    <row r="64" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="U63"/>
+    </row>
+    <row r="64" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B64" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C64" t="s">
         <v>156</v>
@@ -4611,10 +4781,7 @@
         <v>41.797699999999999</v>
       </c>
       <c r="F64" t="s">
-        <v>263</v>
-      </c>
-      <c r="G64" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H64" t="s">
         <v>62</v>
@@ -4623,24 +4790,24 @@
         <v>64</v>
       </c>
       <c r="J64" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K64" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L64" t="s">
-        <v>265</v>
-      </c>
-      <c r="S64" s="2" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="U64" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B65" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C65" t="s">
         <v>149</v>
@@ -4654,9 +4821,6 @@
       <c r="F65" t="s">
         <v>61</v>
       </c>
-      <c r="G65" t="s">
-        <v>61</v>
-      </c>
       <c r="H65" t="s">
         <v>62</v>
       </c>
@@ -4664,22 +4828,22 @@
         <v>63</v>
       </c>
       <c r="J65" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K65" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="S65"/>
-    </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
+        <v>271</v>
+      </c>
+      <c r="U65"/>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B66" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C66" t="s">
         <v>149</v>
@@ -4693,9 +4857,6 @@
       <c r="F66" t="s">
         <v>61</v>
       </c>
-      <c r="G66" t="s">
-        <v>61</v>
-      </c>
       <c r="H66" t="s">
         <v>62</v>
       </c>
@@ -4703,25 +4864,25 @@
         <v>63</v>
       </c>
       <c r="J66" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K66" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="S66"/>
-    </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
+        <v>271</v>
+      </c>
+      <c r="U66"/>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B67" t="s">
         <v>37</v>
       </c>
       <c r="C67" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D67">
         <v>68.252960000000002</v>
@@ -4732,35 +4893,32 @@
       <c r="F67" t="s">
         <v>61</v>
       </c>
-      <c r="G67" t="s">
-        <v>61</v>
-      </c>
       <c r="H67" t="s">
         <v>62</v>
       </c>
       <c r="I67" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J67" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K67" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="S67"/>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
+        <v>271</v>
+      </c>
+      <c r="U67"/>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B68" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C68" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D68">
         <v>44.407859000000002</v>
@@ -4771,35 +4929,32 @@
       <c r="F68" t="s">
         <v>61</v>
       </c>
-      <c r="G68" t="s">
-        <v>61</v>
-      </c>
       <c r="H68" t="s">
         <v>62</v>
       </c>
       <c r="I68" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J68" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K68" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="S68"/>
-    </row>
-    <row r="69" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+        <v>271</v>
+      </c>
+      <c r="U68"/>
+    </row>
+    <row r="69" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B69" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C69" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D69">
         <v>49.142899999999997</v>
@@ -4808,46 +4963,43 @@
         <v>13.556100000000001</v>
       </c>
       <c r="F69" t="s">
+        <v>219</v>
+      </c>
+      <c r="H69" t="s">
         <v>220</v>
       </c>
-      <c r="G69" t="s">
-        <v>220</v>
-      </c>
-      <c r="H69" t="s">
-        <v>221</v>
-      </c>
       <c r="I69" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J69" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K69" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="K69" s="2" t="s">
+      <c r="L69" t="s">
         <v>282</v>
       </c>
-      <c r="L69" t="s">
+      <c r="M69" t="s">
         <v>283</v>
       </c>
-      <c r="M69" t="s">
+      <c r="N69" t="s">
         <v>284</v>
       </c>
-      <c r="N69" t="s">
+      <c r="O69" t="s">
         <v>285</v>
       </c>
-      <c r="O69" t="s">
-        <v>286</v>
-      </c>
-      <c r="S69"/>
-    </row>
-    <row r="70" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="U69"/>
+    </row>
+    <row r="70" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B70" t="s">
+        <v>287</v>
+      </c>
+      <c r="C70" t="s">
         <v>288</v>
-      </c>
-      <c r="C70" t="s">
-        <v>289</v>
       </c>
       <c r="D70">
         <v>50.533000000000001</v>
@@ -4856,43 +5008,52 @@
         <v>13.616</v>
       </c>
       <c r="F70" t="s">
+        <v>219</v>
+      </c>
+      <c r="H70" t="s">
         <v>220</v>
       </c>
-      <c r="G70" t="s">
-        <v>220</v>
-      </c>
-      <c r="H70" t="s">
-        <v>221</v>
-      </c>
       <c r="I70" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J70" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K70" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="K70" s="2" t="s">
+      <c r="L70" t="s">
         <v>282</v>
       </c>
-      <c r="L70" t="s">
+      <c r="M70" t="s">
         <v>283</v>
       </c>
-      <c r="M70" t="s">
+      <c r="N70" t="s">
         <v>284</v>
       </c>
-      <c r="N70" t="s">
+      <c r="O70" t="s">
         <v>285</v>
       </c>
-      <c r="O70" t="s">
-        <v>286</v>
-      </c>
-      <c r="S70"/>
-    </row>
-    <row r="71" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="P70" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q70" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="R70" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="S70" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="U70"/>
+    </row>
+    <row r="71" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B71" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C71" t="s">
         <v>156</v>
@@ -4904,43 +5065,40 @@
         <v>24.655899999999999</v>
       </c>
       <c r="F71" t="s">
+        <v>290</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="L71" t="s">
+        <v>282</v>
+      </c>
+      <c r="M71" t="s">
+        <v>283</v>
+      </c>
+      <c r="N71" t="s">
+        <v>284</v>
+      </c>
+      <c r="O71" t="s">
+        <v>285</v>
+      </c>
+      <c r="U71"/>
+    </row>
+    <row r="72" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>346</v>
+      </c>
+      <c r="B72" t="s">
         <v>291</v>
       </c>
-      <c r="G71" t="s">
-        <v>291</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="J71" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="K71" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="L71" t="s">
-        <v>283</v>
-      </c>
-      <c r="M71" t="s">
-        <v>284</v>
-      </c>
-      <c r="N71" t="s">
-        <v>285</v>
-      </c>
-      <c r="O71" t="s">
-        <v>286</v>
-      </c>
-      <c r="S71"/>
-    </row>
-    <row r="72" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>347</v>
-      </c>
-      <c r="B72" t="s">
-        <v>292</v>
-      </c>
       <c r="C72" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D72">
         <v>62.554000000000002</v>
@@ -4949,40 +5107,40 @@
         <v>24.061900000000001</v>
       </c>
       <c r="F72" t="s">
-        <v>291</v>
-      </c>
-      <c r="G72" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J72" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K72" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="K72" s="2" t="s">
+      <c r="L72" t="s">
         <v>282</v>
       </c>
-      <c r="L72" t="s">
+      <c r="M72" t="s">
         <v>283</v>
       </c>
-      <c r="M72" t="s">
+      <c r="N72" t="s">
         <v>284</v>
       </c>
-      <c r="N72" t="s">
+      <c r="O72" t="s">
         <v>285</v>
       </c>
-      <c r="O72" t="s">
-        <v>286</v>
-      </c>
-      <c r="S72"/>
-    </row>
-    <row r="73" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="P72" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="U72"/>
+    </row>
+    <row r="73" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B73" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C73" t="s">
         <v>156</v>
@@ -4994,43 +5152,40 @@
         <v>24.954999999999998</v>
       </c>
       <c r="F73" t="s">
-        <v>291</v>
-      </c>
-      <c r="G73" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J73" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K73" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="K73" s="2" t="s">
+      <c r="L73" t="s">
         <v>282</v>
       </c>
-      <c r="L73" t="s">
+      <c r="M73" t="s">
         <v>283</v>
       </c>
-      <c r="M73" t="s">
+      <c r="N73" t="s">
         <v>284</v>
       </c>
-      <c r="N73" t="s">
+      <c r="O73" t="s">
         <v>285</v>
       </c>
-      <c r="O73" t="s">
-        <v>286</v>
-      </c>
-      <c r="S73"/>
-    </row>
-    <row r="74" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="U73"/>
+    </row>
+    <row r="74" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B74" t="s">
+        <v>293</v>
+      </c>
+      <c r="C74" t="s">
         <v>294</v>
-      </c>
-      <c r="C74" t="s">
-        <v>295</v>
       </c>
       <c r="D74">
         <v>52.800866999999997</v>
@@ -5039,40 +5194,40 @@
         <v>10.75623</v>
       </c>
       <c r="F74" t="s">
+        <v>295</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="L74" t="s">
+        <v>282</v>
+      </c>
+      <c r="M74" t="s">
+        <v>283</v>
+      </c>
+      <c r="N74" t="s">
+        <v>284</v>
+      </c>
+      <c r="O74" t="s">
+        <v>285</v>
+      </c>
+      <c r="P74" t="s">
+        <v>379</v>
+      </c>
+      <c r="U74"/>
+    </row>
+    <row r="75" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>349</v>
+      </c>
+      <c r="B75" t="s">
         <v>296</v>
-      </c>
-      <c r="G74" t="s">
-        <v>296</v>
-      </c>
-      <c r="I74" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="J74" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="K74" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="L74" t="s">
-        <v>283</v>
-      </c>
-      <c r="M74" t="s">
-        <v>284</v>
-      </c>
-      <c r="N74" t="s">
-        <v>285</v>
-      </c>
-      <c r="O74" t="s">
-        <v>286</v>
-      </c>
-      <c r="S74"/>
-    </row>
-    <row r="75" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>350</v>
-      </c>
-      <c r="B75" t="s">
-        <v>297</v>
       </c>
       <c r="C75" t="s">
         <v>156</v>
@@ -5084,43 +5239,40 @@
         <v>9.1521000000000008</v>
       </c>
       <c r="F75" t="s">
-        <v>296</v>
-      </c>
-      <c r="G75" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J75" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K75" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="K75" s="2" t="s">
+      <c r="L75" t="s">
         <v>282</v>
       </c>
-      <c r="L75" t="s">
+      <c r="M75" t="s">
         <v>283</v>
       </c>
-      <c r="M75" t="s">
+      <c r="N75" t="s">
         <v>284</v>
       </c>
-      <c r="N75" t="s">
+      <c r="O75" t="s">
         <v>285</v>
       </c>
-      <c r="O75" t="s">
-        <v>286</v>
-      </c>
-      <c r="S75"/>
-    </row>
-    <row r="76" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="U75"/>
+    </row>
+    <row r="76" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B76" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C76" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D76">
         <v>51.083863999999998</v>
@@ -5129,40 +5281,40 @@
         <v>6.9210539999999998</v>
       </c>
       <c r="F76" t="s">
-        <v>296</v>
-      </c>
-      <c r="G76" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J76" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K76" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="K76" s="2" t="s">
+      <c r="L76" t="s">
         <v>282</v>
       </c>
-      <c r="L76" t="s">
+      <c r="M76" t="s">
         <v>283</v>
       </c>
-      <c r="M76" t="s">
+      <c r="N76" t="s">
         <v>284</v>
       </c>
-      <c r="N76" t="s">
+      <c r="O76" t="s">
         <v>285</v>
       </c>
-      <c r="O76" t="s">
-        <v>286</v>
-      </c>
-      <c r="S76"/>
-    </row>
-    <row r="77" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="P76" t="s">
+        <v>379</v>
+      </c>
+      <c r="U76"/>
+    </row>
+    <row r="77" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B77" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C77" t="s">
         <v>156</v>
@@ -5174,40 +5326,49 @@
         <v>6.9284999999999997</v>
       </c>
       <c r="F77" t="s">
-        <v>296</v>
-      </c>
-      <c r="G77" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J77" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K77" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="K77" s="2" t="s">
+      <c r="L77" t="s">
         <v>282</v>
       </c>
-      <c r="L77" t="s">
+      <c r="M77" t="s">
         <v>283</v>
       </c>
-      <c r="M77" t="s">
+      <c r="N77" t="s">
         <v>284</v>
       </c>
-      <c r="N77" t="s">
+      <c r="O77" t="s">
         <v>285</v>
       </c>
-      <c r="O77" t="s">
-        <v>286</v>
-      </c>
-      <c r="S77"/>
-    </row>
-    <row r="78" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="P77" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q77" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="R77" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="S77" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="U77"/>
+    </row>
+    <row r="78" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B78" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C78" t="s">
         <v>156</v>
@@ -5219,43 +5380,40 @@
         <v>7.0810000000000004</v>
       </c>
       <c r="F78" t="s">
-        <v>296</v>
-      </c>
-      <c r="G78" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J78" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K78" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="K78" s="2" t="s">
+      <c r="L78" t="s">
         <v>282</v>
       </c>
-      <c r="L78" t="s">
+      <c r="M78" t="s">
         <v>283</v>
       </c>
-      <c r="M78" t="s">
+      <c r="N78" t="s">
         <v>284</v>
       </c>
-      <c r="N78" t="s">
+      <c r="O78" t="s">
         <v>285</v>
       </c>
-      <c r="O78" t="s">
-        <v>286</v>
-      </c>
-      <c r="S78"/>
-    </row>
-    <row r="79" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="U78"/>
+    </row>
+    <row r="79" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B79" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C79" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D79">
         <v>47.491999999999997</v>
@@ -5264,40 +5422,37 @@
         <v>11.095499999999999</v>
       </c>
       <c r="F79" t="s">
-        <v>296</v>
-      </c>
-      <c r="G79" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J79" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K79" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="K79" s="2" t="s">
+      <c r="L79" t="s">
         <v>282</v>
       </c>
-      <c r="L79" t="s">
+      <c r="M79" t="s">
         <v>283</v>
       </c>
-      <c r="M79" t="s">
+      <c r="N79" t="s">
         <v>284</v>
       </c>
-      <c r="N79" t="s">
+      <c r="O79" t="s">
         <v>285</v>
       </c>
-      <c r="O79" t="s">
-        <v>286</v>
-      </c>
-      <c r="S79"/>
-    </row>
-    <row r="80" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="U79"/>
+    </row>
+    <row r="80" spans="1:21" ht="75.3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B80" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C80" t="s">
         <v>156</v>
@@ -5309,43 +5464,52 @@
         <v>12.4964</v>
       </c>
       <c r="F80" t="s">
+        <v>301</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="L80" t="s">
+        <v>282</v>
+      </c>
+      <c r="M80" t="s">
+        <v>283</v>
+      </c>
+      <c r="N80" t="s">
+        <v>284</v>
+      </c>
+      <c r="O80" t="s">
+        <v>285</v>
+      </c>
+      <c r="P80" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q80" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="R80" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="S80" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="U80"/>
+    </row>
+    <row r="81" spans="1:21" ht="75.3" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>355</v>
+      </c>
+      <c r="B81" t="s">
         <v>302</v>
       </c>
-      <c r="G80" t="s">
-        <v>302</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="L80" t="s">
-        <v>283</v>
-      </c>
-      <c r="M80" t="s">
-        <v>284</v>
-      </c>
-      <c r="N80" t="s">
-        <v>285</v>
-      </c>
-      <c r="O80" t="s">
-        <v>286</v>
-      </c>
-      <c r="S80"/>
-    </row>
-    <row r="81" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>356</v>
-      </c>
-      <c r="B81" t="s">
-        <v>303</v>
-      </c>
       <c r="C81" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D81">
         <v>42.05</v>
@@ -5354,40 +5518,49 @@
         <v>12.3</v>
       </c>
       <c r="F81" t="s">
-        <v>302</v>
-      </c>
-      <c r="G81" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>281</v>
+        <v>418</v>
       </c>
       <c r="K81" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="L81" t="s">
         <v>282</v>
       </c>
-      <c r="L81" t="s">
+      <c r="M81" t="s">
         <v>283</v>
       </c>
-      <c r="M81" t="s">
+      <c r="N81" t="s">
         <v>284</v>
       </c>
-      <c r="N81" t="s">
+      <c r="O81" t="s">
         <v>285</v>
       </c>
-      <c r="O81" t="s">
-        <v>286</v>
-      </c>
-      <c r="S81"/>
-    </row>
-    <row r="82" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="P81" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q81" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="R81" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="S81" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="U81"/>
+    </row>
+    <row r="82" spans="1:21" ht="75.3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B82" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C82" t="s">
         <v>156</v>
@@ -5399,40 +5572,49 @@
         <v>9.19</v>
       </c>
       <c r="F82" t="s">
-        <v>302</v>
-      </c>
-      <c r="G82" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>281</v>
+        <v>418</v>
       </c>
       <c r="K82" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="L82" t="s">
         <v>282</v>
       </c>
-      <c r="L82" t="s">
+      <c r="M82" t="s">
         <v>283</v>
       </c>
-      <c r="M82" t="s">
+      <c r="N82" t="s">
         <v>284</v>
       </c>
-      <c r="N82" t="s">
+      <c r="O82" t="s">
         <v>285</v>
       </c>
-      <c r="O82" t="s">
-        <v>286</v>
-      </c>
-      <c r="S82"/>
-    </row>
-    <row r="83" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="P82" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q82" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="R82" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="S82" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="U82"/>
+    </row>
+    <row r="83" spans="1:21" ht="75.3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B83" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C83" t="s">
         <v>156</v>
@@ -5444,43 +5626,52 @@
         <v>12.3155</v>
       </c>
       <c r="F83" t="s">
-        <v>302</v>
-      </c>
-      <c r="G83" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>281</v>
+        <v>418</v>
       </c>
       <c r="K83" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="L83" t="s">
         <v>282</v>
       </c>
-      <c r="L83" t="s">
+      <c r="M83" t="s">
         <v>283</v>
       </c>
-      <c r="M83" t="s">
+      <c r="N83" t="s">
         <v>284</v>
       </c>
-      <c r="N83" t="s">
+      <c r="O83" t="s">
         <v>285</v>
       </c>
-      <c r="O83" t="s">
-        <v>286</v>
-      </c>
-      <c r="S83"/>
-    </row>
-    <row r="84" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="P83" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q83" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="R83" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="S83" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="U83"/>
+    </row>
+    <row r="84" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B84" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C84" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D84">
         <v>51.912500000000001</v>
@@ -5489,43 +5680,40 @@
         <v>4.3417000000000003</v>
       </c>
       <c r="F84" t="s">
+        <v>306</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="L84" t="s">
+        <v>282</v>
+      </c>
+      <c r="M84" t="s">
+        <v>283</v>
+      </c>
+      <c r="N84" t="s">
+        <v>284</v>
+      </c>
+      <c r="O84" t="s">
+        <v>285</v>
+      </c>
+      <c r="U84"/>
+    </row>
+    <row r="85" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>359</v>
+      </c>
+      <c r="B85" t="s">
         <v>307</v>
       </c>
-      <c r="G84" t="s">
-        <v>307</v>
-      </c>
-      <c r="I84" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="J84" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="K84" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="L84" t="s">
-        <v>283</v>
-      </c>
-      <c r="M84" t="s">
-        <v>284</v>
-      </c>
-      <c r="N84" t="s">
-        <v>285</v>
-      </c>
-      <c r="O84" t="s">
-        <v>286</v>
-      </c>
-      <c r="S84"/>
-    </row>
-    <row r="85" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>360</v>
-      </c>
-      <c r="B85" t="s">
-        <v>308</v>
-      </c>
       <c r="C85" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D85">
         <v>52.1</v>
@@ -5534,40 +5722,37 @@
         <v>6.6612</v>
       </c>
       <c r="F85" t="s">
-        <v>307</v>
-      </c>
-      <c r="G85" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J85" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K85" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="K85" s="2" t="s">
+      <c r="L85" t="s">
         <v>282</v>
       </c>
-      <c r="L85" t="s">
+      <c r="M85" t="s">
         <v>283</v>
       </c>
-      <c r="M85" t="s">
+      <c r="N85" t="s">
         <v>284</v>
       </c>
-      <c r="N85" t="s">
+      <c r="O85" t="s">
         <v>285</v>
       </c>
-      <c r="O85" t="s">
-        <v>286</v>
-      </c>
-      <c r="S85"/>
-    </row>
-    <row r="86" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="U85"/>
+    </row>
+    <row r="86" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B86" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C86" t="s">
         <v>157</v>
@@ -5579,40 +5764,37 @@
         <v>5.8678999999999997</v>
       </c>
       <c r="F86" t="s">
-        <v>307</v>
-      </c>
-      <c r="G86" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J86" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K86" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="K86" s="2" t="s">
+      <c r="L86" t="s">
         <v>282</v>
       </c>
-      <c r="L86" t="s">
+      <c r="M86" t="s">
         <v>283</v>
       </c>
-      <c r="M86" t="s">
+      <c r="N86" t="s">
         <v>284</v>
       </c>
-      <c r="N86" t="s">
+      <c r="O86" t="s">
         <v>285</v>
       </c>
-      <c r="O86" t="s">
-        <v>286</v>
-      </c>
-      <c r="S86"/>
-    </row>
-    <row r="87" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="U86"/>
+    </row>
+    <row r="87" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B87" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C87" t="s">
         <v>157</v>
@@ -5624,43 +5806,40 @@
         <v>5.8836000000000004</v>
       </c>
       <c r="F87" t="s">
-        <v>307</v>
-      </c>
-      <c r="G87" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J87" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K87" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="K87" s="2" t="s">
+      <c r="L87" t="s">
         <v>282</v>
       </c>
-      <c r="L87" t="s">
+      <c r="M87" t="s">
         <v>283</v>
       </c>
-      <c r="M87" t="s">
+      <c r="N87" t="s">
         <v>284</v>
       </c>
-      <c r="N87" t="s">
+      <c r="O87" t="s">
         <v>285</v>
       </c>
-      <c r="O87" t="s">
-        <v>286</v>
-      </c>
-      <c r="S87"/>
-    </row>
-    <row r="88" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="U87"/>
+    </row>
+    <row r="88" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B88" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C88" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D88">
         <v>59.276499999999999</v>
@@ -5671,41 +5850,38 @@
       <c r="F88" t="s">
         <v>60</v>
       </c>
-      <c r="G88" t="s">
-        <v>60</v>
-      </c>
       <c r="I88" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J88" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K88" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="K88" s="2" t="s">
+      <c r="L88" t="s">
         <v>282</v>
       </c>
-      <c r="L88" t="s">
+      <c r="M88" t="s">
         <v>283</v>
       </c>
-      <c r="M88" t="s">
+      <c r="N88" t="s">
         <v>284</v>
       </c>
-      <c r="N88" t="s">
+      <c r="O88" t="s">
         <v>285</v>
       </c>
-      <c r="O88" t="s">
-        <v>286</v>
-      </c>
-      <c r="S88"/>
-    </row>
-    <row r="89" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="U88"/>
+    </row>
+    <row r="89" spans="1:21" ht="75.3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B89" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C89" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D89">
         <v>58.383333</v>
@@ -5716,38 +5892,47 @@
       <c r="F89" t="s">
         <v>60</v>
       </c>
-      <c r="G89" t="s">
-        <v>60</v>
-      </c>
       <c r="I89" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>281</v>
+        <v>418</v>
       </c>
       <c r="K89" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="L89" t="s">
         <v>282</v>
       </c>
-      <c r="L89" t="s">
+      <c r="M89" t="s">
         <v>283</v>
       </c>
-      <c r="M89" t="s">
+      <c r="N89" t="s">
         <v>284</v>
       </c>
-      <c r="N89" t="s">
+      <c r="O89" t="s">
         <v>285</v>
       </c>
-      <c r="O89" t="s">
-        <v>286</v>
-      </c>
-      <c r="S89"/>
-    </row>
-    <row r="90" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="P89" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q89" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="R89" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="S89" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="U89"/>
+    </row>
+    <row r="90" spans="1:21" ht="75.3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B90" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C90" t="s">
         <v>156</v>
@@ -5759,40 +5944,49 @@
         <v>18.082999999999998</v>
       </c>
       <c r="F90" t="s">
+        <v>313</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="K90" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="L90" t="s">
+        <v>282</v>
+      </c>
+      <c r="M90" t="s">
+        <v>283</v>
+      </c>
+      <c r="N90" t="s">
+        <v>284</v>
+      </c>
+      <c r="O90" t="s">
+        <v>285</v>
+      </c>
+      <c r="P90" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q90" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="R90" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="S90" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="U90"/>
+    </row>
+    <row r="91" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>365</v>
+      </c>
+      <c r="B91" t="s">
         <v>314</v>
-      </c>
-      <c r="G90" t="s">
-        <v>314</v>
-      </c>
-      <c r="I90" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="J90" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="K90" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="L90" t="s">
-        <v>283</v>
-      </c>
-      <c r="M90" t="s">
-        <v>284</v>
-      </c>
-      <c r="N90" t="s">
-        <v>285</v>
-      </c>
-      <c r="O90" t="s">
-        <v>286</v>
-      </c>
-      <c r="S90"/>
-    </row>
-    <row r="91" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>366</v>
-      </c>
-      <c r="B91" t="s">
-        <v>315</v>
       </c>
       <c r="C91" t="s">
         <v>156</v>
@@ -5804,43 +5998,40 @@
         <v>18.0686</v>
       </c>
       <c r="F91" t="s">
-        <v>314</v>
-      </c>
-      <c r="G91" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J91" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K91" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="K91" s="2" t="s">
+      <c r="L91" t="s">
         <v>282</v>
       </c>
-      <c r="L91" t="s">
+      <c r="M91" t="s">
         <v>283</v>
       </c>
-      <c r="M91" t="s">
+      <c r="N91" t="s">
         <v>284</v>
       </c>
-      <c r="N91" t="s">
+      <c r="O91" t="s">
         <v>285</v>
       </c>
-      <c r="O91" t="s">
-        <v>286</v>
-      </c>
-      <c r="S91"/>
-    </row>
-    <row r="92" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="U91"/>
+    </row>
+    <row r="92" spans="1:21" ht="75.3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B92" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C92" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D92">
         <v>58.8</v>
@@ -5849,43 +6040,52 @@
         <v>17.383333</v>
       </c>
       <c r="F92" t="s">
-        <v>314</v>
-      </c>
-      <c r="G92" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>281</v>
+        <v>418</v>
       </c>
       <c r="K92" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="L92" t="s">
         <v>282</v>
       </c>
-      <c r="L92" t="s">
+      <c r="M92" t="s">
         <v>283</v>
       </c>
-      <c r="M92" t="s">
+      <c r="N92" t="s">
         <v>284</v>
       </c>
-      <c r="N92" t="s">
+      <c r="O92" t="s">
         <v>285</v>
       </c>
-      <c r="O92" t="s">
-        <v>286</v>
-      </c>
-      <c r="S92"/>
-    </row>
-    <row r="93" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="P92" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q92" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="R92" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="S92" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="U92"/>
+    </row>
+    <row r="93" spans="1:21" ht="75.3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>368</v>
+        <v>432</v>
       </c>
       <c r="B93" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C93" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D93">
         <v>53.234000000000002</v>
@@ -5896,41 +6096,48 @@
       <c r="F93" t="s">
         <v>144</v>
       </c>
-      <c r="G93" t="s">
-        <v>144</v>
-      </c>
       <c r="I93" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>281</v>
+        <v>421</v>
       </c>
       <c r="K93" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="L93" t="s">
         <v>282</v>
       </c>
-      <c r="L93" t="s">
+      <c r="M93" t="s">
         <v>283</v>
       </c>
-      <c r="M93" t="s">
+      <c r="N93" t="s">
         <v>284</v>
       </c>
-      <c r="N93" t="s">
+      <c r="O93" t="s">
         <v>285</v>
       </c>
-      <c r="O93" t="s">
-        <v>286</v>
-      </c>
-      <c r="S93"/>
-    </row>
-    <row r="94" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="P93" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q93" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="R93" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="S93" s="7"/>
+      <c r="U93"/>
+    </row>
+    <row r="94" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>369</v>
+        <v>431</v>
       </c>
       <c r="B94" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C94" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D94">
         <v>51.210700000000003</v>
@@ -5941,38 +6148,35 @@
       <c r="F94" t="s">
         <v>144</v>
       </c>
-      <c r="G94" t="s">
-        <v>144</v>
-      </c>
       <c r="I94" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J94" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K94" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="K94" s="2" t="s">
+      <c r="L94" t="s">
         <v>282</v>
       </c>
-      <c r="L94" t="s">
+      <c r="M94" t="s">
         <v>283</v>
       </c>
-      <c r="M94" t="s">
+      <c r="N94" t="s">
         <v>284</v>
       </c>
-      <c r="N94" t="s">
+      <c r="O94" t="s">
         <v>285</v>
       </c>
-      <c r="O94" t="s">
-        <v>286</v>
-      </c>
-      <c r="S94"/>
-    </row>
-    <row r="95" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="U94"/>
+    </row>
+    <row r="95" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>370</v>
+        <v>430</v>
       </c>
       <c r="B95" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C95" t="s">
         <v>154</v>
@@ -5986,38 +6190,35 @@
       <c r="F95" t="s">
         <v>144</v>
       </c>
-      <c r="G95" t="s">
-        <v>144</v>
-      </c>
       <c r="I95" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J95" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K95" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="K95" s="2" t="s">
+      <c r="L95" t="s">
         <v>282</v>
       </c>
-      <c r="L95" t="s">
+      <c r="M95" t="s">
         <v>283</v>
       </c>
-      <c r="M95" t="s">
+      <c r="N95" t="s">
         <v>284</v>
       </c>
-      <c r="N95" t="s">
+      <c r="O95" t="s">
         <v>285</v>
       </c>
-      <c r="O95" t="s">
-        <v>286</v>
-      </c>
-      <c r="S95"/>
-    </row>
-    <row r="96" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="U95"/>
+    </row>
+    <row r="96" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>371</v>
+        <v>429</v>
       </c>
       <c r="B96" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C96" t="s">
         <v>157</v>
@@ -6031,38 +6232,35 @@
       <c r="F96" t="s">
         <v>144</v>
       </c>
-      <c r="G96" t="s">
-        <v>144</v>
-      </c>
       <c r="I96" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J96" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K96" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="K96" s="2" t="s">
+      <c r="L96" t="s">
         <v>282</v>
       </c>
-      <c r="L96" t="s">
+      <c r="M96" t="s">
         <v>283</v>
       </c>
-      <c r="M96" t="s">
+      <c r="N96" t="s">
         <v>284</v>
       </c>
-      <c r="N96" t="s">
+      <c r="O96" t="s">
         <v>285</v>
       </c>
-      <c r="O96" t="s">
-        <v>286</v>
-      </c>
-      <c r="S96"/>
-    </row>
-    <row r="97" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="U96"/>
+    </row>
+    <row r="97" spans="1:21" ht="75.3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B97" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C97" t="s">
         <v>156</v>
@@ -6074,40 +6272,49 @@
         <v>-3.7038000000000002</v>
       </c>
       <c r="F97" t="s">
+        <v>321</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="K97" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="L97" t="s">
+        <v>282</v>
+      </c>
+      <c r="M97" t="s">
+        <v>283</v>
+      </c>
+      <c r="N97" t="s">
+        <v>284</v>
+      </c>
+      <c r="O97" t="s">
+        <v>285</v>
+      </c>
+      <c r="P97" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q97" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="R97" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="S97" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="U97"/>
+    </row>
+    <row r="98" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>368</v>
+      </c>
+      <c r="B98" t="s">
         <v>322</v>
-      </c>
-      <c r="G97" t="s">
-        <v>322</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="J97" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="K97" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="L97" t="s">
-        <v>283</v>
-      </c>
-      <c r="M97" t="s">
-        <v>284</v>
-      </c>
-      <c r="N97" t="s">
-        <v>285</v>
-      </c>
-      <c r="O97" t="s">
-        <v>286</v>
-      </c>
-      <c r="S97"/>
-    </row>
-    <row r="98" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>374</v>
-      </c>
-      <c r="B98" t="s">
-        <v>323</v>
       </c>
       <c r="C98" t="s">
         <v>156</v>
@@ -6119,40 +6326,37 @@
         <v>-2.9350000000000001</v>
       </c>
       <c r="F98" t="s">
-        <v>322</v>
-      </c>
-      <c r="G98" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J98" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K98" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="K98" s="2" t="s">
+      <c r="L98" t="s">
         <v>282</v>
       </c>
-      <c r="L98" t="s">
+      <c r="M98" t="s">
         <v>283</v>
       </c>
-      <c r="M98" t="s">
+      <c r="N98" t="s">
         <v>284</v>
       </c>
-      <c r="N98" t="s">
+      <c r="O98" t="s">
         <v>285</v>
       </c>
-      <c r="O98" t="s">
-        <v>286</v>
-      </c>
-      <c r="S98"/>
-    </row>
-    <row r="99" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="U98"/>
+    </row>
+    <row r="99" spans="1:21" ht="75.3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="B99" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C99" t="s">
         <v>156</v>
@@ -6164,43 +6368,52 @@
         <v>-4.0273000000000003</v>
       </c>
       <c r="F99" t="s">
-        <v>322</v>
-      </c>
-      <c r="G99" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>281</v>
+        <v>419</v>
       </c>
       <c r="K99" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="L99" t="s">
         <v>282</v>
       </c>
-      <c r="L99" t="s">
+      <c r="M99" t="s">
         <v>283</v>
       </c>
-      <c r="M99" t="s">
+      <c r="N99" t="s">
         <v>284</v>
       </c>
-      <c r="N99" t="s">
+      <c r="O99" t="s">
         <v>285</v>
       </c>
-      <c r="O99" t="s">
-        <v>286</v>
-      </c>
-      <c r="S99"/>
-    </row>
-    <row r="100" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="P99" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q99" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="R99" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="S99" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="U99"/>
+    </row>
+    <row r="100" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="B100" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C100" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D100">
         <v>59.576000000000001</v>
@@ -6209,43 +6422,49 @@
         <v>25.8</v>
       </c>
       <c r="F100" t="s">
-        <v>326</v>
-      </c>
-      <c r="G100" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H100" t="s">
         <v>62</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J100" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K100" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="K100" s="2" t="s">
+      <c r="L100" t="s">
         <v>282</v>
       </c>
-      <c r="L100" t="s">
+      <c r="M100" t="s">
         <v>283</v>
       </c>
-      <c r="M100" t="s">
+      <c r="N100" t="s">
         <v>284</v>
       </c>
-      <c r="N100" t="s">
+      <c r="O100" t="s">
         <v>285</v>
       </c>
-      <c r="O100" t="s">
-        <v>286</v>
-      </c>
-      <c r="S100"/>
-    </row>
-    <row r="101" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="P100" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>380</v>
+      </c>
+      <c r="R100" t="s">
+        <v>381</v>
+      </c>
+      <c r="U100"/>
+    </row>
+    <row r="101" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B101" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C101" t="s">
         <v>156</v>
@@ -6257,43 +6476,43 @@
         <v>-9.2063000000000006</v>
       </c>
       <c r="F101" t="s">
-        <v>327</v>
-      </c>
-      <c r="G101" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J101" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K101" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="K101" s="2" t="s">
+      <c r="L101" t="s">
         <v>282</v>
       </c>
-      <c r="L101" t="s">
+      <c r="M101" t="s">
         <v>283</v>
       </c>
-      <c r="M101" t="s">
+      <c r="N101" t="s">
         <v>284</v>
       </c>
-      <c r="N101" t="s">
+      <c r="O101" t="s">
         <v>285</v>
       </c>
-      <c r="O101" t="s">
-        <v>286</v>
-      </c>
-      <c r="S101"/>
-    </row>
-    <row r="102" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="P101" t="s">
+        <v>379</v>
+      </c>
+      <c r="U101"/>
+    </row>
+    <row r="102" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="B102" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C102" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D102">
         <v>45.232999999999997</v>
@@ -6302,43 +6521,46 @@
         <v>-78.882999999999996</v>
       </c>
       <c r="F102" t="s">
-        <v>328</v>
-      </c>
-      <c r="G102" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J102" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K102" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="K102" s="2" t="s">
+      <c r="L102" t="s">
         <v>282</v>
       </c>
-      <c r="L102" t="s">
+      <c r="M102" t="s">
         <v>283</v>
       </c>
-      <c r="M102" t="s">
+      <c r="N102" t="s">
         <v>284</v>
       </c>
-      <c r="N102" t="s">
+      <c r="O102" t="s">
         <v>285</v>
       </c>
-      <c r="O102" t="s">
-        <v>286</v>
-      </c>
-      <c r="S102"/>
-    </row>
-    <row r="103" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="P102" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>380</v>
+      </c>
+      <c r="U102"/>
+    </row>
+    <row r="103" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>379</v>
-      </c>
-      <c r="B103" t="s">
-        <v>384</v>
+        <v>373</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>378</v>
       </c>
       <c r="C103" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D103">
         <v>35.907899999999998</v>
@@ -6349,38 +6571,35 @@
       <c r="F103" t="s">
         <v>143</v>
       </c>
-      <c r="G103" t="s">
-        <v>143</v>
-      </c>
       <c r="I103" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J103" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K103" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="K103" s="2" t="s">
+      <c r="L103" t="s">
         <v>282</v>
       </c>
-      <c r="L103" t="s">
+      <c r="M103" t="s">
         <v>283</v>
       </c>
-      <c r="M103" t="s">
+      <c r="N103" t="s">
         <v>284</v>
       </c>
-      <c r="N103" t="s">
+      <c r="O103" t="s">
         <v>285</v>
       </c>
-      <c r="O103" t="s">
-        <v>286</v>
-      </c>
-      <c r="S103"/>
-    </row>
-    <row r="104" spans="1:19" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="U103"/>
+    </row>
+    <row r="104" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="B104" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C104" t="s">
         <v>156</v>
@@ -6394,31 +6613,508 @@
       <c r="F104" t="s">
         <v>143</v>
       </c>
-      <c r="G104" t="s">
+      <c r="I104" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K104" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="L104" t="s">
+        <v>282</v>
+      </c>
+      <c r="M104" t="s">
+        <v>283</v>
+      </c>
+      <c r="N104" t="s">
+        <v>284</v>
+      </c>
+      <c r="O104" t="s">
+        <v>285</v>
+      </c>
+      <c r="U104"/>
+    </row>
+    <row r="105" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>422</v>
+      </c>
+      <c r="B105" t="s">
+        <v>386</v>
+      </c>
+      <c r="C105" t="s">
+        <v>156</v>
+      </c>
+      <c r="D105">
+        <v>48.8566</v>
+      </c>
+      <c r="E105">
+        <v>2.3521999999999998</v>
+      </c>
+      <c r="F105" t="s">
+        <v>387</v>
+      </c>
+      <c r="I105" t="s">
+        <v>221</v>
+      </c>
+      <c r="J105" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="K105" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="L105" t="s">
+        <v>379</v>
+      </c>
+      <c r="M105" t="s">
+        <v>380</v>
+      </c>
+      <c r="N105" t="s">
+        <v>381</v>
+      </c>
+      <c r="O105" t="s">
+        <v>382</v>
+      </c>
+      <c r="U105"/>
+    </row>
+    <row r="106" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>423</v>
+      </c>
+      <c r="B106" t="s">
+        <v>388</v>
+      </c>
+      <c r="C106" t="s">
+        <v>156</v>
+      </c>
+      <c r="D106">
+        <v>52.52</v>
+      </c>
+      <c r="E106">
+        <v>13.404999999999999</v>
+      </c>
+      <c r="F106" t="s">
+        <v>295</v>
+      </c>
+      <c r="I106" t="s">
+        <v>221</v>
+      </c>
+      <c r="J106" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="K106" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="L106" t="s">
+        <v>379</v>
+      </c>
+      <c r="M106" t="s">
+        <v>380</v>
+      </c>
+      <c r="N106" t="s">
+        <v>381</v>
+      </c>
+      <c r="O106" t="s">
+        <v>382</v>
+      </c>
+      <c r="U106"/>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>424</v>
+      </c>
+      <c r="B107" t="s">
+        <v>389</v>
+      </c>
+      <c r="C107" t="s">
+        <v>156</v>
+      </c>
+      <c r="D107">
+        <v>32.085299999999997</v>
+      </c>
+      <c r="E107">
+        <v>34.781799999999997</v>
+      </c>
+      <c r="F107" t="s">
+        <v>390</v>
+      </c>
+      <c r="I107" t="s">
+        <v>221</v>
+      </c>
+      <c r="J107" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="K107" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="L107" t="s">
+        <v>379</v>
+      </c>
+      <c r="U107"/>
+    </row>
+    <row r="108" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>426</v>
+      </c>
+      <c r="B108" t="s">
+        <v>391</v>
+      </c>
+      <c r="C108" t="s">
+        <v>154</v>
+      </c>
+      <c r="D108">
+        <v>47.030999999999999</v>
+      </c>
+      <c r="E108">
+        <v>6.96</v>
+      </c>
+      <c r="F108" t="s">
+        <v>392</v>
+      </c>
+      <c r="I108" t="s">
+        <v>339</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="K108" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="L108" t="s">
+        <v>379</v>
+      </c>
+      <c r="M108" t="s">
+        <v>380</v>
+      </c>
+      <c r="N108" t="s">
+        <v>381</v>
+      </c>
+      <c r="O108" t="s">
+        <v>382</v>
+      </c>
+      <c r="U108"/>
+    </row>
+    <row r="109" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>428</v>
+      </c>
+      <c r="B109" t="s">
+        <v>393</v>
+      </c>
+      <c r="C109" t="s">
+        <v>156</v>
+      </c>
+      <c r="D109">
+        <v>51.507199999999997</v>
+      </c>
+      <c r="E109">
+        <v>-0.12759999999999999</v>
+      </c>
+      <c r="F109" t="s">
+        <v>144</v>
+      </c>
+      <c r="I109" t="s">
+        <v>221</v>
+      </c>
+      <c r="J109" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="K109" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="L109" t="s">
+        <v>379</v>
+      </c>
+      <c r="U109"/>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>427</v>
+      </c>
+      <c r="B110" t="s">
+        <v>394</v>
+      </c>
+      <c r="C110" t="s">
+        <v>156</v>
+      </c>
+      <c r="D110">
+        <v>34.052199999999999</v>
+      </c>
+      <c r="E110">
+        <v>-118.2437</v>
+      </c>
+      <c r="F110" t="s">
         <v>143</v>
       </c>
-      <c r="I104" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="J104" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="K104" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="L104" t="s">
-        <v>283</v>
-      </c>
-      <c r="M104" t="s">
-        <v>284</v>
-      </c>
-      <c r="N104" t="s">
-        <v>285</v>
-      </c>
-      <c r="O104" t="s">
-        <v>286</v>
-      </c>
-      <c r="S104"/>
+      <c r="I110" t="s">
+        <v>437</v>
+      </c>
+      <c r="J110" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="K110" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="L110" t="s">
+        <v>379</v>
+      </c>
+      <c r="U110"/>
+    </row>
+    <row r="111" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>434</v>
+      </c>
+      <c r="B111" t="s">
+        <v>395</v>
+      </c>
+      <c r="C111" t="s">
+        <v>156</v>
+      </c>
+      <c r="D111">
+        <v>51.221299999999999</v>
+      </c>
+      <c r="E111">
+        <v>4.4051</v>
+      </c>
+      <c r="F111" t="s">
+        <v>396</v>
+      </c>
+      <c r="I111" t="s">
+        <v>437</v>
+      </c>
+      <c r="J111" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="K111" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="L111" t="s">
+        <v>379</v>
+      </c>
+      <c r="U111"/>
+    </row>
+    <row r="112" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>435</v>
+      </c>
+      <c r="B112" t="s">
+        <v>397</v>
+      </c>
+      <c r="C112" t="s">
+        <v>156</v>
+      </c>
+      <c r="D112">
+        <v>50.264899999999997</v>
+      </c>
+      <c r="E112">
+        <v>19.023800000000001</v>
+      </c>
+      <c r="F112" t="s">
+        <v>398</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J112" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="K112" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="L112" t="s">
+        <v>380</v>
+      </c>
+      <c r="M112" t="s">
+        <v>381</v>
+      </c>
+      <c r="N112" t="s">
+        <v>382</v>
+      </c>
+      <c r="U112"/>
+    </row>
+    <row r="113" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>436</v>
+      </c>
+      <c r="B113" t="s">
+        <v>400</v>
+      </c>
+      <c r="C113" t="s">
+        <v>156</v>
+      </c>
+      <c r="D113">
+        <v>37.983800000000002</v>
+      </c>
+      <c r="E113">
+        <v>23.727499999999999</v>
+      </c>
+      <c r="F113" t="s">
+        <v>401</v>
+      </c>
+      <c r="I113" t="s">
+        <v>221</v>
+      </c>
+      <c r="J113" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="K113" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="L113" t="s">
+        <v>380</v>
+      </c>
+      <c r="M113" t="s">
+        <v>381</v>
+      </c>
+      <c r="N113" t="s">
+        <v>382</v>
+      </c>
+      <c r="U113"/>
+    </row>
+    <row r="114" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>438</v>
+      </c>
+      <c r="B114" t="s">
+        <v>403</v>
+      </c>
+      <c r="C114" t="s">
+        <v>156</v>
+      </c>
+      <c r="D114">
+        <v>56.949599999999997</v>
+      </c>
+      <c r="E114">
+        <v>24.1052</v>
+      </c>
+      <c r="F114" t="s">
+        <v>404</v>
+      </c>
+      <c r="I114" t="s">
+        <v>221</v>
+      </c>
+      <c r="J114" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="K114" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="L114" t="s">
+        <v>380</v>
+      </c>
+      <c r="M114" t="s">
+        <v>381</v>
+      </c>
+      <c r="N114" t="s">
+        <v>382</v>
+      </c>
+      <c r="U114"/>
+    </row>
+    <row r="115" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>439</v>
+      </c>
+      <c r="B115" t="s">
+        <v>406</v>
+      </c>
+      <c r="C115" t="s">
+        <v>156</v>
+      </c>
+      <c r="D115">
+        <v>48.208199999999998</v>
+      </c>
+      <c r="E115">
+        <v>16.373799999999999</v>
+      </c>
+      <c r="F115" t="s">
+        <v>407</v>
+      </c>
+      <c r="I115" t="s">
+        <v>221</v>
+      </c>
+      <c r="J115" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="K115" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="L115" t="s">
+        <v>381</v>
+      </c>
+      <c r="M115" t="s">
+        <v>382</v>
+      </c>
+      <c r="U115"/>
+    </row>
+    <row r="116" spans="1:21" ht="30.15" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>440</v>
+      </c>
+      <c r="B116" t="s">
+        <v>409</v>
+      </c>
+      <c r="C116" t="s">
+        <v>156</v>
+      </c>
+      <c r="D116">
+        <v>42.697699999999998</v>
+      </c>
+      <c r="E116">
+        <v>23.321899999999999</v>
+      </c>
+      <c r="F116" t="s">
+        <v>410</v>
+      </c>
+      <c r="I116" t="s">
+        <v>221</v>
+      </c>
+      <c r="J116" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="K116" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="L116" t="s">
+        <v>380</v>
+      </c>
+      <c r="M116" t="s">
+        <v>381</v>
+      </c>
+      <c r="U116"/>
+    </row>
+    <row r="117" spans="1:21" ht="45.2" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>441</v>
+      </c>
+      <c r="B117" t="s">
+        <v>412</v>
+      </c>
+      <c r="C117" t="s">
+        <v>156</v>
+      </c>
+      <c r="D117">
+        <v>59.931100000000001</v>
+      </c>
+      <c r="E117">
+        <v>30.360900000000001</v>
+      </c>
+      <c r="F117" t="s">
+        <v>61</v>
+      </c>
+      <c r="I117" t="s">
+        <v>221</v>
+      </c>
+      <c r="J117" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="K117" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="L117" t="s">
+        <v>382</v>
+      </c>
+      <c r="U117"/>
     </row>
   </sheetData>
   <hyperlinks>
